--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="101">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -280,7 +280,7 @@
     <t>['87', '90+3']</t>
   </si>
   <si>
-    <t>['-1']</t>
+    <t>['9005']</t>
   </si>
   <si>
     <t>['34', '36']</t>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>['74', '80']</t>
+  </si>
+  <si>
+    <t>['60']</t>
   </si>
   <si>
     <t>['21', '27', '39']</t>
@@ -2579,7 +2582,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2785,7 +2788,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3197,7 +3200,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q13">
         <v>4.33</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="103">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>['7', '31']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['12', '70', '90+3']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -678,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -934,7 +940,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1012,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -1140,7 +1146,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1218,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -1427,7 +1433,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1552,7 +1558,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1758,7 +1764,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1964,7 +1970,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2042,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -2170,7 +2176,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2251,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -2376,7 +2382,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2582,7 +2588,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2660,10 +2666,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -2788,7 +2794,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -2866,7 +2872,7 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ11">
         <v>2</v>
@@ -3200,7 +3206,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3357,6 +3363,418 @@
       </c>
       <c r="BP13">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7793109</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45689.75</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>91</v>
+      </c>
+      <c r="P14" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q14">
+        <v>3.2</v>
+      </c>
+      <c r="R14">
+        <v>2.1</v>
+      </c>
+      <c r="S14">
+        <v>3.5</v>
+      </c>
+      <c r="T14">
+        <v>1.44</v>
+      </c>
+      <c r="U14">
+        <v>2.63</v>
+      </c>
+      <c r="V14">
+        <v>3</v>
+      </c>
+      <c r="W14">
+        <v>1.36</v>
+      </c>
+      <c r="X14">
+        <v>9</v>
+      </c>
+      <c r="Y14">
+        <v>1.07</v>
+      </c>
+      <c r="Z14">
+        <v>2.55</v>
+      </c>
+      <c r="AA14">
+        <v>3</v>
+      </c>
+      <c r="AB14">
+        <v>2.8</v>
+      </c>
+      <c r="AC14">
+        <v>1.06</v>
+      </c>
+      <c r="AD14">
+        <v>8</v>
+      </c>
+      <c r="AE14">
+        <v>1.33</v>
+      </c>
+      <c r="AF14">
+        <v>3.15</v>
+      </c>
+      <c r="AG14">
+        <v>1.7</v>
+      </c>
+      <c r="AH14">
+        <v>1.95</v>
+      </c>
+      <c r="AI14">
+        <v>1.8</v>
+      </c>
+      <c r="AJ14">
+        <v>1.91</v>
+      </c>
+      <c r="AK14">
+        <v>1.39</v>
+      </c>
+      <c r="AL14">
+        <v>1.31</v>
+      </c>
+      <c r="AM14">
+        <v>1.55</v>
+      </c>
+      <c r="AN14">
+        <v>0.5</v>
+      </c>
+      <c r="AO14">
+        <v>1</v>
+      </c>
+      <c r="AP14">
+        <v>1.33</v>
+      </c>
+      <c r="AQ14">
+        <v>0.67</v>
+      </c>
+      <c r="AR14">
+        <v>1.54</v>
+      </c>
+      <c r="AS14">
+        <v>1.91</v>
+      </c>
+      <c r="AT14">
+        <v>3.45</v>
+      </c>
+      <c r="AU14">
+        <v>7</v>
+      </c>
+      <c r="AV14">
+        <v>5</v>
+      </c>
+      <c r="AW14">
+        <v>10</v>
+      </c>
+      <c r="AX14">
+        <v>9</v>
+      </c>
+      <c r="AY14">
+        <v>17</v>
+      </c>
+      <c r="AZ14">
+        <v>14</v>
+      </c>
+      <c r="BA14">
+        <v>3</v>
+      </c>
+      <c r="BB14">
+        <v>1</v>
+      </c>
+      <c r="BC14">
+        <v>4</v>
+      </c>
+      <c r="BD14">
+        <v>1.79</v>
+      </c>
+      <c r="BE14">
+        <v>6.5</v>
+      </c>
+      <c r="BF14">
+        <v>2.23</v>
+      </c>
+      <c r="BG14">
+        <v>1.4</v>
+      </c>
+      <c r="BH14">
+        <v>2.63</v>
+      </c>
+      <c r="BI14">
+        <v>1.68</v>
+      </c>
+      <c r="BJ14">
+        <v>2</v>
+      </c>
+      <c r="BK14">
+        <v>2.1</v>
+      </c>
+      <c r="BL14">
+        <v>1.62</v>
+      </c>
+      <c r="BM14">
+        <v>2.7</v>
+      </c>
+      <c r="BN14">
+        <v>1.38</v>
+      </c>
+      <c r="BO14">
+        <v>3.65</v>
+      </c>
+      <c r="BP14">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7793104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45689.85416666666</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>4</v>
+      </c>
+      <c r="O15" t="s">
+        <v>92</v>
+      </c>
+      <c r="P15" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q15">
+        <v>2.4</v>
+      </c>
+      <c r="R15">
+        <v>2.05</v>
+      </c>
+      <c r="S15">
+        <v>5.5</v>
+      </c>
+      <c r="T15">
+        <v>1.5</v>
+      </c>
+      <c r="U15">
+        <v>2.5</v>
+      </c>
+      <c r="V15">
+        <v>3.4</v>
+      </c>
+      <c r="W15">
+        <v>1.3</v>
+      </c>
+      <c r="X15">
+        <v>10</v>
+      </c>
+      <c r="Y15">
+        <v>1.06</v>
+      </c>
+      <c r="Z15">
+        <v>1.7</v>
+      </c>
+      <c r="AA15">
+        <v>3.6</v>
+      </c>
+      <c r="AB15">
+        <v>4.6</v>
+      </c>
+      <c r="AC15">
+        <v>1.08</v>
+      </c>
+      <c r="AD15">
+        <v>7</v>
+      </c>
+      <c r="AE15">
+        <v>1.41</v>
+      </c>
+      <c r="AF15">
+        <v>2.8</v>
+      </c>
+      <c r="AG15">
+        <v>2.05</v>
+      </c>
+      <c r="AH15">
+        <v>1.61</v>
+      </c>
+      <c r="AI15">
+        <v>2.1</v>
+      </c>
+      <c r="AJ15">
+        <v>1.67</v>
+      </c>
+      <c r="AK15">
+        <v>1.18</v>
+      </c>
+      <c r="AL15">
+        <v>1.3</v>
+      </c>
+      <c r="AM15">
+        <v>1.98</v>
+      </c>
+      <c r="AN15">
+        <v>1</v>
+      </c>
+      <c r="AO15">
+        <v>0.5</v>
+      </c>
+      <c r="AP15">
+        <v>1.67</v>
+      </c>
+      <c r="AQ15">
+        <v>0.33</v>
+      </c>
+      <c r="AR15">
+        <v>1.24</v>
+      </c>
+      <c r="AS15">
+        <v>1.11</v>
+      </c>
+      <c r="AT15">
+        <v>2.35</v>
+      </c>
+      <c r="AU15">
+        <v>6</v>
+      </c>
+      <c r="AV15">
+        <v>5</v>
+      </c>
+      <c r="AW15">
+        <v>15</v>
+      </c>
+      <c r="AX15">
+        <v>3</v>
+      </c>
+      <c r="AY15">
+        <v>21</v>
+      </c>
+      <c r="AZ15">
+        <v>8</v>
+      </c>
+      <c r="BA15">
+        <v>3</v>
+      </c>
+      <c r="BB15">
+        <v>5</v>
+      </c>
+      <c r="BC15">
+        <v>8</v>
+      </c>
+      <c r="BD15">
+        <v>1.43</v>
+      </c>
+      <c r="BE15">
+        <v>6.5</v>
+      </c>
+      <c r="BF15">
+        <v>3.65</v>
+      </c>
+      <c r="BG15">
+        <v>1.24</v>
+      </c>
+      <c r="BH15">
+        <v>3.55</v>
+      </c>
+      <c r="BI15">
+        <v>1.48</v>
+      </c>
+      <c r="BJ15">
+        <v>2.42</v>
+      </c>
+      <c r="BK15">
+        <v>1.85</v>
+      </c>
+      <c r="BL15">
+        <v>1.82</v>
+      </c>
+      <c r="BM15">
+        <v>2.45</v>
+      </c>
+      <c r="BN15">
+        <v>1.47</v>
+      </c>
+      <c r="BO15">
+        <v>3.4</v>
+      </c>
+      <c r="BP15">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="108">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -295,6 +295,15 @@
     <t>['12', '70', '90+3']</t>
   </si>
   <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['49', '64', '70', '90', '90+2']</t>
+  </si>
+  <si>
+    <t>['35', '5', '22']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -323,6 +332,12 @@
   </si>
   <si>
     <t>['40', '45+4']</t>
+  </si>
+  <si>
+    <t>['14', '45']</t>
+  </si>
+  <si>
+    <t>['45+2', '53']</t>
   </si>
 </sst>
 </file>
@@ -684,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP15"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -940,7 +955,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1021,7 +1036,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1146,7 +1161,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1227,7 +1242,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1430,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>0.33</v>
@@ -1558,7 +1573,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1636,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1764,7 +1779,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1842,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
         <v>3</v>
@@ -1970,7 +1985,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2051,7 +2066,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ7">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2176,7 +2191,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2254,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ8">
         <v>1.33</v>
@@ -2382,7 +2397,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2460,10 +2475,10 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ9">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2588,7 +2603,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2794,7 +2809,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -2875,7 +2890,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3081,7 +3096,7 @@
         <v>3</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3206,7 +3221,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3284,10 +3299,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -3775,6 +3790,830 @@
       </c>
       <c r="BP15">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7793107</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45690.75</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="s">
+        <v>93</v>
+      </c>
+      <c r="P16" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q16">
+        <v>3.6</v>
+      </c>
+      <c r="R16">
+        <v>1.91</v>
+      </c>
+      <c r="S16">
+        <v>3.6</v>
+      </c>
+      <c r="T16">
+        <v>1.57</v>
+      </c>
+      <c r="U16">
+        <v>2.25</v>
+      </c>
+      <c r="V16">
+        <v>3.75</v>
+      </c>
+      <c r="W16">
+        <v>1.25</v>
+      </c>
+      <c r="X16">
+        <v>13</v>
+      </c>
+      <c r="Y16">
+        <v>1.04</v>
+      </c>
+      <c r="Z16">
+        <v>2.81</v>
+      </c>
+      <c r="AA16">
+        <v>2.84</v>
+      </c>
+      <c r="AB16">
+        <v>2.76</v>
+      </c>
+      <c r="AC16">
+        <v>1.08</v>
+      </c>
+      <c r="AD16">
+        <v>7</v>
+      </c>
+      <c r="AE16">
+        <v>1.5</v>
+      </c>
+      <c r="AF16">
+        <v>2.4</v>
+      </c>
+      <c r="AG16">
+        <v>2.56</v>
+      </c>
+      <c r="AH16">
+        <v>1.45</v>
+      </c>
+      <c r="AI16">
+        <v>2.2</v>
+      </c>
+      <c r="AJ16">
+        <v>1.62</v>
+      </c>
+      <c r="AK16">
+        <v>1.49</v>
+      </c>
+      <c r="AL16">
+        <v>1.32</v>
+      </c>
+      <c r="AM16">
+        <v>1.44</v>
+      </c>
+      <c r="AN16">
+        <v>0.5</v>
+      </c>
+      <c r="AO16">
+        <v>2</v>
+      </c>
+      <c r="AP16">
+        <v>1.33</v>
+      </c>
+      <c r="AQ16">
+        <v>1.33</v>
+      </c>
+      <c r="AR16">
+        <v>1.31</v>
+      </c>
+      <c r="AS16">
+        <v>1.39</v>
+      </c>
+      <c r="AT16">
+        <v>2.7</v>
+      </c>
+      <c r="AU16">
+        <v>2</v>
+      </c>
+      <c r="AV16">
+        <v>2</v>
+      </c>
+      <c r="AW16">
+        <v>7</v>
+      </c>
+      <c r="AX16">
+        <v>12</v>
+      </c>
+      <c r="AY16">
+        <v>9</v>
+      </c>
+      <c r="AZ16">
+        <v>14</v>
+      </c>
+      <c r="BA16">
+        <v>7</v>
+      </c>
+      <c r="BB16">
+        <v>6</v>
+      </c>
+      <c r="BC16">
+        <v>13</v>
+      </c>
+      <c r="BD16">
+        <v>2.05</v>
+      </c>
+      <c r="BE16">
+        <v>7.5</v>
+      </c>
+      <c r="BF16">
+        <v>2</v>
+      </c>
+      <c r="BG16">
+        <v>1.4</v>
+      </c>
+      <c r="BH16">
+        <v>2.82</v>
+      </c>
+      <c r="BI16">
+        <v>1.68</v>
+      </c>
+      <c r="BJ16">
+        <v>2.11</v>
+      </c>
+      <c r="BK16">
+        <v>2.11</v>
+      </c>
+      <c r="BL16">
+        <v>1.68</v>
+      </c>
+      <c r="BM16">
+        <v>2.75</v>
+      </c>
+      <c r="BN16">
+        <v>1.42</v>
+      </c>
+      <c r="BO16">
+        <v>3.82</v>
+      </c>
+      <c r="BP16">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7793105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45690.85416666666</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <v>5</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="N17">
+        <v>7</v>
+      </c>
+      <c r="O17" t="s">
+        <v>94</v>
+      </c>
+      <c r="P17" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q17">
+        <v>1.95</v>
+      </c>
+      <c r="R17">
+        <v>2.3</v>
+      </c>
+      <c r="S17">
+        <v>7.5</v>
+      </c>
+      <c r="T17">
+        <v>1.33</v>
+      </c>
+      <c r="U17">
+        <v>3.25</v>
+      </c>
+      <c r="V17">
+        <v>2.63</v>
+      </c>
+      <c r="W17">
+        <v>1.44</v>
+      </c>
+      <c r="X17">
+        <v>6.5</v>
+      </c>
+      <c r="Y17">
+        <v>1.11</v>
+      </c>
+      <c r="Z17">
+        <v>1.42</v>
+      </c>
+      <c r="AA17">
+        <v>4.2</v>
+      </c>
+      <c r="AB17">
+        <v>7.7</v>
+      </c>
+      <c r="AC17">
+        <v>1.04</v>
+      </c>
+      <c r="AD17">
+        <v>10.5</v>
+      </c>
+      <c r="AE17">
+        <v>1.25</v>
+      </c>
+      <c r="AF17">
+        <v>3.6</v>
+      </c>
+      <c r="AG17">
+        <v>1.77</v>
+      </c>
+      <c r="AH17">
+        <v>1.98</v>
+      </c>
+      <c r="AI17">
+        <v>2.1</v>
+      </c>
+      <c r="AJ17">
+        <v>1.67</v>
+      </c>
+      <c r="AK17">
+        <v>1.1</v>
+      </c>
+      <c r="AL17">
+        <v>1.17</v>
+      </c>
+      <c r="AM17">
+        <v>2.65</v>
+      </c>
+      <c r="AN17">
+        <v>2</v>
+      </c>
+      <c r="AO17">
+        <v>0.5</v>
+      </c>
+      <c r="AP17">
+        <v>2.33</v>
+      </c>
+      <c r="AQ17">
+        <v>0.33</v>
+      </c>
+      <c r="AR17">
+        <v>1.68</v>
+      </c>
+      <c r="AS17">
+        <v>1.33</v>
+      </c>
+      <c r="AT17">
+        <v>3.01</v>
+      </c>
+      <c r="AU17">
+        <v>9</v>
+      </c>
+      <c r="AV17">
+        <v>6</v>
+      </c>
+      <c r="AW17">
+        <v>7</v>
+      </c>
+      <c r="AX17">
+        <v>1</v>
+      </c>
+      <c r="AY17">
+        <v>16</v>
+      </c>
+      <c r="AZ17">
+        <v>7</v>
+      </c>
+      <c r="BA17">
+        <v>7</v>
+      </c>
+      <c r="BB17">
+        <v>5</v>
+      </c>
+      <c r="BC17">
+        <v>12</v>
+      </c>
+      <c r="BD17">
+        <v>1.17</v>
+      </c>
+      <c r="BE17">
+        <v>9.4</v>
+      </c>
+      <c r="BF17">
+        <v>6</v>
+      </c>
+      <c r="BG17">
+        <v>1.38</v>
+      </c>
+      <c r="BH17">
+        <v>2.78</v>
+      </c>
+      <c r="BI17">
+        <v>1.7</v>
+      </c>
+      <c r="BJ17">
+        <v>2</v>
+      </c>
+      <c r="BK17">
+        <v>2.22</v>
+      </c>
+      <c r="BL17">
+        <v>1.55</v>
+      </c>
+      <c r="BM17">
+        <v>3.05</v>
+      </c>
+      <c r="BN17">
+        <v>1.31</v>
+      </c>
+      <c r="BO17">
+        <v>4.35</v>
+      </c>
+      <c r="BP17">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7793106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45691.375</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18">
+        <v>2</v>
+      </c>
+      <c r="O18" t="s">
+        <v>84</v>
+      </c>
+      <c r="P18" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q18">
+        <v>3.75</v>
+      </c>
+      <c r="R18">
+        <v>1.91</v>
+      </c>
+      <c r="S18">
+        <v>3.4</v>
+      </c>
+      <c r="T18">
+        <v>1.53</v>
+      </c>
+      <c r="U18">
+        <v>2.38</v>
+      </c>
+      <c r="V18">
+        <v>3.75</v>
+      </c>
+      <c r="W18">
+        <v>1.25</v>
+      </c>
+      <c r="X18">
+        <v>11</v>
+      </c>
+      <c r="Y18">
+        <v>1.05</v>
+      </c>
+      <c r="Z18">
+        <v>2.97</v>
+      </c>
+      <c r="AA18">
+        <v>2.78</v>
+      </c>
+      <c r="AB18">
+        <v>2.67</v>
+      </c>
+      <c r="AC18">
+        <v>1.08</v>
+      </c>
+      <c r="AD18">
+        <v>7</v>
+      </c>
+      <c r="AE18">
+        <v>1.46</v>
+      </c>
+      <c r="AF18">
+        <v>2.6</v>
+      </c>
+      <c r="AG18">
+        <v>2.3</v>
+      </c>
+      <c r="AH18">
+        <v>1.5</v>
+      </c>
+      <c r="AI18">
+        <v>2.1</v>
+      </c>
+      <c r="AJ18">
+        <v>1.67</v>
+      </c>
+      <c r="AK18">
+        <v>1.51</v>
+      </c>
+      <c r="AL18">
+        <v>1.33</v>
+      </c>
+      <c r="AM18">
+        <v>1.4</v>
+      </c>
+      <c r="AN18">
+        <v>2</v>
+      </c>
+      <c r="AO18">
+        <v>3</v>
+      </c>
+      <c r="AP18">
+        <v>1.33</v>
+      </c>
+      <c r="AQ18">
+        <v>3</v>
+      </c>
+      <c r="AR18">
+        <v>1.16</v>
+      </c>
+      <c r="AS18">
+        <v>0.98</v>
+      </c>
+      <c r="AT18">
+        <v>2.14</v>
+      </c>
+      <c r="AU18">
+        <v>2</v>
+      </c>
+      <c r="AV18">
+        <v>5</v>
+      </c>
+      <c r="AW18">
+        <v>7</v>
+      </c>
+      <c r="AX18">
+        <v>3</v>
+      </c>
+      <c r="AY18">
+        <v>9</v>
+      </c>
+      <c r="AZ18">
+        <v>8</v>
+      </c>
+      <c r="BA18">
+        <v>4</v>
+      </c>
+      <c r="BB18">
+        <v>4</v>
+      </c>
+      <c r="BC18">
+        <v>8</v>
+      </c>
+      <c r="BD18">
+        <v>1.88</v>
+      </c>
+      <c r="BE18">
+        <v>6.15</v>
+      </c>
+      <c r="BF18">
+        <v>2.36</v>
+      </c>
+      <c r="BG18">
+        <v>1.3</v>
+      </c>
+      <c r="BH18">
+        <v>2.97</v>
+      </c>
+      <c r="BI18">
+        <v>1.56</v>
+      </c>
+      <c r="BJ18">
+        <v>2.16</v>
+      </c>
+      <c r="BK18">
+        <v>2</v>
+      </c>
+      <c r="BL18">
+        <v>1.69</v>
+      </c>
+      <c r="BM18">
+        <v>2.59</v>
+      </c>
+      <c r="BN18">
+        <v>1.39</v>
+      </c>
+      <c r="BO18">
+        <v>3.58</v>
+      </c>
+      <c r="BP18">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7793108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45691.83333333334</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>3</v>
+      </c>
+      <c r="O19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P19" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q19">
+        <v>1.83</v>
+      </c>
+      <c r="R19">
+        <v>2.5</v>
+      </c>
+      <c r="S19">
+        <v>7.5</v>
+      </c>
+      <c r="T19">
+        <v>1.3</v>
+      </c>
+      <c r="U19">
+        <v>3.4</v>
+      </c>
+      <c r="V19">
+        <v>2.5</v>
+      </c>
+      <c r="W19">
+        <v>1.5</v>
+      </c>
+      <c r="X19">
+        <v>6</v>
+      </c>
+      <c r="Y19">
+        <v>1.13</v>
+      </c>
+      <c r="Z19">
+        <v>1.37</v>
+      </c>
+      <c r="AA19">
+        <v>4.7</v>
+      </c>
+      <c r="AB19">
+        <v>7.8</v>
+      </c>
+      <c r="AC19">
+        <v>1.04</v>
+      </c>
+      <c r="AD19">
+        <v>9.5</v>
+      </c>
+      <c r="AE19">
+        <v>1.21</v>
+      </c>
+      <c r="AF19">
+        <v>4.1</v>
+      </c>
+      <c r="AG19">
+        <v>1.8</v>
+      </c>
+      <c r="AH19">
+        <v>1.92</v>
+      </c>
+      <c r="AI19">
+        <v>2</v>
+      </c>
+      <c r="AJ19">
+        <v>1.73</v>
+      </c>
+      <c r="AK19">
+        <v>1.07</v>
+      </c>
+      <c r="AL19">
+        <v>1.18</v>
+      </c>
+      <c r="AM19">
+        <v>3.1</v>
+      </c>
+      <c r="AN19">
+        <v>0.5</v>
+      </c>
+      <c r="AO19">
+        <v>1</v>
+      </c>
+      <c r="AP19">
+        <v>1.33</v>
+      </c>
+      <c r="AQ19">
+        <v>0.67</v>
+      </c>
+      <c r="AR19">
+        <v>1.79</v>
+      </c>
+      <c r="AS19">
+        <v>1.56</v>
+      </c>
+      <c r="AT19">
+        <v>3.35</v>
+      </c>
+      <c r="AU19">
+        <v>7</v>
+      </c>
+      <c r="AV19">
+        <v>2</v>
+      </c>
+      <c r="AW19">
+        <v>4</v>
+      </c>
+      <c r="AX19">
+        <v>4</v>
+      </c>
+      <c r="AY19">
+        <v>11</v>
+      </c>
+      <c r="AZ19">
+        <v>6</v>
+      </c>
+      <c r="BA19">
+        <v>2</v>
+      </c>
+      <c r="BB19">
+        <v>9</v>
+      </c>
+      <c r="BC19">
+        <v>11</v>
+      </c>
+      <c r="BD19">
+        <v>1.36</v>
+      </c>
+      <c r="BE19">
+        <v>9</v>
+      </c>
+      <c r="BF19">
+        <v>3.75</v>
+      </c>
+      <c r="BG19">
+        <v>1.44</v>
+      </c>
+      <c r="BH19">
+        <v>2.67</v>
+      </c>
+      <c r="BI19">
+        <v>1.74</v>
+      </c>
+      <c r="BJ19">
+        <v>2.02</v>
+      </c>
+      <c r="BK19">
+        <v>2.22</v>
+      </c>
+      <c r="BL19">
+        <v>1.62</v>
+      </c>
+      <c r="BM19">
+        <v>2.92</v>
+      </c>
+      <c r="BN19">
+        <v>1.38</v>
+      </c>
+      <c r="BO19">
+        <v>4.1</v>
+      </c>
+      <c r="BP19">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="110">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>['35', '5', '22']</t>
+  </si>
+  <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BP21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -955,7 +961,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1033,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ2">
         <v>1.33</v>
@@ -1161,7 +1167,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1448,7 +1454,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1573,7 +1579,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1654,7 +1660,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1779,7 +1785,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1985,7 +1991,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2063,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
         <v>2.33</v>
@@ -2191,7 +2197,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2272,7 +2278,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -2397,7 +2403,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2475,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
         <v>1.33</v>
@@ -2603,7 +2609,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2684,7 +2690,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ10">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -2809,7 +2815,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -2887,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ11">
         <v>2.33</v>
@@ -3221,7 +3227,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3505,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ14">
         <v>0.67</v>
@@ -3711,10 +3717,10 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -4045,7 +4051,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4126,7 +4132,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ17">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4251,7 +4257,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4614,6 +4620,418 @@
       </c>
       <c r="BP19">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7793115</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45696.76041666666</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" t="s">
+        <v>96</v>
+      </c>
+      <c r="P20" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q20">
+        <v>3.6</v>
+      </c>
+      <c r="R20">
+        <v>2.2</v>
+      </c>
+      <c r="S20">
+        <v>3</v>
+      </c>
+      <c r="T20">
+        <v>1.4</v>
+      </c>
+      <c r="U20">
+        <v>2.75</v>
+      </c>
+      <c r="V20">
+        <v>2.75</v>
+      </c>
+      <c r="W20">
+        <v>1.4</v>
+      </c>
+      <c r="X20">
+        <v>8</v>
+      </c>
+      <c r="Y20">
+        <v>1.08</v>
+      </c>
+      <c r="Z20">
+        <v>2.96</v>
+      </c>
+      <c r="AA20">
+        <v>3.45</v>
+      </c>
+      <c r="AB20">
+        <v>2.26</v>
+      </c>
+      <c r="AC20">
+        <v>1.06</v>
+      </c>
+      <c r="AD20">
+        <v>8</v>
+      </c>
+      <c r="AE20">
+        <v>1.3</v>
+      </c>
+      <c r="AF20">
+        <v>3.35</v>
+      </c>
+      <c r="AG20">
+        <v>1.87</v>
+      </c>
+      <c r="AH20">
+        <v>1.87</v>
+      </c>
+      <c r="AI20">
+        <v>1.73</v>
+      </c>
+      <c r="AJ20">
+        <v>2</v>
+      </c>
+      <c r="AK20">
+        <v>1.51</v>
+      </c>
+      <c r="AL20">
+        <v>1.31</v>
+      </c>
+      <c r="AM20">
+        <v>1.43</v>
+      </c>
+      <c r="AN20">
+        <v>0.33</v>
+      </c>
+      <c r="AO20">
+        <v>0.33</v>
+      </c>
+      <c r="AP20">
+        <v>1</v>
+      </c>
+      <c r="AQ20">
+        <v>0.25</v>
+      </c>
+      <c r="AR20">
+        <v>1.3</v>
+      </c>
+      <c r="AS20">
+        <v>1.13</v>
+      </c>
+      <c r="AT20">
+        <v>2.43</v>
+      </c>
+      <c r="AU20">
+        <v>7</v>
+      </c>
+      <c r="AV20">
+        <v>4</v>
+      </c>
+      <c r="AW20">
+        <v>5</v>
+      </c>
+      <c r="AX20">
+        <v>2</v>
+      </c>
+      <c r="AY20">
+        <v>12</v>
+      </c>
+      <c r="AZ20">
+        <v>6</v>
+      </c>
+      <c r="BA20">
+        <v>5</v>
+      </c>
+      <c r="BB20">
+        <v>3</v>
+      </c>
+      <c r="BC20">
+        <v>8</v>
+      </c>
+      <c r="BD20">
+        <v>2.3</v>
+      </c>
+      <c r="BE20">
+        <v>6.7</v>
+      </c>
+      <c r="BF20">
+        <v>1.82</v>
+      </c>
+      <c r="BG20">
+        <v>1.33</v>
+      </c>
+      <c r="BH20">
+        <v>2.98</v>
+      </c>
+      <c r="BI20">
+        <v>1.62</v>
+      </c>
+      <c r="BJ20">
+        <v>2.12</v>
+      </c>
+      <c r="BK20">
+        <v>2.08</v>
+      </c>
+      <c r="BL20">
+        <v>1.65</v>
+      </c>
+      <c r="BM20">
+        <v>2.9</v>
+      </c>
+      <c r="BN20">
+        <v>1.35</v>
+      </c>
+      <c r="BO20">
+        <v>4.25</v>
+      </c>
+      <c r="BP20">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7793110</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45696.85416666666</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
+        <v>97</v>
+      </c>
+      <c r="P21" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q21">
+        <v>4.86</v>
+      </c>
+      <c r="R21">
+        <v>2.19</v>
+      </c>
+      <c r="S21">
+        <v>2.43</v>
+      </c>
+      <c r="T21">
+        <v>1.4</v>
+      </c>
+      <c r="U21">
+        <v>2.83</v>
+      </c>
+      <c r="V21">
+        <v>3.03</v>
+      </c>
+      <c r="W21">
+        <v>1.36</v>
+      </c>
+      <c r="X21">
+        <v>9</v>
+      </c>
+      <c r="Y21">
+        <v>1.07</v>
+      </c>
+      <c r="Z21">
+        <v>4.2</v>
+      </c>
+      <c r="AA21">
+        <v>3.5</v>
+      </c>
+      <c r="AB21">
+        <v>1.82</v>
+      </c>
+      <c r="AC21">
+        <v>1.04</v>
+      </c>
+      <c r="AD21">
+        <v>8.5</v>
+      </c>
+      <c r="AE21">
+        <v>1.33</v>
+      </c>
+      <c r="AF21">
+        <v>3</v>
+      </c>
+      <c r="AG21">
+        <v>2</v>
+      </c>
+      <c r="AH21">
+        <v>1.75</v>
+      </c>
+      <c r="AI21">
+        <v>1.9</v>
+      </c>
+      <c r="AJ21">
+        <v>1.86</v>
+      </c>
+      <c r="AK21">
+        <v>1.91</v>
+      </c>
+      <c r="AL21">
+        <v>1.26</v>
+      </c>
+      <c r="AM21">
+        <v>1.19</v>
+      </c>
+      <c r="AN21">
+        <v>1.33</v>
+      </c>
+      <c r="AO21">
+        <v>1.67</v>
+      </c>
+      <c r="AP21">
+        <v>1.75</v>
+      </c>
+      <c r="AQ21">
+        <v>1.25</v>
+      </c>
+      <c r="AR21">
+        <v>1.66</v>
+      </c>
+      <c r="AS21">
+        <v>1.48</v>
+      </c>
+      <c r="AT21">
+        <v>3.14</v>
+      </c>
+      <c r="AU21">
+        <v>2</v>
+      </c>
+      <c r="AV21">
+        <v>3</v>
+      </c>
+      <c r="AW21">
+        <v>3</v>
+      </c>
+      <c r="AX21">
+        <v>15</v>
+      </c>
+      <c r="AY21">
+        <v>5</v>
+      </c>
+      <c r="AZ21">
+        <v>18</v>
+      </c>
+      <c r="BA21">
+        <v>3</v>
+      </c>
+      <c r="BB21">
+        <v>9</v>
+      </c>
+      <c r="BC21">
+        <v>12</v>
+      </c>
+      <c r="BD21">
+        <v>2.5</v>
+      </c>
+      <c r="BE21">
+        <v>8</v>
+      </c>
+      <c r="BF21">
+        <v>1.67</v>
+      </c>
+      <c r="BG21">
+        <v>1.29</v>
+      </c>
+      <c r="BH21">
+        <v>3.35</v>
+      </c>
+      <c r="BI21">
+        <v>1.53</v>
+      </c>
+      <c r="BJ21">
+        <v>2.41</v>
+      </c>
+      <c r="BK21">
+        <v>1.87</v>
+      </c>
+      <c r="BL21">
+        <v>1.87</v>
+      </c>
+      <c r="BM21">
+        <v>2.38</v>
+      </c>
+      <c r="BN21">
+        <v>1.54</v>
+      </c>
+      <c r="BO21">
+        <v>3.2</v>
+      </c>
+      <c r="BP21">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="112">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -344,6 +344,12 @@
   </si>
   <si>
     <t>['45+2', '53']</t>
+  </si>
+  <si>
+    <t>['59']</t>
+  </si>
+  <si>
+    <t>['74']</t>
   </si>
 </sst>
 </file>
@@ -705,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP21"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1245,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ3">
         <v>0.67</v>
@@ -1863,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ6">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2072,7 +2078,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2687,7 +2693,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ10">
         <v>1.25</v>
@@ -2896,7 +2902,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ11">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3099,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="AP12">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AQ12">
         <v>1.33</v>
@@ -3308,7 +3314,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -3514,7 +3520,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ14">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -4129,7 +4135,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -4338,7 +4344,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AR18">
         <v>1.16</v>
@@ -4541,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ19">
         <v>0.67</v>
@@ -5032,6 +5038,418 @@
       </c>
       <c r="BP21">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7793111</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45697.76041666666</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" t="s">
+        <v>84</v>
+      </c>
+      <c r="P22" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q22">
+        <v>4.79</v>
+      </c>
+      <c r="R22">
+        <v>2.03</v>
+      </c>
+      <c r="S22">
+        <v>2.68</v>
+      </c>
+      <c r="T22">
+        <v>1.5</v>
+      </c>
+      <c r="U22">
+        <v>2.51</v>
+      </c>
+      <c r="V22">
+        <v>3.46</v>
+      </c>
+      <c r="W22">
+        <v>1.28</v>
+      </c>
+      <c r="X22">
+        <v>9.4</v>
+      </c>
+      <c r="Y22">
+        <v>1.04</v>
+      </c>
+      <c r="Z22">
+        <v>4</v>
+      </c>
+      <c r="AA22">
+        <v>3.18</v>
+      </c>
+      <c r="AB22">
+        <v>1.97</v>
+      </c>
+      <c r="AC22">
+        <v>1.08</v>
+      </c>
+      <c r="AD22">
+        <v>6.5</v>
+      </c>
+      <c r="AE22">
+        <v>1.48</v>
+      </c>
+      <c r="AF22">
+        <v>2.5</v>
+      </c>
+      <c r="AG22">
+        <v>2.3</v>
+      </c>
+      <c r="AH22">
+        <v>1.5</v>
+      </c>
+      <c r="AI22">
+        <v>2.05</v>
+      </c>
+      <c r="AJ22">
+        <v>1.73</v>
+      </c>
+      <c r="AK22">
+        <v>1.75</v>
+      </c>
+      <c r="AL22">
+        <v>1.3</v>
+      </c>
+      <c r="AM22">
+        <v>1.22</v>
+      </c>
+      <c r="AN22">
+        <v>0.67</v>
+      </c>
+      <c r="AO22">
+        <v>1.33</v>
+      </c>
+      <c r="AP22">
+        <v>0.5</v>
+      </c>
+      <c r="AQ22">
+        <v>1.75</v>
+      </c>
+      <c r="AR22">
+        <v>1.81</v>
+      </c>
+      <c r="AS22">
+        <v>1.69</v>
+      </c>
+      <c r="AT22">
+        <v>3.5</v>
+      </c>
+      <c r="AU22">
+        <v>2</v>
+      </c>
+      <c r="AV22">
+        <v>5</v>
+      </c>
+      <c r="AW22">
+        <v>13</v>
+      </c>
+      <c r="AX22">
+        <v>19</v>
+      </c>
+      <c r="AY22">
+        <v>15</v>
+      </c>
+      <c r="AZ22">
+        <v>24</v>
+      </c>
+      <c r="BA22">
+        <v>8</v>
+      </c>
+      <c r="BB22">
+        <v>6</v>
+      </c>
+      <c r="BC22">
+        <v>14</v>
+      </c>
+      <c r="BD22">
+        <v>2.75</v>
+      </c>
+      <c r="BE22">
+        <v>8</v>
+      </c>
+      <c r="BF22">
+        <v>1.62</v>
+      </c>
+      <c r="BG22">
+        <v>1.36</v>
+      </c>
+      <c r="BH22">
+        <v>2.98</v>
+      </c>
+      <c r="BI22">
+        <v>1.62</v>
+      </c>
+      <c r="BJ22">
+        <v>2.22</v>
+      </c>
+      <c r="BK22">
+        <v>2.02</v>
+      </c>
+      <c r="BL22">
+        <v>1.74</v>
+      </c>
+      <c r="BM22">
+        <v>2.6</v>
+      </c>
+      <c r="BN22">
+        <v>1.46</v>
+      </c>
+      <c r="BO22">
+        <v>3.58</v>
+      </c>
+      <c r="BP22">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7793114</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45697.85416666666</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>84</v>
+      </c>
+      <c r="P23" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q23">
+        <v>3.74</v>
+      </c>
+      <c r="R23">
+        <v>1.92</v>
+      </c>
+      <c r="S23">
+        <v>3.04</v>
+      </c>
+      <c r="T23">
+        <v>1.51</v>
+      </c>
+      <c r="U23">
+        <v>2.45</v>
+      </c>
+      <c r="V23">
+        <v>3.42</v>
+      </c>
+      <c r="W23">
+        <v>1.28</v>
+      </c>
+      <c r="X23">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y23">
+        <v>1.03</v>
+      </c>
+      <c r="Z23">
+        <v>3.03</v>
+      </c>
+      <c r="AA23">
+        <v>3.06</v>
+      </c>
+      <c r="AB23">
+        <v>2.42</v>
+      </c>
+      <c r="AC23">
+        <v>1.04</v>
+      </c>
+      <c r="AD23">
+        <v>7.1</v>
+      </c>
+      <c r="AE23">
+        <v>1.4</v>
+      </c>
+      <c r="AF23">
+        <v>2.56</v>
+      </c>
+      <c r="AG23">
+        <v>2.29</v>
+      </c>
+      <c r="AH23">
+        <v>1.55</v>
+      </c>
+      <c r="AI23">
+        <v>1.95</v>
+      </c>
+      <c r="AJ23">
+        <v>1.72</v>
+      </c>
+      <c r="AK23">
+        <v>1.51</v>
+      </c>
+      <c r="AL23">
+        <v>1.31</v>
+      </c>
+      <c r="AM23">
+        <v>1.33</v>
+      </c>
+      <c r="AN23">
+        <v>3</v>
+      </c>
+      <c r="AO23">
+        <v>2.33</v>
+      </c>
+      <c r="AP23">
+        <v>2.25</v>
+      </c>
+      <c r="AQ23">
+        <v>2.5</v>
+      </c>
+      <c r="AR23">
+        <v>1.04</v>
+      </c>
+      <c r="AS23">
+        <v>1.87</v>
+      </c>
+      <c r="AT23">
+        <v>2.91</v>
+      </c>
+      <c r="AU23">
+        <v>4</v>
+      </c>
+      <c r="AV23">
+        <v>5</v>
+      </c>
+      <c r="AW23">
+        <v>3</v>
+      </c>
+      <c r="AX23">
+        <v>5</v>
+      </c>
+      <c r="AY23">
+        <v>7</v>
+      </c>
+      <c r="AZ23">
+        <v>10</v>
+      </c>
+      <c r="BA23">
+        <v>3</v>
+      </c>
+      <c r="BB23">
+        <v>3</v>
+      </c>
+      <c r="BC23">
+        <v>6</v>
+      </c>
+      <c r="BD23">
+        <v>2.05</v>
+      </c>
+      <c r="BE23">
+        <v>7.5</v>
+      </c>
+      <c r="BF23">
+        <v>2.05</v>
+      </c>
+      <c r="BG23">
+        <v>1.36</v>
+      </c>
+      <c r="BH23">
+        <v>2.98</v>
+      </c>
+      <c r="BI23">
+        <v>1.62</v>
+      </c>
+      <c r="BJ23">
+        <v>2.22</v>
+      </c>
+      <c r="BK23">
+        <v>2.02</v>
+      </c>
+      <c r="BL23">
+        <v>1.74</v>
+      </c>
+      <c r="BM23">
+        <v>2.6</v>
+      </c>
+      <c r="BN23">
+        <v>1.46</v>
+      </c>
+      <c r="BO23">
+        <v>3.58</v>
+      </c>
+      <c r="BP23">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="113">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['79']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -711,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP23"/>
+  <dimension ref="A1:BP24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -967,7 +970,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1173,7 +1176,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1254,7 +1257,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ3">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1585,7 +1588,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1663,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -1791,7 +1794,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1997,7 +2000,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2203,7 +2206,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2281,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8">
         <v>1.75</v>
@@ -2409,7 +2412,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2615,7 +2618,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2821,7 +2824,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3108,7 +3111,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3233,7 +3236,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3929,7 +3932,7 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
         <v>1.33</v>
@@ -4057,7 +4060,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4263,7 +4266,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4550,7 +4553,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ19">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -5087,7 +5090,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5293,7 +5296,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5450,6 +5453,212 @@
       </c>
       <c r="BP23">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7793112</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45698.76041666666</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" t="s">
+        <v>98</v>
+      </c>
+      <c r="P24" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q24">
+        <v>3.4</v>
+      </c>
+      <c r="R24">
+        <v>2</v>
+      </c>
+      <c r="S24">
+        <v>3.5</v>
+      </c>
+      <c r="T24">
+        <v>1.5</v>
+      </c>
+      <c r="U24">
+        <v>2.5</v>
+      </c>
+      <c r="V24">
+        <v>3.5</v>
+      </c>
+      <c r="W24">
+        <v>1.29</v>
+      </c>
+      <c r="X24">
+        <v>10</v>
+      </c>
+      <c r="Y24">
+        <v>1.06</v>
+      </c>
+      <c r="Z24">
+        <v>2.67</v>
+      </c>
+      <c r="AA24">
+        <v>3.01</v>
+      </c>
+      <c r="AB24">
+        <v>2.75</v>
+      </c>
+      <c r="AC24">
+        <v>1.03</v>
+      </c>
+      <c r="AD24">
+        <v>7.5</v>
+      </c>
+      <c r="AE24">
+        <v>1.41</v>
+      </c>
+      <c r="AF24">
+        <v>2.8</v>
+      </c>
+      <c r="AG24">
+        <v>2.19</v>
+      </c>
+      <c r="AH24">
+        <v>1.6</v>
+      </c>
+      <c r="AI24">
+        <v>1.91</v>
+      </c>
+      <c r="AJ24">
+        <v>1.8</v>
+      </c>
+      <c r="AK24">
+        <v>1.43</v>
+      </c>
+      <c r="AL24">
+        <v>1.31</v>
+      </c>
+      <c r="AM24">
+        <v>1.45</v>
+      </c>
+      <c r="AN24">
+        <v>0.67</v>
+      </c>
+      <c r="AO24">
+        <v>1.33</v>
+      </c>
+      <c r="AP24">
+        <v>1.25</v>
+      </c>
+      <c r="AQ24">
+        <v>1</v>
+      </c>
+      <c r="AR24">
+        <v>1.38</v>
+      </c>
+      <c r="AS24">
+        <v>1.22</v>
+      </c>
+      <c r="AT24">
+        <v>2.6</v>
+      </c>
+      <c r="AU24">
+        <v>5</v>
+      </c>
+      <c r="AV24">
+        <v>2</v>
+      </c>
+      <c r="AW24">
+        <v>13</v>
+      </c>
+      <c r="AX24">
+        <v>5</v>
+      </c>
+      <c r="AY24">
+        <v>18</v>
+      </c>
+      <c r="AZ24">
+        <v>7</v>
+      </c>
+      <c r="BA24">
+        <v>3</v>
+      </c>
+      <c r="BB24">
+        <v>5</v>
+      </c>
+      <c r="BC24">
+        <v>8</v>
+      </c>
+      <c r="BD24">
+        <v>1.91</v>
+      </c>
+      <c r="BE24">
+        <v>7.5</v>
+      </c>
+      <c r="BF24">
+        <v>2.2</v>
+      </c>
+      <c r="BG24">
+        <v>1.4</v>
+      </c>
+      <c r="BH24">
+        <v>2.82</v>
+      </c>
+      <c r="BI24">
+        <v>1.68</v>
+      </c>
+      <c r="BJ24">
+        <v>2.12</v>
+      </c>
+      <c r="BK24">
+        <v>2.11</v>
+      </c>
+      <c r="BL24">
+        <v>1.68</v>
+      </c>
+      <c r="BM24">
+        <v>2.75</v>
+      </c>
+      <c r="BN24">
+        <v>1.42</v>
+      </c>
+      <c r="BO24">
+        <v>3.8</v>
+      </c>
+      <c r="BP24">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="114">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>['79']</t>
+  </si>
+  <si>
+    <t>['26']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -714,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP24"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -970,7 +973,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1051,7 +1054,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1176,7 +1179,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1460,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ4">
         <v>0.25</v>
@@ -1588,7 +1591,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1794,7 +1797,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2000,7 +2003,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2206,7 +2209,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2412,7 +2415,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2493,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="AQ9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2618,7 +2621,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2824,7 +2827,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3236,7 +3239,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3314,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13">
         <v>1.75</v>
@@ -3935,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4060,7 +4063,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4266,7 +4269,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4344,7 +4347,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18">
         <v>2.25</v>
@@ -5090,7 +5093,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5296,7 +5299,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5659,6 +5662,212 @@
       </c>
       <c r="BP24">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7793113</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45698.85416666666</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25" t="s">
+        <v>99</v>
+      </c>
+      <c r="P25" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q25">
+        <v>3.2</v>
+      </c>
+      <c r="R25">
+        <v>1.9</v>
+      </c>
+      <c r="S25">
+        <v>3.8</v>
+      </c>
+      <c r="T25">
+        <v>1.58</v>
+      </c>
+      <c r="U25">
+        <v>2.25</v>
+      </c>
+      <c r="V25">
+        <v>3.7</v>
+      </c>
+      <c r="W25">
+        <v>1.25</v>
+      </c>
+      <c r="X25">
+        <v>11.5</v>
+      </c>
+      <c r="Y25">
+        <v>1.02</v>
+      </c>
+      <c r="Z25">
+        <v>2.5</v>
+      </c>
+      <c r="AA25">
+        <v>2.94</v>
+      </c>
+      <c r="AB25">
+        <v>3.03</v>
+      </c>
+      <c r="AC25">
+        <v>1.1</v>
+      </c>
+      <c r="AD25">
+        <v>6.4</v>
+      </c>
+      <c r="AE25">
+        <v>1.49</v>
+      </c>
+      <c r="AF25">
+        <v>2.5</v>
+      </c>
+      <c r="AG25">
+        <v>2.3</v>
+      </c>
+      <c r="AH25">
+        <v>1.5</v>
+      </c>
+      <c r="AI25">
+        <v>2.08</v>
+      </c>
+      <c r="AJ25">
+        <v>1.67</v>
+      </c>
+      <c r="AK25">
+        <v>1.36</v>
+      </c>
+      <c r="AL25">
+        <v>1.34</v>
+      </c>
+      <c r="AM25">
+        <v>1.5</v>
+      </c>
+      <c r="AN25">
+        <v>1.33</v>
+      </c>
+      <c r="AO25">
+        <v>1.33</v>
+      </c>
+      <c r="AP25">
+        <v>1.25</v>
+      </c>
+      <c r="AQ25">
+        <v>1.25</v>
+      </c>
+      <c r="AR25">
+        <v>1.38</v>
+      </c>
+      <c r="AS25">
+        <v>1.18</v>
+      </c>
+      <c r="AT25">
+        <v>2.56</v>
+      </c>
+      <c r="AU25">
+        <v>6</v>
+      </c>
+      <c r="AV25">
+        <v>4</v>
+      </c>
+      <c r="AW25">
+        <v>6</v>
+      </c>
+      <c r="AX25">
+        <v>2</v>
+      </c>
+      <c r="AY25">
+        <v>12</v>
+      </c>
+      <c r="AZ25">
+        <v>6</v>
+      </c>
+      <c r="BA25">
+        <v>1</v>
+      </c>
+      <c r="BB25">
+        <v>2</v>
+      </c>
+      <c r="BC25">
+        <v>3</v>
+      </c>
+      <c r="BD25">
+        <v>1.8</v>
+      </c>
+      <c r="BE25">
+        <v>7.7</v>
+      </c>
+      <c r="BF25">
+        <v>2.31</v>
+      </c>
+      <c r="BG25">
+        <v>1.38</v>
+      </c>
+      <c r="BH25">
+        <v>2.62</v>
+      </c>
+      <c r="BI25">
+        <v>1.71</v>
+      </c>
+      <c r="BJ25">
+        <v>1.97</v>
+      </c>
+      <c r="BK25">
+        <v>2.17</v>
+      </c>
+      <c r="BL25">
+        <v>1.55</v>
+      </c>
+      <c r="BM25">
+        <v>2.92</v>
+      </c>
+      <c r="BN25">
+        <v>1.31</v>
+      </c>
+      <c r="BO25">
+        <v>4.1</v>
+      </c>
+      <c r="BP25">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="116">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -316,6 +316,9 @@
     <t>['26']</t>
   </si>
   <si>
+    <t>['23']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -356,6 +359,9 @@
   </si>
   <si>
     <t>['74']</t>
+  </si>
+  <si>
+    <t>['15']</t>
   </si>
 </sst>
 </file>
@@ -717,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -973,7 +979,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1179,7 +1185,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1260,7 +1266,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ3">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1463,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ4">
         <v>0.25</v>
@@ -1591,7 +1597,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1797,7 +1803,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2003,7 +2009,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2209,7 +2215,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2287,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ8">
         <v>1.75</v>
@@ -2415,7 +2421,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2496,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="AQ9">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2621,7 +2627,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2827,7 +2833,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3239,7 +3245,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -4063,7 +4069,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4269,7 +4275,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4347,7 +4353,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ18">
         <v>2.25</v>
@@ -4556,7 +4562,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ19">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -5093,7 +5099,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5299,7 +5305,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5583,7 +5589,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -5792,7 +5798,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ25">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -5868,6 +5874,212 @@
       </c>
       <c r="BP25">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7793119</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45702.375</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>2</v>
+      </c>
+      <c r="O26" t="s">
+        <v>100</v>
+      </c>
+      <c r="P26" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q26">
+        <v>2.6</v>
+      </c>
+      <c r="R26">
+        <v>2</v>
+      </c>
+      <c r="S26">
+        <v>4.6</v>
+      </c>
+      <c r="T26">
+        <v>1.51</v>
+      </c>
+      <c r="U26">
+        <v>2.4</v>
+      </c>
+      <c r="V26">
+        <v>3.2</v>
+      </c>
+      <c r="W26">
+        <v>1.3</v>
+      </c>
+      <c r="X26">
+        <v>7.3</v>
+      </c>
+      <c r="Y26">
+        <v>1.06</v>
+      </c>
+      <c r="Z26">
+        <v>1.8</v>
+      </c>
+      <c r="AA26">
+        <v>3.5</v>
+      </c>
+      <c r="AB26">
+        <v>4.33</v>
+      </c>
+      <c r="AC26">
+        <v>1.07</v>
+      </c>
+      <c r="AD26">
+        <v>7</v>
+      </c>
+      <c r="AE26">
+        <v>1.42</v>
+      </c>
+      <c r="AF26">
+        <v>2.75</v>
+      </c>
+      <c r="AG26">
+        <v>2.28</v>
+      </c>
+      <c r="AH26">
+        <v>1.58</v>
+      </c>
+      <c r="AI26">
+        <v>2.01</v>
+      </c>
+      <c r="AJ26">
+        <v>1.72</v>
+      </c>
+      <c r="AK26">
+        <v>1.23</v>
+      </c>
+      <c r="AL26">
+        <v>1.31</v>
+      </c>
+      <c r="AM26">
+        <v>1.74</v>
+      </c>
+      <c r="AN26">
+        <v>1.25</v>
+      </c>
+      <c r="AO26">
+        <v>1.25</v>
+      </c>
+      <c r="AP26">
+        <v>1.2</v>
+      </c>
+      <c r="AQ26">
+        <v>1.2</v>
+      </c>
+      <c r="AR26">
+        <v>1.14</v>
+      </c>
+      <c r="AS26">
+        <v>1.54</v>
+      </c>
+      <c r="AT26">
+        <v>2.68</v>
+      </c>
+      <c r="AU26">
+        <v>2</v>
+      </c>
+      <c r="AV26">
+        <v>5</v>
+      </c>
+      <c r="AW26">
+        <v>7</v>
+      </c>
+      <c r="AX26">
+        <v>3</v>
+      </c>
+      <c r="AY26">
+        <v>9</v>
+      </c>
+      <c r="AZ26">
+        <v>8</v>
+      </c>
+      <c r="BA26">
+        <v>3</v>
+      </c>
+      <c r="BB26">
+        <v>2</v>
+      </c>
+      <c r="BC26">
+        <v>5</v>
+      </c>
+      <c r="BD26">
+        <v>1.67</v>
+      </c>
+      <c r="BE26">
+        <v>6.25</v>
+      </c>
+      <c r="BF26">
+        <v>2.48</v>
+      </c>
+      <c r="BG26">
+        <v>1.49</v>
+      </c>
+      <c r="BH26">
+        <v>2.38</v>
+      </c>
+      <c r="BI26">
+        <v>1.84</v>
+      </c>
+      <c r="BJ26">
+        <v>1.83</v>
+      </c>
+      <c r="BK26">
+        <v>2.35</v>
+      </c>
+      <c r="BL26">
+        <v>1.5</v>
+      </c>
+      <c r="BM26">
+        <v>3.05</v>
+      </c>
+      <c r="BN26">
+        <v>1.3</v>
+      </c>
+      <c r="BO26">
+        <v>4.1</v>
+      </c>
+      <c r="BP26">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="119">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -319,6 +319,12 @@
     <t>['23']</t>
   </si>
   <si>
+    <t>['6', '9', '78']</t>
+  </si>
+  <si>
+    <t>['12']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -362,6 +368,9 @@
   </si>
   <si>
     <t>['15']</t>
+  </si>
+  <si>
+    <t>['3', '72']</t>
   </si>
 </sst>
 </file>
@@ -723,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP26"/>
+  <dimension ref="A1:BP28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -979,7 +988,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1185,7 +1194,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1263,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ3">
         <v>1.2</v>
@@ -1472,7 +1481,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ4">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1597,7 +1606,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1675,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -1803,7 +1812,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1884,7 +1893,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ6">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2009,7 +2018,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2215,7 +2224,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2421,7 +2430,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2627,7 +2636,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2705,7 +2714,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ10">
         <v>1.25</v>
@@ -2833,7 +2842,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -2911,7 +2920,7 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ11">
         <v>2.5</v>
@@ -3117,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="AP12">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3245,7 +3254,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3532,7 +3541,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -3738,7 +3747,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -3941,7 +3950,7 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16">
         <v>1.25</v>
@@ -4069,7 +4078,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4275,7 +4284,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4356,7 +4365,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ18">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AR18">
         <v>1.16</v>
@@ -4768,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="AQ20">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR20">
         <v>1.3</v>
@@ -5099,7 +5108,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5177,7 +5186,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ22">
         <v>1.75</v>
@@ -5305,7 +5314,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5383,7 +5392,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ23">
         <v>2.5</v>
@@ -5592,7 +5601,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -5923,7 +5932,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6080,6 +6089,418 @@
       </c>
       <c r="BP26">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7793120</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45702.8125</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>3</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27" t="s">
+        <v>101</v>
+      </c>
+      <c r="P27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q27">
+        <v>2.87</v>
+      </c>
+      <c r="R27">
+        <v>1.93</v>
+      </c>
+      <c r="S27">
+        <v>3.9</v>
+      </c>
+      <c r="T27">
+        <v>1.51</v>
+      </c>
+      <c r="U27">
+        <v>2.35</v>
+      </c>
+      <c r="V27">
+        <v>3.4</v>
+      </c>
+      <c r="W27">
+        <v>1.27</v>
+      </c>
+      <c r="X27">
+        <v>9.75</v>
+      </c>
+      <c r="Y27">
+        <v>1.04</v>
+      </c>
+      <c r="Z27">
+        <v>2.54</v>
+      </c>
+      <c r="AA27">
+        <v>2.95</v>
+      </c>
+      <c r="AB27">
+        <v>2.96</v>
+      </c>
+      <c r="AC27">
+        <v>1.1</v>
+      </c>
+      <c r="AD27">
+        <v>6.25</v>
+      </c>
+      <c r="AE27">
+        <v>1.45</v>
+      </c>
+      <c r="AF27">
+        <v>2.6</v>
+      </c>
+      <c r="AG27">
+        <v>2.41</v>
+      </c>
+      <c r="AH27">
+        <v>1.5</v>
+      </c>
+      <c r="AI27">
+        <v>2.05</v>
+      </c>
+      <c r="AJ27">
+        <v>1.65</v>
+      </c>
+      <c r="AK27">
+        <v>1.31</v>
+      </c>
+      <c r="AL27">
+        <v>1.34</v>
+      </c>
+      <c r="AM27">
+        <v>1.63</v>
+      </c>
+      <c r="AN27">
+        <v>1</v>
+      </c>
+      <c r="AO27">
+        <v>0.5</v>
+      </c>
+      <c r="AP27">
+        <v>1.4</v>
+      </c>
+      <c r="AQ27">
+        <v>0.4</v>
+      </c>
+      <c r="AR27">
+        <v>1.17</v>
+      </c>
+      <c r="AS27">
+        <v>1.71</v>
+      </c>
+      <c r="AT27">
+        <v>2.88</v>
+      </c>
+      <c r="AU27">
+        <v>8</v>
+      </c>
+      <c r="AV27">
+        <v>7</v>
+      </c>
+      <c r="AW27">
+        <v>13</v>
+      </c>
+      <c r="AX27">
+        <v>14</v>
+      </c>
+      <c r="AY27">
+        <v>21</v>
+      </c>
+      <c r="AZ27">
+        <v>21</v>
+      </c>
+      <c r="BA27">
+        <v>4</v>
+      </c>
+      <c r="BB27">
+        <v>6</v>
+      </c>
+      <c r="BC27">
+        <v>10</v>
+      </c>
+      <c r="BD27">
+        <v>1.81</v>
+      </c>
+      <c r="BE27">
+        <v>6.25</v>
+      </c>
+      <c r="BF27">
+        <v>2.23</v>
+      </c>
+      <c r="BG27">
+        <v>1.53</v>
+      </c>
+      <c r="BH27">
+        <v>2.28</v>
+      </c>
+      <c r="BI27">
+        <v>1.88</v>
+      </c>
+      <c r="BJ27">
+        <v>1.78</v>
+      </c>
+      <c r="BK27">
+        <v>2.4</v>
+      </c>
+      <c r="BL27">
+        <v>1.48</v>
+      </c>
+      <c r="BM27">
+        <v>3.15</v>
+      </c>
+      <c r="BN27">
+        <v>1.29</v>
+      </c>
+      <c r="BO27">
+        <v>4.3</v>
+      </c>
+      <c r="BP27">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7793117</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45703.76041666666</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" t="s">
+        <v>79</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
+      </c>
+      <c r="O28" t="s">
+        <v>102</v>
+      </c>
+      <c r="P28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q28">
+        <v>3.25</v>
+      </c>
+      <c r="R28">
+        <v>1.93</v>
+      </c>
+      <c r="S28">
+        <v>3.4</v>
+      </c>
+      <c r="T28">
+        <v>1.51</v>
+      </c>
+      <c r="U28">
+        <v>2.37</v>
+      </c>
+      <c r="V28">
+        <v>3.4</v>
+      </c>
+      <c r="W28">
+        <v>1.27</v>
+      </c>
+      <c r="X28">
+        <v>9.75</v>
+      </c>
+      <c r="Y28">
+        <v>1.04</v>
+      </c>
+      <c r="Z28">
+        <v>2.68</v>
+      </c>
+      <c r="AA28">
+        <v>2.96</v>
+      </c>
+      <c r="AB28">
+        <v>2.79</v>
+      </c>
+      <c r="AC28">
+        <v>1.04</v>
+      </c>
+      <c r="AD28">
+        <v>6.95</v>
+      </c>
+      <c r="AE28">
+        <v>1.46</v>
+      </c>
+      <c r="AF28">
+        <v>2.6</v>
+      </c>
+      <c r="AG28">
+        <v>2.3</v>
+      </c>
+      <c r="AH28">
+        <v>1.5</v>
+      </c>
+      <c r="AI28">
+        <v>2.05</v>
+      </c>
+      <c r="AJ28">
+        <v>1.68</v>
+      </c>
+      <c r="AK28">
+        <v>1.43</v>
+      </c>
+      <c r="AL28">
+        <v>1.35</v>
+      </c>
+      <c r="AM28">
+        <v>1.46</v>
+      </c>
+      <c r="AN28">
+        <v>0.25</v>
+      </c>
+      <c r="AO28">
+        <v>2.25</v>
+      </c>
+      <c r="AP28">
+        <v>0.2</v>
+      </c>
+      <c r="AQ28">
+        <v>2.4</v>
+      </c>
+      <c r="AR28">
+        <v>1.14</v>
+      </c>
+      <c r="AS28">
+        <v>1.03</v>
+      </c>
+      <c r="AT28">
+        <v>2.17</v>
+      </c>
+      <c r="AU28">
+        <v>2</v>
+      </c>
+      <c r="AV28">
+        <v>7</v>
+      </c>
+      <c r="AW28">
+        <v>10</v>
+      </c>
+      <c r="AX28">
+        <v>3</v>
+      </c>
+      <c r="AY28">
+        <v>12</v>
+      </c>
+      <c r="AZ28">
+        <v>10</v>
+      </c>
+      <c r="BA28">
+        <v>5</v>
+      </c>
+      <c r="BB28">
+        <v>4</v>
+      </c>
+      <c r="BC28">
+        <v>9</v>
+      </c>
+      <c r="BD28">
+        <v>1.98</v>
+      </c>
+      <c r="BE28">
+        <v>6.25</v>
+      </c>
+      <c r="BF28">
+        <v>1.98</v>
+      </c>
+      <c r="BG28">
+        <v>1.52</v>
+      </c>
+      <c r="BH28">
+        <v>2.3</v>
+      </c>
+      <c r="BI28">
+        <v>1.87</v>
+      </c>
+      <c r="BJ28">
+        <v>1.8</v>
+      </c>
+      <c r="BK28">
+        <v>2.38</v>
+      </c>
+      <c r="BL28">
+        <v>1.48</v>
+      </c>
+      <c r="BM28">
+        <v>3.15</v>
+      </c>
+      <c r="BN28">
+        <v>1.29</v>
+      </c>
+      <c r="BO28">
+        <v>4.3</v>
+      </c>
+      <c r="BP28">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="121">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -325,6 +325,9 @@
     <t>['12']</t>
   </si>
   <si>
+    <t>['49', '77']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -371,6 +374,9 @@
   </si>
   <si>
     <t>['3', '72']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -732,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP28"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -988,7 +994,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1194,7 +1200,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1606,7 +1612,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1687,7 +1693,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1812,7 +1818,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2018,7 +2024,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2096,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ7">
         <v>2.5</v>
@@ -2224,7 +2230,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2430,7 +2436,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2508,7 +2514,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ9">
         <v>1.2</v>
@@ -2636,7 +2642,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2717,7 +2723,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ10">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -2842,7 +2848,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3254,7 +3260,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3744,7 +3750,7 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ15">
         <v>0.2</v>
@@ -4078,7 +4084,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4159,7 +4165,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4284,7 +4290,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4774,7 +4780,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ20">
         <v>0.2</v>
@@ -4983,7 +4989,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ21">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5108,7 +5114,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5314,7 +5320,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5932,7 +5938,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6344,7 +6350,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6501,6 +6507,212 @@
       </c>
       <c r="BP28">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7793116</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45703.85416666666</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>2</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+      <c r="O29" t="s">
+        <v>103</v>
+      </c>
+      <c r="P29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q29">
+        <v>1.8</v>
+      </c>
+      <c r="R29">
+        <v>2.38</v>
+      </c>
+      <c r="S29">
+        <v>10</v>
+      </c>
+      <c r="T29">
+        <v>1.4</v>
+      </c>
+      <c r="U29">
+        <v>2.75</v>
+      </c>
+      <c r="V29">
+        <v>2.75</v>
+      </c>
+      <c r="W29">
+        <v>1.4</v>
+      </c>
+      <c r="X29">
+        <v>8</v>
+      </c>
+      <c r="Y29">
+        <v>1.08</v>
+      </c>
+      <c r="Z29">
+        <v>1.31</v>
+      </c>
+      <c r="AA29">
+        <v>4.8</v>
+      </c>
+      <c r="AB29">
+        <v>10</v>
+      </c>
+      <c r="AC29">
+        <v>1.01</v>
+      </c>
+      <c r="AD29">
+        <v>10.4</v>
+      </c>
+      <c r="AE29">
+        <v>1.3</v>
+      </c>
+      <c r="AF29">
+        <v>3.46</v>
+      </c>
+      <c r="AG29">
+        <v>1.92</v>
+      </c>
+      <c r="AH29">
+        <v>1.82</v>
+      </c>
+      <c r="AI29">
+        <v>2.63</v>
+      </c>
+      <c r="AJ29">
+        <v>1.44</v>
+      </c>
+      <c r="AK29">
+        <v>1.07</v>
+      </c>
+      <c r="AL29">
+        <v>1.17</v>
+      </c>
+      <c r="AM29">
+        <v>3.1</v>
+      </c>
+      <c r="AN29">
+        <v>1.25</v>
+      </c>
+      <c r="AO29">
+        <v>1</v>
+      </c>
+      <c r="AP29">
+        <v>1.6</v>
+      </c>
+      <c r="AQ29">
+        <v>0.8</v>
+      </c>
+      <c r="AR29">
+        <v>1.56</v>
+      </c>
+      <c r="AS29">
+        <v>1.37</v>
+      </c>
+      <c r="AT29">
+        <v>2.93</v>
+      </c>
+      <c r="AU29">
+        <v>5</v>
+      </c>
+      <c r="AV29">
+        <v>4</v>
+      </c>
+      <c r="AW29">
+        <v>10</v>
+      </c>
+      <c r="AX29">
+        <v>3</v>
+      </c>
+      <c r="AY29">
+        <v>15</v>
+      </c>
+      <c r="AZ29">
+        <v>7</v>
+      </c>
+      <c r="BA29">
+        <v>3</v>
+      </c>
+      <c r="BB29">
+        <v>3</v>
+      </c>
+      <c r="BC29">
+        <v>6</v>
+      </c>
+      <c r="BD29">
+        <v>1.15</v>
+      </c>
+      <c r="BE29">
+        <v>11.25</v>
+      </c>
+      <c r="BF29">
+        <v>6.2</v>
+      </c>
+      <c r="BG29">
+        <v>1.28</v>
+      </c>
+      <c r="BH29">
+        <v>3.08</v>
+      </c>
+      <c r="BI29">
+        <v>1.53</v>
+      </c>
+      <c r="BJ29">
+        <v>2.21</v>
+      </c>
+      <c r="BK29">
+        <v>1.85</v>
+      </c>
+      <c r="BL29">
+        <v>1.85</v>
+      </c>
+      <c r="BM29">
+        <v>2.49</v>
+      </c>
+      <c r="BN29">
+        <v>1.42</v>
+      </c>
+      <c r="BO29">
+        <v>3.42</v>
+      </c>
+      <c r="BP29">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="124">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -328,6 +328,12 @@
     <t>['49', '77']</t>
   </si>
   <si>
+    <t>['10', '18', '38', '90+4']</t>
+  </si>
+  <si>
+    <t>['66', '75']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -377,6 +383,9 @@
   </si>
   <si>
     <t>['27']</t>
+  </si>
+  <si>
+    <t>['44', '70']</t>
   </si>
 </sst>
 </file>
@@ -738,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -994,7 +1003,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1072,10 +1081,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ2">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1200,7 +1209,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1612,7 +1621,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1818,7 +1827,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1896,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>2.4</v>
@@ -2024,7 +2033,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2105,7 +2114,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ7">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2230,7 +2239,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2311,7 +2320,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ8">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -2436,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2642,7 +2651,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2848,7 +2857,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -2929,7 +2938,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ11">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3260,7 +3269,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3338,10 +3347,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -3544,7 +3553,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14">
         <v>0.4</v>
@@ -3959,7 +3968,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ16">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4084,7 +4093,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4162,7 +4171,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ17">
         <v>0.8</v>
@@ -4290,7 +4299,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4574,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>1.2</v>
@@ -4986,7 +4995,7 @@
         <v>1.67</v>
       </c>
       <c r="AP21">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ21">
         <v>1.6</v>
@@ -5114,7 +5123,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5195,7 +5204,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ22">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5320,7 +5329,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5401,7 +5410,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ23">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AR23">
         <v>1.04</v>
@@ -5810,7 +5819,7 @@
         <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ25">
         <v>1.2</v>
@@ -5938,7 +5947,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6350,7 +6359,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6556,7 +6565,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6713,6 +6722,418 @@
       </c>
       <c r="BP29">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7793121</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45704.76041666666</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30">
+        <v>4</v>
+      </c>
+      <c r="M30">
+        <v>2</v>
+      </c>
+      <c r="N30">
+        <v>6</v>
+      </c>
+      <c r="O30" t="s">
+        <v>104</v>
+      </c>
+      <c r="P30" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q30">
+        <v>2.2</v>
+      </c>
+      <c r="R30">
+        <v>2.1</v>
+      </c>
+      <c r="S30">
+        <v>5.25</v>
+      </c>
+      <c r="T30">
+        <v>1.43</v>
+      </c>
+      <c r="U30">
+        <v>2.6</v>
+      </c>
+      <c r="V30">
+        <v>2.95</v>
+      </c>
+      <c r="W30">
+        <v>1.34</v>
+      </c>
+      <c r="X30">
+        <v>8</v>
+      </c>
+      <c r="Y30">
+        <v>1.07</v>
+      </c>
+      <c r="Z30">
+        <v>1.59</v>
+      </c>
+      <c r="AA30">
+        <v>3.79</v>
+      </c>
+      <c r="AB30">
+        <v>5.7</v>
+      </c>
+      <c r="AC30">
+        <v>1.03</v>
+      </c>
+      <c r="AD30">
+        <v>8.35</v>
+      </c>
+      <c r="AE30">
+        <v>1.37</v>
+      </c>
+      <c r="AF30">
+        <v>2.97</v>
+      </c>
+      <c r="AG30">
+        <v>2</v>
+      </c>
+      <c r="AH30">
+        <v>1.67</v>
+      </c>
+      <c r="AI30">
+        <v>2.05</v>
+      </c>
+      <c r="AJ30">
+        <v>1.66</v>
+      </c>
+      <c r="AK30">
+        <v>1.15</v>
+      </c>
+      <c r="AL30">
+        <v>1.26</v>
+      </c>
+      <c r="AM30">
+        <v>2.2</v>
+      </c>
+      <c r="AN30">
+        <v>1.75</v>
+      </c>
+      <c r="AO30">
+        <v>1.75</v>
+      </c>
+      <c r="AP30">
+        <v>2</v>
+      </c>
+      <c r="AQ30">
+        <v>1.4</v>
+      </c>
+      <c r="AR30">
+        <v>1.83</v>
+      </c>
+      <c r="AS30">
+        <v>1.39</v>
+      </c>
+      <c r="AT30">
+        <v>3.22</v>
+      </c>
+      <c r="AU30">
+        <v>7</v>
+      </c>
+      <c r="AV30">
+        <v>6</v>
+      </c>
+      <c r="AW30">
+        <v>8</v>
+      </c>
+      <c r="AX30">
+        <v>15</v>
+      </c>
+      <c r="AY30">
+        <v>15</v>
+      </c>
+      <c r="AZ30">
+        <v>21</v>
+      </c>
+      <c r="BA30">
+        <v>2</v>
+      </c>
+      <c r="BB30">
+        <v>5</v>
+      </c>
+      <c r="BC30">
+        <v>7</v>
+      </c>
+      <c r="BD30">
+        <v>1.73</v>
+      </c>
+      <c r="BE30">
+        <v>8</v>
+      </c>
+      <c r="BF30">
+        <v>2.5</v>
+      </c>
+      <c r="BG30">
+        <v>1.39</v>
+      </c>
+      <c r="BH30">
+        <v>2.77</v>
+      </c>
+      <c r="BI30">
+        <v>1.68</v>
+      </c>
+      <c r="BJ30">
+        <v>2.11</v>
+      </c>
+      <c r="BK30">
+        <v>2.11</v>
+      </c>
+      <c r="BL30">
+        <v>1.68</v>
+      </c>
+      <c r="BM30">
+        <v>2.7</v>
+      </c>
+      <c r="BN30">
+        <v>1.41</v>
+      </c>
+      <c r="BO30">
+        <v>3.65</v>
+      </c>
+      <c r="BP30">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7793118</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45704.85416666666</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" t="s">
+        <v>80</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>2</v>
+      </c>
+      <c r="O31" t="s">
+        <v>105</v>
+      </c>
+      <c r="P31" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q31">
+        <v>2.5</v>
+      </c>
+      <c r="R31">
+        <v>1.93</v>
+      </c>
+      <c r="S31">
+        <v>4.8</v>
+      </c>
+      <c r="T31">
+        <v>1.52</v>
+      </c>
+      <c r="U31">
+        <v>2.35</v>
+      </c>
+      <c r="V31">
+        <v>3.4</v>
+      </c>
+      <c r="W31">
+        <v>1.28</v>
+      </c>
+      <c r="X31">
+        <v>9.5</v>
+      </c>
+      <c r="Y31">
+        <v>1.04</v>
+      </c>
+      <c r="Z31">
+        <v>1.86</v>
+      </c>
+      <c r="AA31">
+        <v>3.26</v>
+      </c>
+      <c r="AB31">
+        <v>4.5</v>
+      </c>
+      <c r="AC31">
+        <v>1.09</v>
+      </c>
+      <c r="AD31">
+        <v>6.5</v>
+      </c>
+      <c r="AE31">
+        <v>1.45</v>
+      </c>
+      <c r="AF31">
+        <v>2.68</v>
+      </c>
+      <c r="AG31">
+        <v>2.35</v>
+      </c>
+      <c r="AH31">
+        <v>1.53</v>
+      </c>
+      <c r="AI31">
+        <v>2.15</v>
+      </c>
+      <c r="AJ31">
+        <v>1.6</v>
+      </c>
+      <c r="AK31">
+        <v>1.2</v>
+      </c>
+      <c r="AL31">
+        <v>1.32</v>
+      </c>
+      <c r="AM31">
+        <v>1.88</v>
+      </c>
+      <c r="AN31">
+        <v>2.5</v>
+      </c>
+      <c r="AO31">
+        <v>1.25</v>
+      </c>
+      <c r="AP31">
+        <v>2.6</v>
+      </c>
+      <c r="AQ31">
+        <v>1</v>
+      </c>
+      <c r="AR31">
+        <v>1.72</v>
+      </c>
+      <c r="AS31">
+        <v>1.41</v>
+      </c>
+      <c r="AT31">
+        <v>3.13</v>
+      </c>
+      <c r="AU31">
+        <v>7</v>
+      </c>
+      <c r="AV31">
+        <v>5</v>
+      </c>
+      <c r="AW31">
+        <v>7</v>
+      </c>
+      <c r="AX31">
+        <v>3</v>
+      </c>
+      <c r="AY31">
+        <v>14</v>
+      </c>
+      <c r="AZ31">
+        <v>8</v>
+      </c>
+      <c r="BA31">
+        <v>6</v>
+      </c>
+      <c r="BB31">
+        <v>3</v>
+      </c>
+      <c r="BC31">
+        <v>9</v>
+      </c>
+      <c r="BD31">
+        <v>1.49</v>
+      </c>
+      <c r="BE31">
+        <v>6.55</v>
+      </c>
+      <c r="BF31">
+        <v>3.4</v>
+      </c>
+      <c r="BG31">
+        <v>1.44</v>
+      </c>
+      <c r="BH31">
+        <v>2.6</v>
+      </c>
+      <c r="BI31">
+        <v>1.77</v>
+      </c>
+      <c r="BJ31">
+        <v>2.03</v>
+      </c>
+      <c r="BK31">
+        <v>2.25</v>
+      </c>
+      <c r="BL31">
+        <v>1.62</v>
+      </c>
+      <c r="BM31">
+        <v>2.8</v>
+      </c>
+      <c r="BN31">
+        <v>1.38</v>
+      </c>
+      <c r="BO31">
+        <v>3.8</v>
+      </c>
+      <c r="BP31">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="126">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -334,6 +334,9 @@
     <t>['66', '75']</t>
   </si>
   <si>
+    <t>['16']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -386,6 +389,9 @@
   </si>
   <si>
     <t>['44', '70']</t>
+  </si>
+  <si>
+    <t>['35', '50', '76']</t>
   </si>
 </sst>
 </file>
@@ -747,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP31"/>
+  <dimension ref="A1:BP33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1003,7 +1009,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1209,7 +1215,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1287,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ3">
         <v>1.2</v>
@@ -1493,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ4">
         <v>0.2</v>
@@ -1621,7 +1627,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1702,7 +1708,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1827,7 +1833,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1908,7 +1914,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2033,7 +2039,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2239,7 +2245,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2445,7 +2451,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2523,10 +2529,10 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ9">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2651,7 +2657,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2729,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ10">
         <v>1.6</v>
@@ -2857,7 +2863,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3141,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="AP12">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>1.4</v>
@@ -3269,7 +3275,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3556,7 +3562,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -4093,7 +4099,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4174,7 +4180,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ17">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4299,7 +4305,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4377,10 +4383,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ18">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AR18">
         <v>1.16</v>
@@ -4789,7 +4795,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ20">
         <v>0.2</v>
@@ -5123,7 +5129,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5201,7 +5207,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ22">
         <v>2</v>
@@ -5329,7 +5335,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5407,7 +5413,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>2.6</v>
@@ -5822,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -5947,7 +5953,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6025,7 +6031,7 @@
         <v>1.25</v>
       </c>
       <c r="AP26">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26">
         <v>1.2</v>
@@ -6234,7 +6240,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ27">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR27">
         <v>1.17</v>
@@ -6359,7 +6365,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6440,7 +6446,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ28">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AR28">
         <v>1.14</v>
@@ -6565,7 +6571,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6646,7 +6652,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -6771,7 +6777,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7134,6 +7140,418 @@
       </c>
       <c r="BP31">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7793127</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45709.76041666666</v>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32" t="s">
+        <v>79</v>
+      </c>
+      <c r="H32" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>3</v>
+      </c>
+      <c r="N32">
+        <v>4</v>
+      </c>
+      <c r="O32" t="s">
+        <v>106</v>
+      </c>
+      <c r="P32" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q32">
+        <v>2.6</v>
+      </c>
+      <c r="R32">
+        <v>2</v>
+      </c>
+      <c r="S32">
+        <v>5</v>
+      </c>
+      <c r="T32">
+        <v>1.5</v>
+      </c>
+      <c r="U32">
+        <v>2.5</v>
+      </c>
+      <c r="V32">
+        <v>3.5</v>
+      </c>
+      <c r="W32">
+        <v>1.29</v>
+      </c>
+      <c r="X32">
+        <v>11</v>
+      </c>
+      <c r="Y32">
+        <v>1.05</v>
+      </c>
+      <c r="Z32">
+        <v>1.85</v>
+      </c>
+      <c r="AA32">
+        <v>3.51</v>
+      </c>
+      <c r="AB32">
+        <v>4.1</v>
+      </c>
+      <c r="AC32">
+        <v>1.08</v>
+      </c>
+      <c r="AD32">
+        <v>7.25</v>
+      </c>
+      <c r="AE32">
+        <v>1.4</v>
+      </c>
+      <c r="AF32">
+        <v>2.7</v>
+      </c>
+      <c r="AG32">
+        <v>2.19</v>
+      </c>
+      <c r="AH32">
+        <v>1.6</v>
+      </c>
+      <c r="AI32">
+        <v>2.1</v>
+      </c>
+      <c r="AJ32">
+        <v>1.67</v>
+      </c>
+      <c r="AK32">
+        <v>1.27</v>
+      </c>
+      <c r="AL32">
+        <v>1.32</v>
+      </c>
+      <c r="AM32">
+        <v>1.72</v>
+      </c>
+      <c r="AN32">
+        <v>2.4</v>
+      </c>
+      <c r="AO32">
+        <v>0.8</v>
+      </c>
+      <c r="AP32">
+        <v>2</v>
+      </c>
+      <c r="AQ32">
+        <v>1.17</v>
+      </c>
+      <c r="AR32">
+        <v>1.08</v>
+      </c>
+      <c r="AS32">
+        <v>1.3</v>
+      </c>
+      <c r="AT32">
+        <v>2.38</v>
+      </c>
+      <c r="AU32">
+        <v>5</v>
+      </c>
+      <c r="AV32">
+        <v>5</v>
+      </c>
+      <c r="AW32">
+        <v>5</v>
+      </c>
+      <c r="AX32">
+        <v>1</v>
+      </c>
+      <c r="AY32">
+        <v>10</v>
+      </c>
+      <c r="AZ32">
+        <v>6</v>
+      </c>
+      <c r="BA32">
+        <v>1</v>
+      </c>
+      <c r="BB32">
+        <v>3</v>
+      </c>
+      <c r="BC32">
+        <v>4</v>
+      </c>
+      <c r="BD32">
+        <v>1.52</v>
+      </c>
+      <c r="BE32">
+        <v>6.8</v>
+      </c>
+      <c r="BF32">
+        <v>3.05</v>
+      </c>
+      <c r="BG32">
+        <v>1.52</v>
+      </c>
+      <c r="BH32">
+        <v>2.3</v>
+      </c>
+      <c r="BI32">
+        <v>2</v>
+      </c>
+      <c r="BJ32">
+        <v>1.7</v>
+      </c>
+      <c r="BK32">
+        <v>2.78</v>
+      </c>
+      <c r="BL32">
+        <v>1.38</v>
+      </c>
+      <c r="BM32">
+        <v>4.1</v>
+      </c>
+      <c r="BN32">
+        <v>1.19</v>
+      </c>
+      <c r="BO32">
+        <v>4.35</v>
+      </c>
+      <c r="BP32">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7793124</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45709.85416666666</v>
+      </c>
+      <c r="F33">
+        <v>6</v>
+      </c>
+      <c r="G33" t="s">
+        <v>71</v>
+      </c>
+      <c r="H33" t="s">
+        <v>72</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>84</v>
+      </c>
+      <c r="P33" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q33">
+        <v>3.3</v>
+      </c>
+      <c r="R33">
+        <v>1.93</v>
+      </c>
+      <c r="S33">
+        <v>3.5</v>
+      </c>
+      <c r="T33">
+        <v>1.55</v>
+      </c>
+      <c r="U33">
+        <v>2.32</v>
+      </c>
+      <c r="V33">
+        <v>3.62</v>
+      </c>
+      <c r="W33">
+        <v>1.25</v>
+      </c>
+      <c r="X33">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y33">
+        <v>1.02</v>
+      </c>
+      <c r="Z33">
+        <v>2.74</v>
+      </c>
+      <c r="AA33">
+        <v>2.92</v>
+      </c>
+      <c r="AB33">
+        <v>2.77</v>
+      </c>
+      <c r="AC33">
+        <v>1.09</v>
+      </c>
+      <c r="AD33">
+        <v>6</v>
+      </c>
+      <c r="AE33">
+        <v>1.46</v>
+      </c>
+      <c r="AF33">
+        <v>2.6</v>
+      </c>
+      <c r="AG33">
+        <v>2.3</v>
+      </c>
+      <c r="AH33">
+        <v>1.5</v>
+      </c>
+      <c r="AI33">
+        <v>1.98</v>
+      </c>
+      <c r="AJ33">
+        <v>1.74</v>
+      </c>
+      <c r="AK33">
+        <v>1.4</v>
+      </c>
+      <c r="AL33">
+        <v>1.36</v>
+      </c>
+      <c r="AM33">
+        <v>1.43</v>
+      </c>
+      <c r="AN33">
+        <v>0.4</v>
+      </c>
+      <c r="AO33">
+        <v>1.2</v>
+      </c>
+      <c r="AP33">
+        <v>0.5</v>
+      </c>
+      <c r="AQ33">
+        <v>1.17</v>
+      </c>
+      <c r="AR33">
+        <v>1.83</v>
+      </c>
+      <c r="AS33">
+        <v>1.12</v>
+      </c>
+      <c r="AT33">
+        <v>2.95</v>
+      </c>
+      <c r="AU33">
+        <v>2</v>
+      </c>
+      <c r="AV33">
+        <v>4</v>
+      </c>
+      <c r="AW33">
+        <v>6</v>
+      </c>
+      <c r="AX33">
+        <v>5</v>
+      </c>
+      <c r="AY33">
+        <v>8</v>
+      </c>
+      <c r="AZ33">
+        <v>9</v>
+      </c>
+      <c r="BA33">
+        <v>5</v>
+      </c>
+      <c r="BB33">
+        <v>9</v>
+      </c>
+      <c r="BC33">
+        <v>14</v>
+      </c>
+      <c r="BD33">
+        <v>1.98</v>
+      </c>
+      <c r="BE33">
+        <v>6.1</v>
+      </c>
+      <c r="BF33">
+        <v>2.02</v>
+      </c>
+      <c r="BG33">
+        <v>1.49</v>
+      </c>
+      <c r="BH33">
+        <v>2.38</v>
+      </c>
+      <c r="BI33">
+        <v>1.83</v>
+      </c>
+      <c r="BJ33">
+        <v>1.83</v>
+      </c>
+      <c r="BK33">
+        <v>2.33</v>
+      </c>
+      <c r="BL33">
+        <v>1.5</v>
+      </c>
+      <c r="BM33">
+        <v>3.15</v>
+      </c>
+      <c r="BN33">
+        <v>1.3</v>
+      </c>
+      <c r="BO33">
+        <v>4.1</v>
+      </c>
+      <c r="BP33">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="130">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -337,6 +337,12 @@
     <t>['16']</t>
   </si>
   <si>
+    <t>['79', '88']</t>
+  </si>
+  <si>
+    <t>['48']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -392,6 +398,12 @@
   </si>
   <si>
     <t>['35', '50', '76']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['44', '64']</t>
   </si>
 </sst>
 </file>
@@ -753,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP33"/>
+  <dimension ref="A1:BP35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1009,7 +1021,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1090,7 +1102,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1215,7 +1227,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1296,7 +1308,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ3">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1502,7 +1514,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ4">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1627,7 +1639,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1833,7 +1845,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2039,7 +2051,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2120,7 +2132,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ7">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2245,7 +2257,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2323,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>1.4</v>
@@ -2451,7 +2463,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2657,7 +2669,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2863,7 +2875,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -2941,10 +2953,10 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AQ11">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3275,7 +3287,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3353,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
         <v>2</v>
@@ -3768,7 +3780,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ15">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -3974,7 +3986,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4099,7 +4111,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4177,7 +4189,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ17">
         <v>1.17</v>
@@ -4305,7 +4317,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4592,7 +4604,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -4798,7 +4810,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ20">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR20">
         <v>1.3</v>
@@ -5129,7 +5141,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5335,7 +5347,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5416,7 +5428,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AR23">
         <v>1.04</v>
@@ -5619,7 +5631,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.4</v>
@@ -5825,7 +5837,7 @@
         <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25">
         <v>1.17</v>
@@ -5953,7 +5965,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6034,7 +6046,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ26">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>1.14</v>
@@ -6365,7 +6377,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6443,7 +6455,7 @@
         <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AQ28">
         <v>2</v>
@@ -6571,7 +6583,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6777,7 +6789,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7061,10 +7073,10 @@
         <v>1.25</v>
       </c>
       <c r="AP31">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR31">
         <v>1.72</v>
@@ -7189,7 +7201,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7552,6 +7564,418 @@
       </c>
       <c r="BP33">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7793126</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45710.76041666666</v>
+      </c>
+      <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34" t="s">
+        <v>80</v>
+      </c>
+      <c r="H34" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34" t="s">
+        <v>107</v>
+      </c>
+      <c r="P34" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q34">
+        <v>3.29</v>
+      </c>
+      <c r="R34">
+        <v>1.96</v>
+      </c>
+      <c r="S34">
+        <v>3.85</v>
+      </c>
+      <c r="T34">
+        <v>1.53</v>
+      </c>
+      <c r="U34">
+        <v>2.42</v>
+      </c>
+      <c r="V34">
+        <v>3.4</v>
+      </c>
+      <c r="W34">
+        <v>1.29</v>
+      </c>
+      <c r="X34">
+        <v>9</v>
+      </c>
+      <c r="Y34">
+        <v>1.03</v>
+      </c>
+      <c r="Z34">
+        <v>2.49</v>
+      </c>
+      <c r="AA34">
+        <v>3.01</v>
+      </c>
+      <c r="AB34">
+        <v>2.97</v>
+      </c>
+      <c r="AC34">
+        <v>1.09</v>
+      </c>
+      <c r="AD34">
+        <v>6</v>
+      </c>
+      <c r="AE34">
+        <v>1.5</v>
+      </c>
+      <c r="AF34">
+        <v>2.4</v>
+      </c>
+      <c r="AG34">
+        <v>2.37</v>
+      </c>
+      <c r="AH34">
+        <v>1.48</v>
+      </c>
+      <c r="AI34">
+        <v>2.1</v>
+      </c>
+      <c r="AJ34">
+        <v>1.67</v>
+      </c>
+      <c r="AK34">
+        <v>1.4</v>
+      </c>
+      <c r="AL34">
+        <v>1.36</v>
+      </c>
+      <c r="AM34">
+        <v>1.53</v>
+      </c>
+      <c r="AN34">
+        <v>1</v>
+      </c>
+      <c r="AO34">
+        <v>0.2</v>
+      </c>
+      <c r="AP34">
+        <v>1.33</v>
+      </c>
+      <c r="AQ34">
+        <v>0.17</v>
+      </c>
+      <c r="AR34">
+        <v>1.34</v>
+      </c>
+      <c r="AS34">
+        <v>1.16</v>
+      </c>
+      <c r="AT34">
+        <v>2.5</v>
+      </c>
+      <c r="AU34">
+        <v>4</v>
+      </c>
+      <c r="AV34">
+        <v>5</v>
+      </c>
+      <c r="AW34">
+        <v>7</v>
+      </c>
+      <c r="AX34">
+        <v>5</v>
+      </c>
+      <c r="AY34">
+        <v>11</v>
+      </c>
+      <c r="AZ34">
+        <v>10</v>
+      </c>
+      <c r="BA34">
+        <v>7</v>
+      </c>
+      <c r="BB34">
+        <v>4</v>
+      </c>
+      <c r="BC34">
+        <v>11</v>
+      </c>
+      <c r="BD34">
+        <v>1.9</v>
+      </c>
+      <c r="BE34">
+        <v>6.1</v>
+      </c>
+      <c r="BF34">
+        <v>2.15</v>
+      </c>
+      <c r="BG34">
+        <v>1.55</v>
+      </c>
+      <c r="BH34">
+        <v>2.25</v>
+      </c>
+      <c r="BI34">
+        <v>1.92</v>
+      </c>
+      <c r="BJ34">
+        <v>1.75</v>
+      </c>
+      <c r="BK34">
+        <v>2.48</v>
+      </c>
+      <c r="BL34">
+        <v>1.45</v>
+      </c>
+      <c r="BM34">
+        <v>3.3</v>
+      </c>
+      <c r="BN34">
+        <v>1.26</v>
+      </c>
+      <c r="BO34">
+        <v>4.4</v>
+      </c>
+      <c r="BP34">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7793125</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45710.85416666666</v>
+      </c>
+      <c r="F35">
+        <v>6</v>
+      </c>
+      <c r="G35" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" t="s">
+        <v>81</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>2</v>
+      </c>
+      <c r="N35">
+        <v>3</v>
+      </c>
+      <c r="O35" t="s">
+        <v>108</v>
+      </c>
+      <c r="P35" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q35">
+        <v>5.47</v>
+      </c>
+      <c r="R35">
+        <v>2.2</v>
+      </c>
+      <c r="S35">
+        <v>2.29</v>
+      </c>
+      <c r="T35">
+        <v>1.41</v>
+      </c>
+      <c r="U35">
+        <v>2.78</v>
+      </c>
+      <c r="V35">
+        <v>3.09</v>
+      </c>
+      <c r="W35">
+        <v>1.34</v>
+      </c>
+      <c r="X35">
+        <v>7.5</v>
+      </c>
+      <c r="Y35">
+        <v>1.06</v>
+      </c>
+      <c r="Z35">
+        <v>5.3</v>
+      </c>
+      <c r="AA35">
+        <v>3.14</v>
+      </c>
+      <c r="AB35">
+        <v>1.78</v>
+      </c>
+      <c r="AC35">
+        <v>1.05</v>
+      </c>
+      <c r="AD35">
+        <v>8</v>
+      </c>
+      <c r="AE35">
+        <v>1.36</v>
+      </c>
+      <c r="AF35">
+        <v>2.9</v>
+      </c>
+      <c r="AG35">
+        <v>2.05</v>
+      </c>
+      <c r="AH35">
+        <v>1.65</v>
+      </c>
+      <c r="AI35">
+        <v>2</v>
+      </c>
+      <c r="AJ35">
+        <v>1.73</v>
+      </c>
+      <c r="AK35">
+        <v>2.1</v>
+      </c>
+      <c r="AL35">
+        <v>1.3</v>
+      </c>
+      <c r="AM35">
+        <v>1.17</v>
+      </c>
+      <c r="AN35">
+        <v>1.2</v>
+      </c>
+      <c r="AO35">
+        <v>2.6</v>
+      </c>
+      <c r="AP35">
+        <v>1</v>
+      </c>
+      <c r="AQ35">
+        <v>2.67</v>
+      </c>
+      <c r="AR35">
+        <v>1.46</v>
+      </c>
+      <c r="AS35">
+        <v>1.71</v>
+      </c>
+      <c r="AT35">
+        <v>3.17</v>
+      </c>
+      <c r="AU35">
+        <v>2</v>
+      </c>
+      <c r="AV35">
+        <v>4</v>
+      </c>
+      <c r="AW35">
+        <v>7</v>
+      </c>
+      <c r="AX35">
+        <v>1</v>
+      </c>
+      <c r="AY35">
+        <v>9</v>
+      </c>
+      <c r="AZ35">
+        <v>5</v>
+      </c>
+      <c r="BA35">
+        <v>2</v>
+      </c>
+      <c r="BB35">
+        <v>3</v>
+      </c>
+      <c r="BC35">
+        <v>5</v>
+      </c>
+      <c r="BD35">
+        <v>3</v>
+      </c>
+      <c r="BE35">
+        <v>8</v>
+      </c>
+      <c r="BF35">
+        <v>1.53</v>
+      </c>
+      <c r="BG35">
+        <v>1.43</v>
+      </c>
+      <c r="BH35">
+        <v>2.63</v>
+      </c>
+      <c r="BI35">
+        <v>1.77</v>
+      </c>
+      <c r="BJ35">
+        <v>1.95</v>
+      </c>
+      <c r="BK35">
+        <v>2.22</v>
+      </c>
+      <c r="BL35">
+        <v>1.62</v>
+      </c>
+      <c r="BM35">
+        <v>2.85</v>
+      </c>
+      <c r="BN35">
+        <v>1.37</v>
+      </c>
+      <c r="BO35">
+        <v>3.9</v>
+      </c>
+      <c r="BP35">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="132">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -343,6 +343,9 @@
     <t>['48']</t>
   </si>
   <si>
+    <t>['37', '71']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -404,6 +407,9 @@
   </si>
   <si>
     <t>['44', '64']</t>
+  </si>
+  <si>
+    <t>['32']</t>
   </si>
 </sst>
 </file>
@@ -765,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP35"/>
+  <dimension ref="A1:BP36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1021,7 +1027,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1227,7 +1233,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1639,7 +1645,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1845,7 +1851,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1923,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ6">
         <v>2</v>
@@ -2051,7 +2057,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2129,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7">
         <v>2.67</v>
@@ -2257,7 +2263,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2463,7 +2469,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2669,7 +2675,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2750,7 +2756,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -2875,7 +2881,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3287,7 +3293,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3368,7 +3374,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -3777,7 +3783,7 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
         <v>0.17</v>
@@ -4111,7 +4117,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4317,7 +4323,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4601,7 +4607,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5016,7 +5022,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ21">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5141,7 +5147,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5222,7 +5228,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5347,7 +5353,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5965,7 +5971,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6377,7 +6383,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6583,7 +6589,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6661,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ29">
         <v>1.17</v>
@@ -6789,7 +6795,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6867,7 +6873,7 @@
         <v>1.75</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ30">
         <v>1.4</v>
@@ -7201,7 +7207,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7613,7 +7619,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7819,7 +7825,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -7975,6 +7981,212 @@
         <v>3.9</v>
       </c>
       <c r="BP35">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7793122</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45711.75</v>
+      </c>
+      <c r="F36">
+        <v>6</v>
+      </c>
+      <c r="G36" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36" t="s">
+        <v>75</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36">
+        <v>2</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36" t="s">
+        <v>109</v>
+      </c>
+      <c r="P36" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q36">
+        <v>3</v>
+      </c>
+      <c r="R36">
+        <v>1.95</v>
+      </c>
+      <c r="S36">
+        <v>3.7</v>
+      </c>
+      <c r="T36">
+        <v>1.49</v>
+      </c>
+      <c r="U36">
+        <v>2.4</v>
+      </c>
+      <c r="V36">
+        <v>3.25</v>
+      </c>
+      <c r="W36">
+        <v>1.29</v>
+      </c>
+      <c r="X36">
+        <v>9.25</v>
+      </c>
+      <c r="Y36">
+        <v>1.05</v>
+      </c>
+      <c r="Z36">
+        <v>2.27</v>
+      </c>
+      <c r="AA36">
+        <v>3.06</v>
+      </c>
+      <c r="AB36">
+        <v>3.31</v>
+      </c>
+      <c r="AC36">
+        <v>1.03</v>
+      </c>
+      <c r="AD36">
+        <v>7.2</v>
+      </c>
+      <c r="AE36">
+        <v>1.39</v>
+      </c>
+      <c r="AF36">
+        <v>2.59</v>
+      </c>
+      <c r="AG36">
+        <v>2.2</v>
+      </c>
+      <c r="AH36">
+        <v>1.53</v>
+      </c>
+      <c r="AI36">
+        <v>1.98</v>
+      </c>
+      <c r="AJ36">
+        <v>1.71</v>
+      </c>
+      <c r="AK36">
+        <v>1.35</v>
+      </c>
+      <c r="AL36">
+        <v>1.34</v>
+      </c>
+      <c r="AM36">
+        <v>1.57</v>
+      </c>
+      <c r="AN36">
+        <v>2</v>
+      </c>
+      <c r="AO36">
+        <v>1.6</v>
+      </c>
+      <c r="AP36">
+        <v>2.17</v>
+      </c>
+      <c r="AQ36">
+        <v>1.33</v>
+      </c>
+      <c r="AR36">
+        <v>1.8</v>
+      </c>
+      <c r="AS36">
+        <v>1.61</v>
+      </c>
+      <c r="AT36">
+        <v>3.41</v>
+      </c>
+      <c r="AU36">
+        <v>3</v>
+      </c>
+      <c r="AV36">
+        <v>3</v>
+      </c>
+      <c r="AW36">
+        <v>7</v>
+      </c>
+      <c r="AX36">
+        <v>6</v>
+      </c>
+      <c r="AY36">
+        <v>10</v>
+      </c>
+      <c r="AZ36">
+        <v>9</v>
+      </c>
+      <c r="BA36">
+        <v>2</v>
+      </c>
+      <c r="BB36">
+        <v>1</v>
+      </c>
+      <c r="BC36">
+        <v>3</v>
+      </c>
+      <c r="BD36">
+        <v>1.77</v>
+      </c>
+      <c r="BE36">
+        <v>6.1</v>
+      </c>
+      <c r="BF36">
+        <v>2.3</v>
+      </c>
+      <c r="BG36">
+        <v>1.47</v>
+      </c>
+      <c r="BH36">
+        <v>2.43</v>
+      </c>
+      <c r="BI36">
+        <v>1.79</v>
+      </c>
+      <c r="BJ36">
+        <v>1.88</v>
+      </c>
+      <c r="BK36">
+        <v>2.28</v>
+      </c>
+      <c r="BL36">
+        <v>1.53</v>
+      </c>
+      <c r="BM36">
+        <v>2.95</v>
+      </c>
+      <c r="BN36">
+        <v>1.33</v>
+      </c>
+      <c r="BO36">
+        <v>3.95</v>
+      </c>
+      <c r="BP36">
         <v>1.19</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="132">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -771,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP36"/>
+  <dimension ref="A1:BP37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1105,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2">
         <v>1.33</v>
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
         <v>1.17</v>
@@ -2344,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -3168,7 +3168,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3577,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14">
         <v>0.5</v>
@@ -3989,7 +3989,7 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16">
         <v>1.33</v>
@@ -5019,7 +5019,7 @@
         <v>1.67</v>
       </c>
       <c r="AP21">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21">
         <v>1.33</v>
@@ -5640,7 +5640,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -6255,7 +6255,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ27">
         <v>0.5</v>
@@ -6876,7 +6876,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ30">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.83</v>
@@ -8188,6 +8188,212 @@
       </c>
       <c r="BP36">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7793123</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45712.8125</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>84</v>
+      </c>
+      <c r="P37" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q37">
+        <v>2.94</v>
+      </c>
+      <c r="R37">
+        <v>2</v>
+      </c>
+      <c r="S37">
+        <v>3.62</v>
+      </c>
+      <c r="T37">
+        <v>1.44</v>
+      </c>
+      <c r="U37">
+        <v>2.61</v>
+      </c>
+      <c r="V37">
+        <v>3.1</v>
+      </c>
+      <c r="W37">
+        <v>1.33</v>
+      </c>
+      <c r="X37">
+        <v>7.6</v>
+      </c>
+      <c r="Y37">
+        <v>1.03</v>
+      </c>
+      <c r="Z37">
+        <v>2.36</v>
+      </c>
+      <c r="AA37">
+        <v>3.25</v>
+      </c>
+      <c r="AB37">
+        <v>2.95</v>
+      </c>
+      <c r="AC37">
+        <v>1.03</v>
+      </c>
+      <c r="AD37">
+        <v>7.5</v>
+      </c>
+      <c r="AE37">
+        <v>1.33</v>
+      </c>
+      <c r="AF37">
+        <v>2.81</v>
+      </c>
+      <c r="AG37">
+        <v>2.05</v>
+      </c>
+      <c r="AH37">
+        <v>1.61</v>
+      </c>
+      <c r="AI37">
+        <v>1.83</v>
+      </c>
+      <c r="AJ37">
+        <v>1.83</v>
+      </c>
+      <c r="AK37">
+        <v>1.35</v>
+      </c>
+      <c r="AL37">
+        <v>1.3</v>
+      </c>
+      <c r="AM37">
+        <v>1.52</v>
+      </c>
+      <c r="AN37">
+        <v>1.4</v>
+      </c>
+      <c r="AO37">
+        <v>1.4</v>
+      </c>
+      <c r="AP37">
+        <v>1.33</v>
+      </c>
+      <c r="AQ37">
+        <v>1.33</v>
+      </c>
+      <c r="AR37">
+        <v>1.52</v>
+      </c>
+      <c r="AS37">
+        <v>1.37</v>
+      </c>
+      <c r="AT37">
+        <v>2.89</v>
+      </c>
+      <c r="AU37">
+        <v>-1</v>
+      </c>
+      <c r="AV37">
+        <v>-1</v>
+      </c>
+      <c r="AW37">
+        <v>-1</v>
+      </c>
+      <c r="AX37">
+        <v>-1</v>
+      </c>
+      <c r="AY37">
+        <v>-1</v>
+      </c>
+      <c r="AZ37">
+        <v>-1</v>
+      </c>
+      <c r="BA37">
+        <v>-1</v>
+      </c>
+      <c r="BB37">
+        <v>-1</v>
+      </c>
+      <c r="BC37">
+        <v>-1</v>
+      </c>
+      <c r="BD37">
+        <v>1.62</v>
+      </c>
+      <c r="BE37">
+        <v>8</v>
+      </c>
+      <c r="BF37">
+        <v>2.62</v>
+      </c>
+      <c r="BG37">
+        <v>1.39</v>
+      </c>
+      <c r="BH37">
+        <v>2.77</v>
+      </c>
+      <c r="BI37">
+        <v>1.68</v>
+      </c>
+      <c r="BJ37">
+        <v>2.12</v>
+      </c>
+      <c r="BK37">
+        <v>2.11</v>
+      </c>
+      <c r="BL37">
+        <v>1.68</v>
+      </c>
+      <c r="BM37">
+        <v>2.7</v>
+      </c>
+      <c r="BN37">
+        <v>1.41</v>
+      </c>
+      <c r="BO37">
+        <v>3.65</v>
+      </c>
+      <c r="BP37">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="135">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -346,6 +346,12 @@
     <t>['37', '71']</t>
   </si>
   <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['12', '65', '89']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -410,6 +416,9 @@
   </si>
   <si>
     <t>['32']</t>
+  </si>
+  <si>
+    <t>['84']</t>
   </si>
 </sst>
 </file>
@@ -771,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP37"/>
+  <dimension ref="A1:BP39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1027,7 +1036,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1108,7 +1117,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1233,7 +1242,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1311,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -1645,7 +1654,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1726,7 +1735,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1851,7 +1860,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2057,7 +2066,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2138,7 +2147,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ7">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2263,7 +2272,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2469,7 +2478,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2547,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ9">
         <v>1.17</v>
@@ -2675,7 +2684,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2753,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -2881,7 +2890,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -2962,7 +2971,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ11">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3293,7 +3302,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3371,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13">
         <v>2.17</v>
@@ -3580,7 +3589,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -3992,7 +4001,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4117,7 +4126,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4195,10 +4204,10 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ17">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4323,7 +4332,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4813,7 +4822,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ20">
         <v>0.17</v>
@@ -5147,7 +5156,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5225,7 +5234,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ22">
         <v>2.17</v>
@@ -5353,7 +5362,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5434,7 +5443,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AR23">
         <v>1.04</v>
@@ -5843,7 +5852,7 @@
         <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ25">
         <v>1.17</v>
@@ -5971,7 +5980,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6258,7 +6267,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ27">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR27">
         <v>1.17</v>
@@ -6383,7 +6392,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6589,7 +6598,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6670,7 +6679,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ29">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -6795,7 +6804,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7079,10 +7088,10 @@
         <v>1.25</v>
       </c>
       <c r="AP31">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR31">
         <v>1.72</v>
@@ -7207,7 +7216,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7288,7 +7297,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR32">
         <v>1.08</v>
@@ -7491,7 +7500,7 @@
         <v>1.2</v>
       </c>
       <c r="AP33">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ33">
         <v>1.17</v>
@@ -7619,7 +7628,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7697,7 +7706,7 @@
         <v>0.2</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ34">
         <v>0.17</v>
@@ -7825,7 +7834,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -7906,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AR35">
         <v>1.46</v>
@@ -8031,7 +8040,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8394,6 +8403,418 @@
       </c>
       <c r="BP37">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7793129</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45716.76041666666</v>
+      </c>
+      <c r="F38">
+        <v>7</v>
+      </c>
+      <c r="G38" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" t="s">
+        <v>80</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>2</v>
+      </c>
+      <c r="O38" t="s">
+        <v>110</v>
+      </c>
+      <c r="P38" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q38">
+        <v>3.75</v>
+      </c>
+      <c r="R38">
+        <v>1.95</v>
+      </c>
+      <c r="S38">
+        <v>3.4</v>
+      </c>
+      <c r="T38">
+        <v>1.57</v>
+      </c>
+      <c r="U38">
+        <v>2.25</v>
+      </c>
+      <c r="V38">
+        <v>3.75</v>
+      </c>
+      <c r="W38">
+        <v>1.25</v>
+      </c>
+      <c r="X38">
+        <v>11</v>
+      </c>
+      <c r="Y38">
+        <v>1.05</v>
+      </c>
+      <c r="Z38">
+        <v>2.97</v>
+      </c>
+      <c r="AA38">
+        <v>3.08</v>
+      </c>
+      <c r="AB38">
+        <v>2.45</v>
+      </c>
+      <c r="AC38">
+        <v>1.1</v>
+      </c>
+      <c r="AD38">
+        <v>6.25</v>
+      </c>
+      <c r="AE38">
+        <v>1.49</v>
+      </c>
+      <c r="AF38">
+        <v>2.4</v>
+      </c>
+      <c r="AG38">
+        <v>2.41</v>
+      </c>
+      <c r="AH38">
+        <v>1.5</v>
+      </c>
+      <c r="AI38">
+        <v>2.1</v>
+      </c>
+      <c r="AJ38">
+        <v>1.67</v>
+      </c>
+      <c r="AK38">
+        <v>1.42</v>
+      </c>
+      <c r="AL38">
+        <v>1.36</v>
+      </c>
+      <c r="AM38">
+        <v>1.47</v>
+      </c>
+      <c r="AN38">
+        <v>1.17</v>
+      </c>
+      <c r="AO38">
+        <v>1.33</v>
+      </c>
+      <c r="AP38">
+        <v>1.14</v>
+      </c>
+      <c r="AQ38">
+        <v>1.29</v>
+      </c>
+      <c r="AR38">
+        <v>1.26</v>
+      </c>
+      <c r="AS38">
+        <v>1.32</v>
+      </c>
+      <c r="AT38">
+        <v>2.58</v>
+      </c>
+      <c r="AU38">
+        <v>7</v>
+      </c>
+      <c r="AV38">
+        <v>4</v>
+      </c>
+      <c r="AW38">
+        <v>4</v>
+      </c>
+      <c r="AX38">
+        <v>1</v>
+      </c>
+      <c r="AY38">
+        <v>11</v>
+      </c>
+      <c r="AZ38">
+        <v>5</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>9</v>
+      </c>
+      <c r="BC38">
+        <v>9</v>
+      </c>
+      <c r="BD38">
+        <v>2.1</v>
+      </c>
+      <c r="BE38">
+        <v>6.05</v>
+      </c>
+      <c r="BF38">
+        <v>2.1</v>
+      </c>
+      <c r="BG38">
+        <v>1.32</v>
+      </c>
+      <c r="BH38">
+        <v>2.88</v>
+      </c>
+      <c r="BI38">
+        <v>1.7</v>
+      </c>
+      <c r="BJ38">
+        <v>2.05</v>
+      </c>
+      <c r="BK38">
+        <v>2.05</v>
+      </c>
+      <c r="BL38">
+        <v>1.65</v>
+      </c>
+      <c r="BM38">
+        <v>2.7</v>
+      </c>
+      <c r="BN38">
+        <v>1.36</v>
+      </c>
+      <c r="BO38">
+        <v>3.78</v>
+      </c>
+      <c r="BP38">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7793131</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45716.85416666666</v>
+      </c>
+      <c r="F39">
+        <v>7</v>
+      </c>
+      <c r="G39" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>3</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>3</v>
+      </c>
+      <c r="O39" t="s">
+        <v>111</v>
+      </c>
+      <c r="P39" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q39">
+        <v>2.05</v>
+      </c>
+      <c r="R39">
+        <v>2.23</v>
+      </c>
+      <c r="S39">
+        <v>6</v>
+      </c>
+      <c r="T39">
+        <v>1.42</v>
+      </c>
+      <c r="U39">
+        <v>2.7</v>
+      </c>
+      <c r="V39">
+        <v>2.75</v>
+      </c>
+      <c r="W39">
+        <v>1.4</v>
+      </c>
+      <c r="X39">
+        <v>8.1</v>
+      </c>
+      <c r="Y39">
+        <v>1.02</v>
+      </c>
+      <c r="Z39">
+        <v>1.61</v>
+      </c>
+      <c r="AA39">
+        <v>3.78</v>
+      </c>
+      <c r="AB39">
+        <v>5.4</v>
+      </c>
+      <c r="AC39">
+        <v>1.03</v>
+      </c>
+      <c r="AD39">
+        <v>9</v>
+      </c>
+      <c r="AE39">
+        <v>1.32</v>
+      </c>
+      <c r="AF39">
+        <v>3.2</v>
+      </c>
+      <c r="AG39">
+        <v>1.91</v>
+      </c>
+      <c r="AH39">
+        <v>1.83</v>
+      </c>
+      <c r="AI39">
+        <v>2.01</v>
+      </c>
+      <c r="AJ39">
+        <v>1.72</v>
+      </c>
+      <c r="AK39">
+        <v>1.13</v>
+      </c>
+      <c r="AL39">
+        <v>1.22</v>
+      </c>
+      <c r="AM39">
+        <v>2.25</v>
+      </c>
+      <c r="AN39">
+        <v>2.67</v>
+      </c>
+      <c r="AO39">
+        <v>0.5</v>
+      </c>
+      <c r="AP39">
+        <v>2.71</v>
+      </c>
+      <c r="AQ39">
+        <v>0.43</v>
+      </c>
+      <c r="AR39">
+        <v>1.59</v>
+      </c>
+      <c r="AS39">
+        <v>1.72</v>
+      </c>
+      <c r="AT39">
+        <v>3.31</v>
+      </c>
+      <c r="AU39">
+        <v>6</v>
+      </c>
+      <c r="AV39">
+        <v>3</v>
+      </c>
+      <c r="AW39">
+        <v>6</v>
+      </c>
+      <c r="AX39">
+        <v>8</v>
+      </c>
+      <c r="AY39">
+        <v>12</v>
+      </c>
+      <c r="AZ39">
+        <v>11</v>
+      </c>
+      <c r="BA39">
+        <v>6</v>
+      </c>
+      <c r="BB39">
+        <v>9</v>
+      </c>
+      <c r="BC39">
+        <v>15</v>
+      </c>
+      <c r="BD39">
+        <v>1.43</v>
+      </c>
+      <c r="BE39">
+        <v>8.4</v>
+      </c>
+      <c r="BF39">
+        <v>3.34</v>
+      </c>
+      <c r="BG39">
+        <v>1.36</v>
+      </c>
+      <c r="BH39">
+        <v>2.69</v>
+      </c>
+      <c r="BI39">
+        <v>1.75</v>
+      </c>
+      <c r="BJ39">
+        <v>2.03</v>
+      </c>
+      <c r="BK39">
+        <v>2.21</v>
+      </c>
+      <c r="BL39">
+        <v>1.63</v>
+      </c>
+      <c r="BM39">
+        <v>2.88</v>
+      </c>
+      <c r="BN39">
+        <v>1.32</v>
+      </c>
+      <c r="BO39">
+        <v>3.6</v>
+      </c>
+      <c r="BP39">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="137">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -352,6 +352,9 @@
     <t>['12', '65', '89']</t>
   </si>
   <si>
+    <t>['8']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -419,6 +422,9 @@
   </si>
   <si>
     <t>['84']</t>
+  </si>
+  <si>
+    <t>['83']</t>
   </si>
 </sst>
 </file>
@@ -780,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP39"/>
+  <dimension ref="A1:BP40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1036,7 +1042,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1242,7 +1248,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1654,7 +1660,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1732,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5">
         <v>1.14</v>
@@ -1860,7 +1866,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1938,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>2</v>
@@ -2066,7 +2072,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2272,7 +2278,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2478,7 +2484,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2684,7 +2690,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2890,7 +2896,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3177,7 +3183,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3302,7 +3308,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3383,7 +3389,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ13">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -3998,7 +4004,7 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ16">
         <v>1.29</v>
@@ -4126,7 +4132,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4332,7 +4338,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4616,7 +4622,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5156,7 +5162,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5237,7 +5243,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ22">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5362,7 +5368,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5649,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -5980,7 +5986,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6264,7 +6270,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ27">
         <v>0.43</v>
@@ -6392,7 +6398,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6598,7 +6604,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6804,7 +6810,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6882,7 +6888,7 @@
         <v>1.75</v>
       </c>
       <c r="AP30">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>1.33</v>
@@ -7216,7 +7222,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7628,7 +7634,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7834,7 +7840,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8040,7 +8046,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8118,7 +8124,7 @@
         <v>1.6</v>
       </c>
       <c r="AP36">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -8327,7 +8333,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR37">
         <v>1.52</v>
@@ -8452,7 +8458,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8815,6 +8821,212 @@
       </c>
       <c r="BP39">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7793133</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45717.76041666666</v>
+      </c>
+      <c r="F40">
+        <v>7</v>
+      </c>
+      <c r="G40" t="s">
+        <v>73</v>
+      </c>
+      <c r="H40" t="s">
+        <v>74</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>2</v>
+      </c>
+      <c r="O40" t="s">
+        <v>112</v>
+      </c>
+      <c r="P40" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q40">
+        <v>4.4</v>
+      </c>
+      <c r="R40">
+        <v>2.15</v>
+      </c>
+      <c r="S40">
+        <v>2.4</v>
+      </c>
+      <c r="T40">
+        <v>1.41</v>
+      </c>
+      <c r="U40">
+        <v>2.65</v>
+      </c>
+      <c r="V40">
+        <v>2.95</v>
+      </c>
+      <c r="W40">
+        <v>1.34</v>
+      </c>
+      <c r="X40">
+        <v>7</v>
+      </c>
+      <c r="Y40">
+        <v>1.06</v>
+      </c>
+      <c r="Z40">
+        <v>4.6</v>
+      </c>
+      <c r="AA40">
+        <v>3.55</v>
+      </c>
+      <c r="AB40">
+        <v>1.75</v>
+      </c>
+      <c r="AC40">
+        <v>1.03</v>
+      </c>
+      <c r="AD40">
+        <v>10.5</v>
+      </c>
+      <c r="AE40">
+        <v>1.32</v>
+      </c>
+      <c r="AF40">
+        <v>3.25</v>
+      </c>
+      <c r="AG40">
+        <v>1.91</v>
+      </c>
+      <c r="AH40">
+        <v>1.73</v>
+      </c>
+      <c r="AI40">
+        <v>1.93</v>
+      </c>
+      <c r="AJ40">
+        <v>1.77</v>
+      </c>
+      <c r="AK40">
+        <v>1.98</v>
+      </c>
+      <c r="AL40">
+        <v>1.27</v>
+      </c>
+      <c r="AM40">
+        <v>1.22</v>
+      </c>
+      <c r="AN40">
+        <v>1.33</v>
+      </c>
+      <c r="AO40">
+        <v>2.17</v>
+      </c>
+      <c r="AP40">
+        <v>1.29</v>
+      </c>
+      <c r="AQ40">
+        <v>2</v>
+      </c>
+      <c r="AR40">
+        <v>1.37</v>
+      </c>
+      <c r="AS40">
+        <v>1.68</v>
+      </c>
+      <c r="AT40">
+        <v>3.05</v>
+      </c>
+      <c r="AU40">
+        <v>5</v>
+      </c>
+      <c r="AV40">
+        <v>8</v>
+      </c>
+      <c r="AW40">
+        <v>2</v>
+      </c>
+      <c r="AX40">
+        <v>11</v>
+      </c>
+      <c r="AY40">
+        <v>7</v>
+      </c>
+      <c r="AZ40">
+        <v>19</v>
+      </c>
+      <c r="BA40">
+        <v>3</v>
+      </c>
+      <c r="BB40">
+        <v>9</v>
+      </c>
+      <c r="BC40">
+        <v>12</v>
+      </c>
+      <c r="BD40">
+        <v>2.65</v>
+      </c>
+      <c r="BE40">
+        <v>6.5</v>
+      </c>
+      <c r="BF40">
+        <v>1.57</v>
+      </c>
+      <c r="BG40">
+        <v>1.43</v>
+      </c>
+      <c r="BH40">
+        <v>2.55</v>
+      </c>
+      <c r="BI40">
+        <v>1.73</v>
+      </c>
+      <c r="BJ40">
+        <v>1.94</v>
+      </c>
+      <c r="BK40">
+        <v>2.18</v>
+      </c>
+      <c r="BL40">
+        <v>1.58</v>
+      </c>
+      <c r="BM40">
+        <v>2.85</v>
+      </c>
+      <c r="BN40">
+        <v>1.35</v>
+      </c>
+      <c r="BO40">
+        <v>3.8</v>
+      </c>
+      <c r="BP40">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="138">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>['8']</t>
+  </si>
+  <si>
+    <t>['25']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -786,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP40"/>
+  <dimension ref="A1:BP41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1042,7 +1045,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1248,7 +1251,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1329,7 +1332,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1535,7 +1538,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ4">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1660,7 +1663,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1866,7 +1869,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2072,7 +2075,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2278,7 +2281,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2356,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ8">
         <v>1.33</v>
@@ -2484,7 +2487,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2690,7 +2693,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2896,7 +2899,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -2974,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AQ11">
         <v>2.71</v>
@@ -3308,7 +3311,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3801,7 +3804,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -4132,7 +4135,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4338,7 +4341,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4625,7 +4628,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -4831,7 +4834,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ20">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR20">
         <v>1.3</v>
@@ -5162,7 +5165,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5368,7 +5371,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5652,7 +5655,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ24">
         <v>1.29</v>
@@ -5986,7 +5989,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6067,7 +6070,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR26">
         <v>1.14</v>
@@ -6398,7 +6401,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6476,7 +6479,7 @@
         <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AQ28">
         <v>2</v>
@@ -6604,7 +6607,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6810,7 +6813,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7222,7 +7225,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7634,7 +7637,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7715,7 +7718,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ34">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR34">
         <v>1.34</v>
@@ -7840,7 +7843,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -7918,7 +7921,7 @@
         <v>2.6</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ35">
         <v>2.71</v>
@@ -8046,7 +8049,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8458,7 +8461,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8870,7 +8873,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9027,6 +9030,212 @@
       </c>
       <c r="BP40">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>7793130</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45717.85416666666</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" t="s">
+        <v>76</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
+        <v>113</v>
+      </c>
+      <c r="P41" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q41">
+        <v>2.32</v>
+      </c>
+      <c r="R41">
+        <v>2.12</v>
+      </c>
+      <c r="S41">
+        <v>5</v>
+      </c>
+      <c r="T41">
+        <v>1.44</v>
+      </c>
+      <c r="U41">
+        <v>2.6</v>
+      </c>
+      <c r="V41">
+        <v>3.09</v>
+      </c>
+      <c r="W41">
+        <v>1.34</v>
+      </c>
+      <c r="X41">
+        <v>7.3</v>
+      </c>
+      <c r="Y41">
+        <v>1.04</v>
+      </c>
+      <c r="Z41">
+        <v>1.83</v>
+      </c>
+      <c r="AA41">
+        <v>3.47</v>
+      </c>
+      <c r="AB41">
+        <v>4.2</v>
+      </c>
+      <c r="AC41">
+        <v>1.05</v>
+      </c>
+      <c r="AD41">
+        <v>8</v>
+      </c>
+      <c r="AE41">
+        <v>1.35</v>
+      </c>
+      <c r="AF41">
+        <v>3.05</v>
+      </c>
+      <c r="AG41">
+        <v>2.05</v>
+      </c>
+      <c r="AH41">
+        <v>1.65</v>
+      </c>
+      <c r="AI41">
+        <v>1.93</v>
+      </c>
+      <c r="AJ41">
+        <v>1.78</v>
+      </c>
+      <c r="AK41">
+        <v>1.18</v>
+      </c>
+      <c r="AL41">
+        <v>1.27</v>
+      </c>
+      <c r="AM41">
+        <v>1.92</v>
+      </c>
+      <c r="AN41">
+        <v>0.17</v>
+      </c>
+      <c r="AO41">
+        <v>1</v>
+      </c>
+      <c r="AP41">
+        <v>0.57</v>
+      </c>
+      <c r="AQ41">
+        <v>0.86</v>
+      </c>
+      <c r="AR41">
+        <v>1.17</v>
+      </c>
+      <c r="AS41">
+        <v>1.4</v>
+      </c>
+      <c r="AT41">
+        <v>2.57</v>
+      </c>
+      <c r="AU41">
+        <v>8</v>
+      </c>
+      <c r="AV41">
+        <v>4</v>
+      </c>
+      <c r="AW41">
+        <v>11</v>
+      </c>
+      <c r="AX41">
+        <v>3</v>
+      </c>
+      <c r="AY41">
+        <v>19</v>
+      </c>
+      <c r="AZ41">
+        <v>7</v>
+      </c>
+      <c r="BA41">
+        <v>4</v>
+      </c>
+      <c r="BB41">
+        <v>2</v>
+      </c>
+      <c r="BC41">
+        <v>6</v>
+      </c>
+      <c r="BD41">
+        <v>1.57</v>
+      </c>
+      <c r="BE41">
+        <v>6.4</v>
+      </c>
+      <c r="BF41">
+        <v>2.65</v>
+      </c>
+      <c r="BG41">
+        <v>1.44</v>
+      </c>
+      <c r="BH41">
+        <v>2.48</v>
+      </c>
+      <c r="BI41">
+        <v>1.76</v>
+      </c>
+      <c r="BJ41">
+        <v>1.91</v>
+      </c>
+      <c r="BK41">
+        <v>2.23</v>
+      </c>
+      <c r="BL41">
+        <v>1.55</v>
+      </c>
+      <c r="BM41">
+        <v>2.9</v>
+      </c>
+      <c r="BN41">
+        <v>1.34</v>
+      </c>
+      <c r="BO41">
+        <v>3.9</v>
+      </c>
+      <c r="BP41">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="140">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -358,6 +358,9 @@
     <t>['25']</t>
   </si>
   <si>
+    <t>['21']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -428,6 +431,9 @@
   </si>
   <si>
     <t>['83']</t>
+  </si>
+  <si>
+    <t>['82']</t>
   </si>
 </sst>
 </file>
@@ -789,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP41"/>
+  <dimension ref="A1:BP42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1045,7 +1051,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1123,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ2">
         <v>1.29</v>
@@ -1251,7 +1257,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1535,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4">
         <v>0.57</v>
@@ -1663,7 +1669,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1869,7 +1875,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2075,7 +2081,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2281,7 +2287,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2362,7 +2368,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -2487,7 +2493,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2568,7 +2574,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2693,7 +2699,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2899,7 +2905,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3311,7 +3317,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3595,7 +3601,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ14">
         <v>0.43</v>
@@ -4135,7 +4141,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4341,7 +4347,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4419,7 +4425,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ18">
         <v>2</v>
@@ -5037,7 +5043,7 @@
         <v>1.67</v>
       </c>
       <c r="AP21">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21">
         <v>1.33</v>
@@ -5165,7 +5171,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5371,7 +5377,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5864,7 +5870,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ25">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -5989,7 +5995,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6067,7 +6073,7 @@
         <v>1.25</v>
       </c>
       <c r="AP26">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ26">
         <v>0.86</v>
@@ -6401,7 +6407,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6607,7 +6613,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6813,7 +6819,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6894,7 +6900,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR30">
         <v>1.83</v>
@@ -7225,7 +7231,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7512,7 +7518,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ33">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR33">
         <v>1.83</v>
@@ -7637,7 +7643,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7843,7 +7849,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8049,7 +8055,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8333,7 +8339,7 @@
         <v>1.4</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ37">
         <v>1.29</v>
@@ -8461,7 +8467,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8873,7 +8879,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9236,6 +9242,212 @@
       </c>
       <c r="BP41">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7793132</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45718.375</v>
+      </c>
+      <c r="F42">
+        <v>7</v>
+      </c>
+      <c r="G42" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42" t="s">
+        <v>70</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
+      </c>
+      <c r="O42" t="s">
+        <v>114</v>
+      </c>
+      <c r="P42" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q42">
+        <v>3.25</v>
+      </c>
+      <c r="R42">
+        <v>2</v>
+      </c>
+      <c r="S42">
+        <v>3.6</v>
+      </c>
+      <c r="T42">
+        <v>1.51</v>
+      </c>
+      <c r="U42">
+        <v>2.4</v>
+      </c>
+      <c r="V42">
+        <v>3.2</v>
+      </c>
+      <c r="W42">
+        <v>1.28</v>
+      </c>
+      <c r="X42">
+        <v>7.5</v>
+      </c>
+      <c r="Y42">
+        <v>1.05</v>
+      </c>
+      <c r="Z42">
+        <v>2.5</v>
+      </c>
+      <c r="AA42">
+        <v>2.9</v>
+      </c>
+      <c r="AB42">
+        <v>2.9</v>
+      </c>
+      <c r="AC42">
+        <v>1.08</v>
+      </c>
+      <c r="AD42">
+        <v>6.5</v>
+      </c>
+      <c r="AE42">
+        <v>1.41</v>
+      </c>
+      <c r="AF42">
+        <v>2.75</v>
+      </c>
+      <c r="AG42">
+        <v>2.25</v>
+      </c>
+      <c r="AH42">
+        <v>1.57</v>
+      </c>
+      <c r="AI42">
+        <v>1.91</v>
+      </c>
+      <c r="AJ42">
+        <v>1.8</v>
+      </c>
+      <c r="AK42">
+        <v>1.37</v>
+      </c>
+      <c r="AL42">
+        <v>1.33</v>
+      </c>
+      <c r="AM42">
+        <v>1.5</v>
+      </c>
+      <c r="AN42">
+        <v>1.17</v>
+      </c>
+      <c r="AO42">
+        <v>1.33</v>
+      </c>
+      <c r="AP42">
+        <v>1.14</v>
+      </c>
+      <c r="AQ42">
+        <v>1.29</v>
+      </c>
+      <c r="AR42">
+        <v>1.17</v>
+      </c>
+      <c r="AS42">
+        <v>1.52</v>
+      </c>
+      <c r="AT42">
+        <v>2.69</v>
+      </c>
+      <c r="AU42">
+        <v>3</v>
+      </c>
+      <c r="AV42">
+        <v>4</v>
+      </c>
+      <c r="AW42">
+        <v>4</v>
+      </c>
+      <c r="AX42">
+        <v>2</v>
+      </c>
+      <c r="AY42">
+        <v>7</v>
+      </c>
+      <c r="AZ42">
+        <v>6</v>
+      </c>
+      <c r="BA42">
+        <v>3</v>
+      </c>
+      <c r="BB42">
+        <v>1</v>
+      </c>
+      <c r="BC42">
+        <v>4</v>
+      </c>
+      <c r="BD42">
+        <v>1.9</v>
+      </c>
+      <c r="BE42">
+        <v>6.25</v>
+      </c>
+      <c r="BF42">
+        <v>2.12</v>
+      </c>
+      <c r="BG42">
+        <v>1.48</v>
+      </c>
+      <c r="BH42">
+        <v>2.38</v>
+      </c>
+      <c r="BI42">
+        <v>1.81</v>
+      </c>
+      <c r="BJ42">
+        <v>1.85</v>
+      </c>
+      <c r="BK42">
+        <v>2.3</v>
+      </c>
+      <c r="BL42">
+        <v>1.52</v>
+      </c>
+      <c r="BM42">
+        <v>3.05</v>
+      </c>
+      <c r="BN42">
+        <v>1.3</v>
+      </c>
+      <c r="BO42">
+        <v>4</v>
+      </c>
+      <c r="BP42">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="141">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t>['82']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
   </si>
 </sst>
 </file>
@@ -795,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP42"/>
+  <dimension ref="A1:BP43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1956,7 +1959,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2159,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ7">
         <v>2.71</v>
@@ -2780,7 +2783,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -3189,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ12">
         <v>1.29</v>
@@ -3807,7 +3810,7 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ15">
         <v>0.57</v>
@@ -4428,7 +4431,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR18">
         <v>1.16</v>
@@ -5046,7 +5049,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ21">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5455,7 +5458,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ23">
         <v>2.71</v>
@@ -6488,7 +6491,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR28">
         <v>1.14</v>
@@ -6691,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ29">
         <v>1.14</v>
@@ -7309,7 +7312,7 @@
         <v>0.8</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ32">
         <v>1.14</v>
@@ -8136,7 +8139,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR36">
         <v>1.8</v>
@@ -9447,6 +9450,212 @@
         <v>4</v>
       </c>
       <c r="BP42">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:68">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7793128</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45718.8125</v>
+      </c>
+      <c r="F43">
+        <v>7</v>
+      </c>
+      <c r="G43" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" t="s">
+        <v>79</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43" t="s">
+        <v>84</v>
+      </c>
+      <c r="P43" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q43">
+        <v>2.4</v>
+      </c>
+      <c r="R43">
+        <v>2.05</v>
+      </c>
+      <c r="S43">
+        <v>5.5</v>
+      </c>
+      <c r="T43">
+        <v>1.48</v>
+      </c>
+      <c r="U43">
+        <v>2.5</v>
+      </c>
+      <c r="V43">
+        <v>3.2</v>
+      </c>
+      <c r="W43">
+        <v>1.31</v>
+      </c>
+      <c r="X43">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y43">
+        <v>1.02</v>
+      </c>
+      <c r="Z43">
+        <v>1.72</v>
+      </c>
+      <c r="AA43">
+        <v>3.47</v>
+      </c>
+      <c r="AB43">
+        <v>5</v>
+      </c>
+      <c r="AC43">
+        <v>1.02</v>
+      </c>
+      <c r="AD43">
+        <v>7.7</v>
+      </c>
+      <c r="AE43">
+        <v>1.4</v>
+      </c>
+      <c r="AF43">
+        <v>2.8</v>
+      </c>
+      <c r="AG43">
+        <v>2.15</v>
+      </c>
+      <c r="AH43">
+        <v>1.57</v>
+      </c>
+      <c r="AI43">
+        <v>2.1</v>
+      </c>
+      <c r="AJ43">
+        <v>1.67</v>
+      </c>
+      <c r="AK43">
+        <v>1.17</v>
+      </c>
+      <c r="AL43">
+        <v>1.27</v>
+      </c>
+      <c r="AM43">
+        <v>1.98</v>
+      </c>
+      <c r="AN43">
+        <v>1.33</v>
+      </c>
+      <c r="AO43">
+        <v>2</v>
+      </c>
+      <c r="AP43">
+        <v>1.14</v>
+      </c>
+      <c r="AQ43">
+        <v>2.14</v>
+      </c>
+      <c r="AR43">
+        <v>1.5</v>
+      </c>
+      <c r="AS43">
+        <v>1.12</v>
+      </c>
+      <c r="AT43">
+        <v>2.62</v>
+      </c>
+      <c r="AU43">
+        <v>4</v>
+      </c>
+      <c r="AV43">
+        <v>4</v>
+      </c>
+      <c r="AW43">
+        <v>8</v>
+      </c>
+      <c r="AX43">
+        <v>5</v>
+      </c>
+      <c r="AY43">
+        <v>12</v>
+      </c>
+      <c r="AZ43">
+        <v>9</v>
+      </c>
+      <c r="BA43">
+        <v>5</v>
+      </c>
+      <c r="BB43">
+        <v>3</v>
+      </c>
+      <c r="BC43">
+        <v>8</v>
+      </c>
+      <c r="BD43">
+        <v>1.54</v>
+      </c>
+      <c r="BE43">
+        <v>6.4</v>
+      </c>
+      <c r="BF43">
+        <v>2.8</v>
+      </c>
+      <c r="BG43">
+        <v>1.49</v>
+      </c>
+      <c r="BH43">
+        <v>2.38</v>
+      </c>
+      <c r="BI43">
+        <v>1.82</v>
+      </c>
+      <c r="BJ43">
+        <v>1.84</v>
+      </c>
+      <c r="BK43">
+        <v>2.32</v>
+      </c>
+      <c r="BL43">
+        <v>1.52</v>
+      </c>
+      <c r="BM43">
+        <v>3.05</v>
+      </c>
+      <c r="BN43">
+        <v>1.3</v>
+      </c>
+      <c r="BO43">
+        <v>4.1</v>
+      </c>
+      <c r="BP43">
         <v>1.18</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="143">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -361,6 +361,9 @@
     <t>['21']</t>
   </si>
   <si>
+    <t>['9', '90+1']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -437,6 +440,9 @@
   </si>
   <si>
     <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['43', '50', '55']</t>
   </si>
 </sst>
 </file>
@@ -798,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP43"/>
+  <dimension ref="A1:BP44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1054,7 +1060,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1260,7 +1266,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1341,7 +1347,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ3">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1672,7 +1678,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1753,7 +1759,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ5">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1878,7 +1884,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2084,7 +2090,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2290,7 +2296,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2368,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ8">
         <v>1.29</v>
@@ -2496,7 +2502,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2574,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9">
         <v>1.14</v>
@@ -2702,7 +2708,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2908,7 +2914,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3320,7 +3326,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -4144,7 +4150,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4225,7 +4231,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ17">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4350,7 +4356,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4637,7 +4643,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -4840,7 +4846,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ20">
         <v>0.57</v>
@@ -5174,7 +5180,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5380,7 +5386,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5664,7 +5670,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ24">
         <v>1.29</v>
@@ -5998,7 +6004,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6079,7 +6085,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ26">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR26">
         <v>1.14</v>
@@ -6410,7 +6416,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6616,7 +6622,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6697,7 +6703,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ29">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -6822,7 +6828,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7234,7 +7240,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7315,7 +7321,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ32">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR32">
         <v>1.08</v>
@@ -7646,7 +7652,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7852,7 +7858,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -7930,7 +7936,7 @@
         <v>2.6</v>
       </c>
       <c r="AP35">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ35">
         <v>2.71</v>
@@ -8058,7 +8064,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8470,7 +8476,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8548,7 +8554,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ38">
         <v>1.29</v>
@@ -8882,7 +8888,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9169,7 +9175,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ41">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR41">
         <v>1.17</v>
@@ -9294,7 +9300,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9500,7 +9506,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9657,6 +9663,212 @@
       </c>
       <c r="BP43">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:68">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>7793138</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45724.76041666666</v>
+      </c>
+      <c r="F44">
+        <v>8</v>
+      </c>
+      <c r="G44" t="s">
+        <v>76</v>
+      </c>
+      <c r="H44" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>2</v>
+      </c>
+      <c r="L44">
+        <v>2</v>
+      </c>
+      <c r="M44">
+        <v>3</v>
+      </c>
+      <c r="N44">
+        <v>5</v>
+      </c>
+      <c r="O44" t="s">
+        <v>115</v>
+      </c>
+      <c r="P44" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q44">
+        <v>3.5</v>
+      </c>
+      <c r="R44">
+        <v>2</v>
+      </c>
+      <c r="S44">
+        <v>3.4</v>
+      </c>
+      <c r="T44">
+        <v>1.5</v>
+      </c>
+      <c r="U44">
+        <v>2.5</v>
+      </c>
+      <c r="V44">
+        <v>3.4</v>
+      </c>
+      <c r="W44">
+        <v>1.3</v>
+      </c>
+      <c r="X44">
+        <v>10</v>
+      </c>
+      <c r="Y44">
+        <v>1.06</v>
+      </c>
+      <c r="Z44">
+        <v>2.79</v>
+      </c>
+      <c r="AA44">
+        <v>3.15</v>
+      </c>
+      <c r="AB44">
+        <v>2.54</v>
+      </c>
+      <c r="AC44">
+        <v>1.02</v>
+      </c>
+      <c r="AD44">
+        <v>8.1</v>
+      </c>
+      <c r="AE44">
+        <v>1.35</v>
+      </c>
+      <c r="AF44">
+        <v>3.04</v>
+      </c>
+      <c r="AG44">
+        <v>2.05</v>
+      </c>
+      <c r="AH44">
+        <v>1.61</v>
+      </c>
+      <c r="AI44">
+        <v>1.91</v>
+      </c>
+      <c r="AJ44">
+        <v>1.8</v>
+      </c>
+      <c r="AK44">
+        <v>1.49</v>
+      </c>
+      <c r="AL44">
+        <v>1.32</v>
+      </c>
+      <c r="AM44">
+        <v>1.43</v>
+      </c>
+      <c r="AN44">
+        <v>0.86</v>
+      </c>
+      <c r="AO44">
+        <v>1.14</v>
+      </c>
+      <c r="AP44">
+        <v>0.75</v>
+      </c>
+      <c r="AQ44">
+        <v>1.38</v>
+      </c>
+      <c r="AR44">
+        <v>1.37</v>
+      </c>
+      <c r="AS44">
+        <v>1.31</v>
+      </c>
+      <c r="AT44">
+        <v>2.68</v>
+      </c>
+      <c r="AU44">
+        <v>4</v>
+      </c>
+      <c r="AV44">
+        <v>10</v>
+      </c>
+      <c r="AW44">
+        <v>5</v>
+      </c>
+      <c r="AX44">
+        <v>5</v>
+      </c>
+      <c r="AY44">
+        <v>9</v>
+      </c>
+      <c r="AZ44">
+        <v>15</v>
+      </c>
+      <c r="BA44">
+        <v>0</v>
+      </c>
+      <c r="BB44">
+        <v>9</v>
+      </c>
+      <c r="BC44">
+        <v>9</v>
+      </c>
+      <c r="BD44">
+        <v>2.13</v>
+      </c>
+      <c r="BE44">
+        <v>5.95</v>
+      </c>
+      <c r="BF44">
+        <v>2.08</v>
+      </c>
+      <c r="BG44">
+        <v>1.41</v>
+      </c>
+      <c r="BH44">
+        <v>2.52</v>
+      </c>
+      <c r="BI44">
+        <v>1.8</v>
+      </c>
+      <c r="BJ44">
+        <v>1.91</v>
+      </c>
+      <c r="BK44">
+        <v>2.26</v>
+      </c>
+      <c r="BL44">
+        <v>1.51</v>
+      </c>
+      <c r="BM44">
+        <v>3.08</v>
+      </c>
+      <c r="BN44">
+        <v>1.28</v>
+      </c>
+      <c r="BO44">
+        <v>3.9</v>
+      </c>
+      <c r="BP44">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="145">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -364,6 +364,9 @@
     <t>['9', '90+1']</t>
   </si>
   <si>
+    <t>['18']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -443,6 +446,9 @@
   </si>
   <si>
     <t>['43', '50', '55']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
   </si>
 </sst>
 </file>
@@ -804,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP44"/>
+  <dimension ref="A1:BP45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1060,7 +1066,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1138,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ2">
         <v>1.29</v>
@@ -1266,7 +1272,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1678,7 +1684,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1884,7 +1890,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2090,7 +2096,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2171,7 +2177,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ7">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2296,7 +2302,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2377,7 +2383,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ8">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -2502,7 +2508,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2708,7 +2714,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2914,7 +2920,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -2995,7 +3001,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ11">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3326,7 +3332,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3610,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14">
         <v>0.43</v>
@@ -4150,7 +4156,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4228,7 +4234,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17">
         <v>1.38</v>
@@ -4356,7 +4362,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -5052,7 +5058,7 @@
         <v>1.67</v>
       </c>
       <c r="AP21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ21">
         <v>1.14</v>
@@ -5180,7 +5186,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5386,7 +5392,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5467,7 +5473,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ23">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AR23">
         <v>1.04</v>
@@ -6004,7 +6010,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6416,7 +6422,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6622,7 +6628,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6828,7 +6834,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6909,7 +6915,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR30">
         <v>1.83</v>
@@ -7112,7 +7118,7 @@
         <v>1.25</v>
       </c>
       <c r="AP31">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ31">
         <v>1.29</v>
@@ -7240,7 +7246,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7652,7 +7658,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7858,7 +7864,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -7939,7 +7945,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ35">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AR35">
         <v>1.46</v>
@@ -8064,7 +8070,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8348,7 +8354,7 @@
         <v>1.4</v>
       </c>
       <c r="AP37">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
         <v>1.29</v>
@@ -8476,7 +8482,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8760,7 +8766,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ39">
         <v>0.43</v>
@@ -8888,7 +8894,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9300,7 +9306,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9381,7 +9387,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ42">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR42">
         <v>1.17</v>
@@ -9506,7 +9512,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9712,7 +9718,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9869,6 +9875,212 @@
       </c>
       <c r="BP44">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:68">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>7793136</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45724.85416666666</v>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="G45" t="s">
+        <v>70</v>
+      </c>
+      <c r="H45" t="s">
+        <v>81</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>2</v>
+      </c>
+      <c r="O45" t="s">
+        <v>116</v>
+      </c>
+      <c r="P45" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q45">
+        <v>4.6</v>
+      </c>
+      <c r="R45">
+        <v>2.18</v>
+      </c>
+      <c r="S45">
+        <v>2.51</v>
+      </c>
+      <c r="T45">
+        <v>1.41</v>
+      </c>
+      <c r="U45">
+        <v>2.88</v>
+      </c>
+      <c r="V45">
+        <v>3.07</v>
+      </c>
+      <c r="W45">
+        <v>1.37</v>
+      </c>
+      <c r="X45">
+        <v>7.8</v>
+      </c>
+      <c r="Y45">
+        <v>1.02</v>
+      </c>
+      <c r="Z45">
+        <v>3.98</v>
+      </c>
+      <c r="AA45">
+        <v>3.41</v>
+      </c>
+      <c r="AB45">
+        <v>1.9</v>
+      </c>
+      <c r="AC45">
+        <v>1.04</v>
+      </c>
+      <c r="AD45">
+        <v>8.5</v>
+      </c>
+      <c r="AE45">
+        <v>1.33</v>
+      </c>
+      <c r="AF45">
+        <v>3</v>
+      </c>
+      <c r="AG45">
+        <v>1.98</v>
+      </c>
+      <c r="AH45">
+        <v>1.77</v>
+      </c>
+      <c r="AI45">
+        <v>1.83</v>
+      </c>
+      <c r="AJ45">
+        <v>1.93</v>
+      </c>
+      <c r="AK45">
+        <v>1.85</v>
+      </c>
+      <c r="AL45">
+        <v>1.26</v>
+      </c>
+      <c r="AM45">
+        <v>1.21</v>
+      </c>
+      <c r="AN45">
+        <v>1.29</v>
+      </c>
+      <c r="AO45">
+        <v>2.71</v>
+      </c>
+      <c r="AP45">
+        <v>1.25</v>
+      </c>
+      <c r="AQ45">
+        <v>2.5</v>
+      </c>
+      <c r="AR45">
+        <v>1.43</v>
+      </c>
+      <c r="AS45">
+        <v>1.56</v>
+      </c>
+      <c r="AT45">
+        <v>2.99</v>
+      </c>
+      <c r="AU45">
+        <v>2</v>
+      </c>
+      <c r="AV45">
+        <v>5</v>
+      </c>
+      <c r="AW45">
+        <v>4</v>
+      </c>
+      <c r="AX45">
+        <v>8</v>
+      </c>
+      <c r="AY45">
+        <v>6</v>
+      </c>
+      <c r="AZ45">
+        <v>13</v>
+      </c>
+      <c r="BA45">
+        <v>3</v>
+      </c>
+      <c r="BB45">
+        <v>3</v>
+      </c>
+      <c r="BC45">
+        <v>6</v>
+      </c>
+      <c r="BD45">
+        <v>2.2</v>
+      </c>
+      <c r="BE45">
+        <v>7.5</v>
+      </c>
+      <c r="BF45">
+        <v>1.91</v>
+      </c>
+      <c r="BG45">
+        <v>1.42</v>
+      </c>
+      <c r="BH45">
+        <v>2.65</v>
+      </c>
+      <c r="BI45">
+        <v>1.7</v>
+      </c>
+      <c r="BJ45">
+        <v>2.05</v>
+      </c>
+      <c r="BK45">
+        <v>2.2</v>
+      </c>
+      <c r="BL45">
+        <v>1.63</v>
+      </c>
+      <c r="BM45">
+        <v>2.83</v>
+      </c>
+      <c r="BN45">
+        <v>1.37</v>
+      </c>
+      <c r="BO45">
+        <v>3.85</v>
+      </c>
+      <c r="BP45">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="148">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -367,6 +367,9 @@
     <t>['18']</t>
   </si>
   <si>
+    <t>['11', '25']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -449,6 +452,12 @@
   </si>
   <si>
     <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['90+11']</t>
+  </si>
+  <si>
+    <t>['42']</t>
   </si>
 </sst>
 </file>
@@ -810,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP45"/>
+  <dimension ref="A1:BP47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1066,7 +1075,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1272,7 +1281,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1556,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>0.57</v>
@@ -1684,7 +1693,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1762,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ5">
         <v>1.38</v>
@@ -1890,7 +1899,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1968,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ6">
         <v>2.14</v>
@@ -2096,7 +2105,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2174,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ7">
         <v>2.5</v>
@@ -2302,7 +2311,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2508,7 +2517,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2589,7 +2598,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2714,7 +2723,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2795,7 +2804,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ10">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -2920,7 +2929,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3207,7 +3216,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ12">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3332,7 +3341,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3413,7 +3422,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ13">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -3822,7 +3831,7 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15">
         <v>0.57</v>
@@ -4028,7 +4037,7 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ16">
         <v>1.29</v>
@@ -4156,7 +4165,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4362,7 +4371,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4440,7 +4449,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
         <v>2.14</v>
@@ -4646,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ19">
         <v>0.75</v>
@@ -5061,7 +5070,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ21">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5186,7 +5195,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5267,7 +5276,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5392,7 +5401,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5679,7 +5688,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ24">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -5885,7 +5894,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ25">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -6010,7 +6019,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6088,7 +6097,7 @@
         <v>1.25</v>
       </c>
       <c r="AP26">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>0.75</v>
@@ -6294,7 +6303,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ27">
         <v>0.43</v>
@@ -6422,7 +6431,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6628,7 +6637,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6706,7 +6715,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ29">
         <v>1.38</v>
@@ -6834,7 +6843,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6912,7 +6921,7 @@
         <v>1.75</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ30">
         <v>1.25</v>
@@ -7246,7 +7255,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7533,7 +7542,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ33">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.83</v>
@@ -7658,7 +7667,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7864,7 +7873,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8070,7 +8079,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8148,10 +8157,10 @@
         <v>1.6</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ36">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR36">
         <v>1.8</v>
@@ -8357,7 +8366,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR37">
         <v>1.52</v>
@@ -8482,7 +8491,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8894,7 +8903,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -8972,10 +8981,10 @@
         <v>2.17</v>
       </c>
       <c r="AP40">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -9306,7 +9315,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9384,7 +9393,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
         <v>1.25</v>
@@ -9512,7 +9521,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9590,7 +9599,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ43">
         <v>2.14</v>
@@ -9718,7 +9727,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9924,7 +9933,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10081,6 +10090,418 @@
       </c>
       <c r="BP45">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:68">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>7793134</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="2">
+        <v>45725.76041666666</v>
+      </c>
+      <c r="F46">
+        <v>8</v>
+      </c>
+      <c r="G46" t="s">
+        <v>73</v>
+      </c>
+      <c r="H46" t="s">
+        <v>75</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46" t="s">
+        <v>84</v>
+      </c>
+      <c r="P46" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q46">
+        <v>4</v>
+      </c>
+      <c r="R46">
+        <v>1.95</v>
+      </c>
+      <c r="S46">
+        <v>3.25</v>
+      </c>
+      <c r="T46">
+        <v>1.53</v>
+      </c>
+      <c r="U46">
+        <v>2.38</v>
+      </c>
+      <c r="V46">
+        <v>3.75</v>
+      </c>
+      <c r="W46">
+        <v>1.25</v>
+      </c>
+      <c r="X46">
+        <v>11</v>
+      </c>
+      <c r="Y46">
+        <v>1.05</v>
+      </c>
+      <c r="Z46">
+        <v>4.3</v>
+      </c>
+      <c r="AA46">
+        <v>3.01</v>
+      </c>
+      <c r="AB46">
+        <v>1.98</v>
+      </c>
+      <c r="AC46">
+        <v>1.02</v>
+      </c>
+      <c r="AD46">
+        <v>7.8</v>
+      </c>
+      <c r="AE46">
+        <v>1.4</v>
+      </c>
+      <c r="AF46">
+        <v>2.56</v>
+      </c>
+      <c r="AG46">
+        <v>2.25</v>
+      </c>
+      <c r="AH46">
+        <v>1.53</v>
+      </c>
+      <c r="AI46">
+        <v>2</v>
+      </c>
+      <c r="AJ46">
+        <v>1.73</v>
+      </c>
+      <c r="AK46">
+        <v>1.55</v>
+      </c>
+      <c r="AL46">
+        <v>1.31</v>
+      </c>
+      <c r="AM46">
+        <v>1.31</v>
+      </c>
+      <c r="AN46">
+        <v>1.29</v>
+      </c>
+      <c r="AO46">
+        <v>1.14</v>
+      </c>
+      <c r="AP46">
+        <v>1.13</v>
+      </c>
+      <c r="AQ46">
+        <v>1.38</v>
+      </c>
+      <c r="AR46">
+        <v>1.32</v>
+      </c>
+      <c r="AS46">
+        <v>1.48</v>
+      </c>
+      <c r="AT46">
+        <v>2.8</v>
+      </c>
+      <c r="AU46">
+        <v>5</v>
+      </c>
+      <c r="AV46">
+        <v>5</v>
+      </c>
+      <c r="AW46">
+        <v>6</v>
+      </c>
+      <c r="AX46">
+        <v>12</v>
+      </c>
+      <c r="AY46">
+        <v>11</v>
+      </c>
+      <c r="AZ46">
+        <v>17</v>
+      </c>
+      <c r="BA46">
+        <v>0</v>
+      </c>
+      <c r="BB46">
+        <v>5</v>
+      </c>
+      <c r="BC46">
+        <v>5</v>
+      </c>
+      <c r="BD46">
+        <v>2.4</v>
+      </c>
+      <c r="BE46">
+        <v>7.5</v>
+      </c>
+      <c r="BF46">
+        <v>1.73</v>
+      </c>
+      <c r="BG46">
+        <v>1.39</v>
+      </c>
+      <c r="BH46">
+        <v>2.75</v>
+      </c>
+      <c r="BI46">
+        <v>1.7</v>
+      </c>
+      <c r="BJ46">
+        <v>2.05</v>
+      </c>
+      <c r="BK46">
+        <v>2.12</v>
+      </c>
+      <c r="BL46">
+        <v>1.67</v>
+      </c>
+      <c r="BM46">
+        <v>2.72</v>
+      </c>
+      <c r="BN46">
+        <v>1.4</v>
+      </c>
+      <c r="BO46">
+        <v>3.68</v>
+      </c>
+      <c r="BP46">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:68">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>7793135</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="2">
+        <v>45725.85416666666</v>
+      </c>
+      <c r="F47">
+        <v>8</v>
+      </c>
+      <c r="G47" t="s">
+        <v>74</v>
+      </c>
+      <c r="H47" t="s">
+        <v>72</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>3</v>
+      </c>
+      <c r="L47">
+        <v>2</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>3</v>
+      </c>
+      <c r="O47" t="s">
+        <v>117</v>
+      </c>
+      <c r="P47" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q47">
+        <v>2.06</v>
+      </c>
+      <c r="R47">
+        <v>2.13</v>
+      </c>
+      <c r="S47">
+        <v>6.15</v>
+      </c>
+      <c r="T47">
+        <v>1.42</v>
+      </c>
+      <c r="U47">
+        <v>2.65</v>
+      </c>
+      <c r="V47">
+        <v>2.98</v>
+      </c>
+      <c r="W47">
+        <v>1.34</v>
+      </c>
+      <c r="X47">
+        <v>7.1</v>
+      </c>
+      <c r="Y47">
+        <v>1.04</v>
+      </c>
+      <c r="Z47">
+        <v>1.51</v>
+      </c>
+      <c r="AA47">
+        <v>3.95</v>
+      </c>
+      <c r="AB47">
+        <v>6.4</v>
+      </c>
+      <c r="AC47">
+        <v>1.02</v>
+      </c>
+      <c r="AD47">
+        <v>7.9</v>
+      </c>
+      <c r="AE47">
+        <v>1.31</v>
+      </c>
+      <c r="AF47">
+        <v>2.92</v>
+      </c>
+      <c r="AG47">
+        <v>2.05</v>
+      </c>
+      <c r="AH47">
+        <v>1.61</v>
+      </c>
+      <c r="AI47">
+        <v>2.11</v>
+      </c>
+      <c r="AJ47">
+        <v>1.62</v>
+      </c>
+      <c r="AK47">
+        <v>1.08</v>
+      </c>
+      <c r="AL47">
+        <v>1.21</v>
+      </c>
+      <c r="AM47">
+        <v>2.38</v>
+      </c>
+      <c r="AN47">
+        <v>2</v>
+      </c>
+      <c r="AO47">
+        <v>1.14</v>
+      </c>
+      <c r="AP47">
+        <v>2.13</v>
+      </c>
+      <c r="AQ47">
+        <v>1</v>
+      </c>
+      <c r="AR47">
+        <v>1.75</v>
+      </c>
+      <c r="AS47">
+        <v>1.15</v>
+      </c>
+      <c r="AT47">
+        <v>2.9</v>
+      </c>
+      <c r="AU47">
+        <v>8</v>
+      </c>
+      <c r="AV47">
+        <v>2</v>
+      </c>
+      <c r="AW47">
+        <v>10</v>
+      </c>
+      <c r="AX47">
+        <v>4</v>
+      </c>
+      <c r="AY47">
+        <v>18</v>
+      </c>
+      <c r="AZ47">
+        <v>6</v>
+      </c>
+      <c r="BA47">
+        <v>4</v>
+      </c>
+      <c r="BB47">
+        <v>2</v>
+      </c>
+      <c r="BC47">
+        <v>6</v>
+      </c>
+      <c r="BD47">
+        <v>1.41</v>
+      </c>
+      <c r="BE47">
+        <v>6.75</v>
+      </c>
+      <c r="BF47">
+        <v>3.4</v>
+      </c>
+      <c r="BG47">
+        <v>1.44</v>
+      </c>
+      <c r="BH47">
+        <v>2.5</v>
+      </c>
+      <c r="BI47">
+        <v>1.74</v>
+      </c>
+      <c r="BJ47">
+        <v>1.93</v>
+      </c>
+      <c r="BK47">
+        <v>2.18</v>
+      </c>
+      <c r="BL47">
+        <v>1.58</v>
+      </c>
+      <c r="BM47">
+        <v>2.8</v>
+      </c>
+      <c r="BN47">
+        <v>1.36</v>
+      </c>
+      <c r="BO47">
+        <v>3.7</v>
+      </c>
+      <c r="BP47">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="150">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -370,6 +370,9 @@
     <t>['11', '25']</t>
   </si>
   <si>
+    <t>['51', '80']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -458,6 +461,9 @@
   </si>
   <si>
     <t>['42']</t>
+  </si>
+  <si>
+    <t>['39']</t>
   </si>
 </sst>
 </file>
@@ -819,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP47"/>
+  <dimension ref="A1:BP48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1075,7 +1081,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1281,7 +1287,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1359,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ3">
         <v>0.75</v>
@@ -1568,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1693,7 +1699,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1899,7 +1905,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2105,7 +2111,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2311,7 +2317,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2517,7 +2523,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2723,7 +2729,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2801,7 +2807,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ10">
         <v>1.38</v>
@@ -2929,7 +2935,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3007,7 +3013,7 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ11">
         <v>2.5</v>
@@ -3341,7 +3347,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3628,7 +3634,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ14">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -3834,7 +3840,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ15">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -4165,7 +4171,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4371,7 +4377,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4864,7 +4870,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ20">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR20">
         <v>1.3</v>
@@ -5195,7 +5201,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5273,7 +5279,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ22">
         <v>2.13</v>
@@ -5401,7 +5407,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -6019,7 +6025,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6306,7 +6312,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ27">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR27">
         <v>1.17</v>
@@ -6431,7 +6437,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6509,7 +6515,7 @@
         <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ28">
         <v>2.14</v>
@@ -6637,7 +6643,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6843,7 +6849,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7255,7 +7261,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7539,7 +7545,7 @@
         <v>1.2</v>
       </c>
       <c r="AP33">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -7667,7 +7673,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7748,7 +7754,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ34">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR34">
         <v>1.34</v>
@@ -7873,7 +7879,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8079,7 +8085,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8491,7 +8497,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8778,7 +8784,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ39">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR39">
         <v>1.59</v>
@@ -8903,7 +8909,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9187,7 +9193,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ41">
         <v>0.75</v>
@@ -9315,7 +9321,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9521,7 +9527,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9727,7 +9733,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9933,7 +9939,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10139,7 +10145,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10345,7 +10351,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10502,6 +10508,212 @@
       </c>
       <c r="BP47">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:68">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>7793137</v>
+      </c>
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="2">
+        <v>45726.76041666666</v>
+      </c>
+      <c r="F48">
+        <v>8</v>
+      </c>
+      <c r="G48" t="s">
+        <v>71</v>
+      </c>
+      <c r="H48" t="s">
+        <v>78</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <v>2</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>3</v>
+      </c>
+      <c r="O48" t="s">
+        <v>118</v>
+      </c>
+      <c r="P48" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q48">
+        <v>3.4</v>
+      </c>
+      <c r="R48">
+        <v>1.95</v>
+      </c>
+      <c r="S48">
+        <v>3.4</v>
+      </c>
+      <c r="T48">
+        <v>1.53</v>
+      </c>
+      <c r="U48">
+        <v>2.43</v>
+      </c>
+      <c r="V48">
+        <v>3.56</v>
+      </c>
+      <c r="W48">
+        <v>1.23</v>
+      </c>
+      <c r="X48">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y48">
+        <v>1.02</v>
+      </c>
+      <c r="Z48">
+        <v>3.02</v>
+      </c>
+      <c r="AA48">
+        <v>2.89</v>
+      </c>
+      <c r="AB48">
+        <v>2.55</v>
+      </c>
+      <c r="AC48">
+        <v>1.07</v>
+      </c>
+      <c r="AD48">
+        <v>7</v>
+      </c>
+      <c r="AE48">
+        <v>1.45</v>
+      </c>
+      <c r="AF48">
+        <v>2.55</v>
+      </c>
+      <c r="AG48">
+        <v>2.37</v>
+      </c>
+      <c r="AH48">
+        <v>1.48</v>
+      </c>
+      <c r="AI48">
+        <v>2.05</v>
+      </c>
+      <c r="AJ48">
+        <v>1.73</v>
+      </c>
+      <c r="AK48">
+        <v>1.44</v>
+      </c>
+      <c r="AL48">
+        <v>1.4</v>
+      </c>
+      <c r="AM48">
+        <v>1.36</v>
+      </c>
+      <c r="AN48">
+        <v>0.43</v>
+      </c>
+      <c r="AO48">
+        <v>0.57</v>
+      </c>
+      <c r="AP48">
+        <v>0.75</v>
+      </c>
+      <c r="AQ48">
+        <v>0.5</v>
+      </c>
+      <c r="AR48">
+        <v>1.65</v>
+      </c>
+      <c r="AS48">
+        <v>1.32</v>
+      </c>
+      <c r="AT48">
+        <v>2.97</v>
+      </c>
+      <c r="AU48">
+        <v>6</v>
+      </c>
+      <c r="AV48">
+        <v>5</v>
+      </c>
+      <c r="AW48">
+        <v>5</v>
+      </c>
+      <c r="AX48">
+        <v>8</v>
+      </c>
+      <c r="AY48">
+        <v>11</v>
+      </c>
+      <c r="AZ48">
+        <v>13</v>
+      </c>
+      <c r="BA48">
+        <v>5</v>
+      </c>
+      <c r="BB48">
+        <v>8</v>
+      </c>
+      <c r="BC48">
+        <v>13</v>
+      </c>
+      <c r="BD48">
+        <v>2.1</v>
+      </c>
+      <c r="BE48">
+        <v>6.05</v>
+      </c>
+      <c r="BF48">
+        <v>2.1</v>
+      </c>
+      <c r="BG48">
+        <v>1.31</v>
+      </c>
+      <c r="BH48">
+        <v>2.92</v>
+      </c>
+      <c r="BI48">
+        <v>1.58</v>
+      </c>
+      <c r="BJ48">
+        <v>2.12</v>
+      </c>
+      <c r="BK48">
+        <v>2.01</v>
+      </c>
+      <c r="BL48">
+        <v>1.68</v>
+      </c>
+      <c r="BM48">
+        <v>2.62</v>
+      </c>
+      <c r="BN48">
+        <v>1.38</v>
+      </c>
+      <c r="BO48">
+        <v>3.68</v>
+      </c>
+      <c r="BP48">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="151">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>['51', '80']</t>
+  </si>
+  <si>
+    <t>['78', '85']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -825,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP48"/>
+  <dimension ref="A1:BP49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1081,7 +1084,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1162,7 +1165,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ2">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1287,7 +1290,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1699,7 +1702,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1905,7 +1908,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1986,7 +1989,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ6">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2111,7 +2114,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2317,7 +2320,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2523,7 +2526,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2729,7 +2732,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2935,7 +2938,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3219,7 +3222,7 @@
         <v>1</v>
       </c>
       <c r="AP12">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ12">
         <v>1.13</v>
@@ -3347,7 +3350,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3425,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>2.13</v>
@@ -4046,7 +4049,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ16">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4171,7 +4174,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4377,7 +4380,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4458,7 +4461,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR18">
         <v>1.16</v>
@@ -5201,7 +5204,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5407,7 +5410,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5485,7 +5488,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ23">
         <v>2.5</v>
@@ -5897,7 +5900,7 @@
         <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6025,7 +6028,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6437,7 +6440,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6518,7 +6521,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ28">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR28">
         <v>1.14</v>
@@ -6643,7 +6646,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6849,7 +6852,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7136,7 +7139,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ31">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR31">
         <v>1.72</v>
@@ -7261,7 +7264,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7339,7 +7342,7 @@
         <v>0.8</v>
       </c>
       <c r="AP32">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ32">
         <v>1.38</v>
@@ -7673,7 +7676,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7751,7 +7754,7 @@
         <v>0.2</v>
       </c>
       <c r="AP34">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34">
         <v>0.5</v>
@@ -7879,7 +7882,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8085,7 +8088,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8497,7 +8500,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8578,7 +8581,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ38">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR38">
         <v>1.26</v>
@@ -8909,7 +8912,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9321,7 +9324,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9527,7 +9530,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9608,7 +9611,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ43">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR43">
         <v>1.5</v>
@@ -9733,7 +9736,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9939,7 +9942,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10145,7 +10148,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10351,7 +10354,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10557,7 +10560,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -10714,6 +10717,212 @@
       </c>
       <c r="BP48">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:68">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>7793139</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="2">
+        <v>45726.85416666666</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+      <c r="G49" t="s">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s">
+        <v>79</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>2</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>2</v>
+      </c>
+      <c r="O49" t="s">
+        <v>119</v>
+      </c>
+      <c r="P49" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q49">
+        <v>3.45</v>
+      </c>
+      <c r="R49">
+        <v>1.8</v>
+      </c>
+      <c r="S49">
+        <v>3.68</v>
+      </c>
+      <c r="T49">
+        <v>1.57</v>
+      </c>
+      <c r="U49">
+        <v>2.31</v>
+      </c>
+      <c r="V49">
+        <v>3.65</v>
+      </c>
+      <c r="W49">
+        <v>1.22</v>
+      </c>
+      <c r="X49">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y49">
+        <v>1.01</v>
+      </c>
+      <c r="Z49">
+        <v>2.66</v>
+      </c>
+      <c r="AA49">
+        <v>2.92</v>
+      </c>
+      <c r="AB49">
+        <v>2.84</v>
+      </c>
+      <c r="AC49">
+        <v>1.04</v>
+      </c>
+      <c r="AD49">
+        <v>6.75</v>
+      </c>
+      <c r="AE49">
+        <v>1.5</v>
+      </c>
+      <c r="AF49">
+        <v>2.4</v>
+      </c>
+      <c r="AG49">
+        <v>2.37</v>
+      </c>
+      <c r="AH49">
+        <v>1.48</v>
+      </c>
+      <c r="AI49">
+        <v>2.03</v>
+      </c>
+      <c r="AJ49">
+        <v>1.67</v>
+      </c>
+      <c r="AK49">
+        <v>1.37</v>
+      </c>
+      <c r="AL49">
+        <v>1.36</v>
+      </c>
+      <c r="AM49">
+        <v>1.42</v>
+      </c>
+      <c r="AN49">
+        <v>1.29</v>
+      </c>
+      <c r="AO49">
+        <v>2.14</v>
+      </c>
+      <c r="AP49">
+        <v>1.5</v>
+      </c>
+      <c r="AQ49">
+        <v>1.88</v>
+      </c>
+      <c r="AR49">
+        <v>1.28</v>
+      </c>
+      <c r="AS49">
+        <v>1.1</v>
+      </c>
+      <c r="AT49">
+        <v>2.38</v>
+      </c>
+      <c r="AU49">
+        <v>3</v>
+      </c>
+      <c r="AV49">
+        <v>5</v>
+      </c>
+      <c r="AW49">
+        <v>6</v>
+      </c>
+      <c r="AX49">
+        <v>7</v>
+      </c>
+      <c r="AY49">
+        <v>9</v>
+      </c>
+      <c r="AZ49">
+        <v>12</v>
+      </c>
+      <c r="BA49">
+        <v>2</v>
+      </c>
+      <c r="BB49">
+        <v>3</v>
+      </c>
+      <c r="BC49">
+        <v>5</v>
+      </c>
+      <c r="BD49">
+        <v>1.98</v>
+      </c>
+      <c r="BE49">
+        <v>6.1</v>
+      </c>
+      <c r="BF49">
+        <v>2.02</v>
+      </c>
+      <c r="BG49">
+        <v>1.52</v>
+      </c>
+      <c r="BH49">
+        <v>2.32</v>
+      </c>
+      <c r="BI49">
+        <v>1.88</v>
+      </c>
+      <c r="BJ49">
+        <v>1.78</v>
+      </c>
+      <c r="BK49">
+        <v>2.4</v>
+      </c>
+      <c r="BL49">
+        <v>1.48</v>
+      </c>
+      <c r="BM49">
+        <v>3.15</v>
+      </c>
+      <c r="BN49">
+        <v>1.29</v>
+      </c>
+      <c r="BO49">
+        <v>4.3</v>
+      </c>
+      <c r="BP49">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="151">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -828,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP49"/>
+  <dimension ref="A1:BP51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1371,7 +1371,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ3">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ4">
         <v>0.5</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
         <v>1.38</v>
@@ -1989,7 +1989,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ6">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ8">
         <v>1.25</v>
@@ -2607,7 +2607,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -3222,10 +3222,10 @@
         <v>1</v>
       </c>
       <c r="AP12">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -4046,7 +4046,7 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16">
         <v>1.5</v>
@@ -4458,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ18">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR18">
         <v>1.16</v>
@@ -4667,7 +4667,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ19">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -5488,7 +5488,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ23">
         <v>2.5</v>
@@ -5694,10 +5694,10 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ24">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -5903,7 +5903,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -6106,10 +6106,10 @@
         <v>1.25</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ26">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR26">
         <v>1.14</v>
@@ -6312,7 +6312,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ27">
         <v>0.75</v>
@@ -6521,7 +6521,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ28">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR28">
         <v>1.14</v>
@@ -7342,7 +7342,7 @@
         <v>0.8</v>
       </c>
       <c r="AP32">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ32">
         <v>1.38</v>
@@ -7551,7 +7551,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR33">
         <v>1.83</v>
@@ -7960,7 +7960,7 @@
         <v>2.6</v>
       </c>
       <c r="AP35">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ35">
         <v>2.5</v>
@@ -8375,7 +8375,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
         <v>1.52</v>
@@ -8990,7 +8990,7 @@
         <v>2.17</v>
       </c>
       <c r="AP40">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ40">
         <v>2.13</v>
@@ -9199,7 +9199,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ41">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR41">
         <v>1.17</v>
@@ -9402,7 +9402,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ42">
         <v>1.25</v>
@@ -9611,7 +9611,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ43">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR43">
         <v>1.5</v>
@@ -9814,7 +9814,7 @@
         <v>1.14</v>
       </c>
       <c r="AP44">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ44">
         <v>1.38</v>
@@ -10226,7 +10226,7 @@
         <v>1.14</v>
       </c>
       <c r="AP46">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ46">
         <v>1.38</v>
@@ -10435,7 +10435,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -10847,7 +10847,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR49">
         <v>1.28</v>
@@ -10923,6 +10923,418 @@
       </c>
       <c r="BP49">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:68">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>7793145</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="2">
+        <v>45730.375</v>
+      </c>
+      <c r="F50">
+        <v>9</v>
+      </c>
+      <c r="G50" t="s">
+        <v>72</v>
+      </c>
+      <c r="H50" t="s">
+        <v>73</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
+        <v>84</v>
+      </c>
+      <c r="P50" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q50">
+        <v>2.88</v>
+      </c>
+      <c r="R50">
+        <v>1.91</v>
+      </c>
+      <c r="S50">
+        <v>4</v>
+      </c>
+      <c r="T50">
+        <v>1.57</v>
+      </c>
+      <c r="U50">
+        <v>2.25</v>
+      </c>
+      <c r="V50">
+        <v>3.75</v>
+      </c>
+      <c r="W50">
+        <v>1.25</v>
+      </c>
+      <c r="X50">
+        <v>11</v>
+      </c>
+      <c r="Y50">
+        <v>1.05</v>
+      </c>
+      <c r="Z50">
+        <v>2.21</v>
+      </c>
+      <c r="AA50">
+        <v>3.01</v>
+      </c>
+      <c r="AB50">
+        <v>3.51</v>
+      </c>
+      <c r="AC50">
+        <v>1.1</v>
+      </c>
+      <c r="AD50">
+        <v>6.25</v>
+      </c>
+      <c r="AE50">
+        <v>1.5</v>
+      </c>
+      <c r="AF50">
+        <v>2.5</v>
+      </c>
+      <c r="AG50">
+        <v>2.37</v>
+      </c>
+      <c r="AH50">
+        <v>1.48</v>
+      </c>
+      <c r="AI50">
+        <v>2.1</v>
+      </c>
+      <c r="AJ50">
+        <v>1.67</v>
+      </c>
+      <c r="AK50">
+        <v>1.3</v>
+      </c>
+      <c r="AL50">
+        <v>1.3</v>
+      </c>
+      <c r="AM50">
+        <v>1.62</v>
+      </c>
+      <c r="AN50">
+        <v>1</v>
+      </c>
+      <c r="AO50">
+        <v>1.13</v>
+      </c>
+      <c r="AP50">
+        <v>0.89</v>
+      </c>
+      <c r="AQ50">
+        <v>1.33</v>
+      </c>
+      <c r="AR50">
+        <v>1.1</v>
+      </c>
+      <c r="AS50">
+        <v>1.32</v>
+      </c>
+      <c r="AT50">
+        <v>2.42</v>
+      </c>
+      <c r="AU50">
+        <v>7</v>
+      </c>
+      <c r="AV50">
+        <v>5</v>
+      </c>
+      <c r="AW50">
+        <v>12</v>
+      </c>
+      <c r="AX50">
+        <v>5</v>
+      </c>
+      <c r="AY50">
+        <v>19</v>
+      </c>
+      <c r="AZ50">
+        <v>10</v>
+      </c>
+      <c r="BA50">
+        <v>5</v>
+      </c>
+      <c r="BB50">
+        <v>4</v>
+      </c>
+      <c r="BC50">
+        <v>9</v>
+      </c>
+      <c r="BD50">
+        <v>1.57</v>
+      </c>
+      <c r="BE50">
+        <v>8</v>
+      </c>
+      <c r="BF50">
+        <v>2.88</v>
+      </c>
+      <c r="BG50">
+        <v>1.54</v>
+      </c>
+      <c r="BH50">
+        <v>2.25</v>
+      </c>
+      <c r="BI50">
+        <v>1.77</v>
+      </c>
+      <c r="BJ50">
+        <v>1.95</v>
+      </c>
+      <c r="BK50">
+        <v>2.45</v>
+      </c>
+      <c r="BL50">
+        <v>1.46</v>
+      </c>
+      <c r="BM50">
+        <v>3.3</v>
+      </c>
+      <c r="BN50">
+        <v>1.27</v>
+      </c>
+      <c r="BO50">
+        <v>4.4</v>
+      </c>
+      <c r="BP50">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:68">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>7793141</v>
+      </c>
+      <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="2">
+        <v>45730.8125</v>
+      </c>
+      <c r="F51">
+        <v>9</v>
+      </c>
+      <c r="G51" t="s">
+        <v>79</v>
+      </c>
+      <c r="H51" t="s">
+        <v>76</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>84</v>
+      </c>
+      <c r="P51" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q51">
+        <v>2.5</v>
+      </c>
+      <c r="R51">
+        <v>2.1</v>
+      </c>
+      <c r="S51">
+        <v>5.06</v>
+      </c>
+      <c r="T51">
+        <v>1.45</v>
+      </c>
+      <c r="U51">
+        <v>2.6</v>
+      </c>
+      <c r="V51">
+        <v>3.3</v>
+      </c>
+      <c r="W51">
+        <v>1.28</v>
+      </c>
+      <c r="X51">
+        <v>8.5</v>
+      </c>
+      <c r="Y51">
+        <v>1.01</v>
+      </c>
+      <c r="Z51">
+        <v>1.92</v>
+      </c>
+      <c r="AA51">
+        <v>2.96</v>
+      </c>
+      <c r="AB51">
+        <v>4.7</v>
+      </c>
+      <c r="AC51">
+        <v>1.06</v>
+      </c>
+      <c r="AD51">
+        <v>6.25</v>
+      </c>
+      <c r="AE51">
+        <v>1.37</v>
+      </c>
+      <c r="AF51">
+        <v>2.66</v>
+      </c>
+      <c r="AG51">
+        <v>2.2</v>
+      </c>
+      <c r="AH51">
+        <v>1.55</v>
+      </c>
+      <c r="AI51">
+        <v>1.95</v>
+      </c>
+      <c r="AJ51">
+        <v>1.7</v>
+      </c>
+      <c r="AK51">
+        <v>1.16</v>
+      </c>
+      <c r="AL51">
+        <v>1.35</v>
+      </c>
+      <c r="AM51">
+        <v>1.81</v>
+      </c>
+      <c r="AN51">
+        <v>1.88</v>
+      </c>
+      <c r="AO51">
+        <v>0.75</v>
+      </c>
+      <c r="AP51">
+        <v>1.78</v>
+      </c>
+      <c r="AQ51">
+        <v>0.78</v>
+      </c>
+      <c r="AR51">
+        <v>1.14</v>
+      </c>
+      <c r="AS51">
+        <v>1.36</v>
+      </c>
+      <c r="AT51">
+        <v>2.5</v>
+      </c>
+      <c r="AU51">
+        <v>2</v>
+      </c>
+      <c r="AV51">
+        <v>8</v>
+      </c>
+      <c r="AW51">
+        <v>5</v>
+      </c>
+      <c r="AX51">
+        <v>6</v>
+      </c>
+      <c r="AY51">
+        <v>7</v>
+      </c>
+      <c r="AZ51">
+        <v>14</v>
+      </c>
+      <c r="BA51">
+        <v>4</v>
+      </c>
+      <c r="BB51">
+        <v>2</v>
+      </c>
+      <c r="BC51">
+        <v>6</v>
+      </c>
+      <c r="BD51">
+        <v>1.58</v>
+      </c>
+      <c r="BE51">
+        <v>6.4</v>
+      </c>
+      <c r="BF51">
+        <v>2.65</v>
+      </c>
+      <c r="BG51">
+        <v>1.49</v>
+      </c>
+      <c r="BH51">
+        <v>2.38</v>
+      </c>
+      <c r="BI51">
+        <v>1.83</v>
+      </c>
+      <c r="BJ51">
+        <v>1.83</v>
+      </c>
+      <c r="BK51">
+        <v>2.32</v>
+      </c>
+      <c r="BL51">
+        <v>1.52</v>
+      </c>
+      <c r="BM51">
+        <v>3.05</v>
+      </c>
+      <c r="BN51">
+        <v>1.3</v>
+      </c>
+      <c r="BO51">
+        <v>4.1</v>
+      </c>
+      <c r="BP51">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="153">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -376,6 +376,9 @@
     <t>['78', '85']</t>
   </si>
   <si>
+    <t>['36', '90+2']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -467,6 +470,9 @@
   </si>
   <si>
     <t>['39']</t>
+  </si>
+  <si>
+    <t>['3']</t>
   </si>
 </sst>
 </file>
@@ -828,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP51"/>
+  <dimension ref="A1:BP52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1084,7 +1090,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1290,7 +1296,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1702,7 +1708,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1908,7 +1914,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -1986,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ6">
         <v>1.78</v>
@@ -2114,7 +2120,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2195,7 +2201,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ7">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2320,7 +2326,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2526,7 +2532,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2732,7 +2738,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2938,7 +2944,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3019,7 +3025,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ11">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3350,7 +3356,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3431,7 +3437,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ13">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -4174,7 +4180,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4252,7 +4258,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ17">
         <v>1.38</v>
@@ -4380,7 +4386,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4664,7 +4670,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ19">
         <v>0.78</v>
@@ -5204,7 +5210,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5285,7 +5291,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ22">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5410,7 +5416,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5491,7 +5497,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ23">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR23">
         <v>1.04</v>
@@ -6028,7 +6034,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6440,7 +6446,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6646,7 +6652,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6852,7 +6858,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6930,7 +6936,7 @@
         <v>1.75</v>
       </c>
       <c r="AP30">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ30">
         <v>1.25</v>
@@ -7136,7 +7142,7 @@
         <v>1.25</v>
       </c>
       <c r="AP31">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ31">
         <v>1.5</v>
@@ -7264,7 +7270,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7676,7 +7682,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7882,7 +7888,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -7963,7 +7969,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ35">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR35">
         <v>1.46</v>
@@ -8088,7 +8094,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8166,7 +8172,7 @@
         <v>1.6</v>
       </c>
       <c r="AP36">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ36">
         <v>1.38</v>
@@ -8500,7 +8506,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8784,7 +8790,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ39">
         <v>0.75</v>
@@ -8912,7 +8918,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -8993,7 +8999,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ40">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -9324,7 +9330,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9530,7 +9536,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9736,7 +9742,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9942,7 +9948,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10023,7 +10029,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ45">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR45">
         <v>1.43</v>
@@ -10148,7 +10154,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10354,7 +10360,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10432,7 +10438,7 @@
         <v>1.14</v>
       </c>
       <c r="AP47">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ47">
         <v>0.89</v>
@@ -10560,7 +10566,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11335,6 +11341,212 @@
       </c>
       <c r="BP51">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:68">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>7793144</v>
+      </c>
+      <c r="C52" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="2">
+        <v>45731.8125</v>
+      </c>
+      <c r="F52">
+        <v>9</v>
+      </c>
+      <c r="G52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H52" t="s">
+        <v>74</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>2</v>
+      </c>
+      <c r="L52">
+        <v>2</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>3</v>
+      </c>
+      <c r="O52" t="s">
+        <v>120</v>
+      </c>
+      <c r="P52" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q52">
+        <v>3.1</v>
+      </c>
+      <c r="R52">
+        <v>1.95</v>
+      </c>
+      <c r="S52">
+        <v>4</v>
+      </c>
+      <c r="T52">
+        <v>1.53</v>
+      </c>
+      <c r="U52">
+        <v>2.38</v>
+      </c>
+      <c r="V52">
+        <v>3.75</v>
+      </c>
+      <c r="W52">
+        <v>1.25</v>
+      </c>
+      <c r="X52">
+        <v>11</v>
+      </c>
+      <c r="Y52">
+        <v>1.05</v>
+      </c>
+      <c r="Z52">
+        <v>2.38</v>
+      </c>
+      <c r="AA52">
+        <v>2.74</v>
+      </c>
+      <c r="AB52">
+        <v>3.52</v>
+      </c>
+      <c r="AC52">
+        <v>1.1</v>
+      </c>
+      <c r="AD52">
+        <v>6.25</v>
+      </c>
+      <c r="AE52">
+        <v>1.48</v>
+      </c>
+      <c r="AF52">
+        <v>2.55</v>
+      </c>
+      <c r="AG52">
+        <v>2.37</v>
+      </c>
+      <c r="AH52">
+        <v>1.48</v>
+      </c>
+      <c r="AI52">
+        <v>2</v>
+      </c>
+      <c r="AJ52">
+        <v>1.73</v>
+      </c>
+      <c r="AK52">
+        <v>1.32</v>
+      </c>
+      <c r="AL52">
+        <v>1.37</v>
+      </c>
+      <c r="AM52">
+        <v>1.57</v>
+      </c>
+      <c r="AN52">
+        <v>2.5</v>
+      </c>
+      <c r="AO52">
+        <v>2.13</v>
+      </c>
+      <c r="AP52">
+        <v>2.56</v>
+      </c>
+      <c r="AQ52">
+        <v>1.89</v>
+      </c>
+      <c r="AR52">
+        <v>1.57</v>
+      </c>
+      <c r="AS52">
+        <v>1.77</v>
+      </c>
+      <c r="AT52">
+        <v>3.34</v>
+      </c>
+      <c r="AU52">
+        <v>4</v>
+      </c>
+      <c r="AV52">
+        <v>5</v>
+      </c>
+      <c r="AW52">
+        <v>12</v>
+      </c>
+      <c r="AX52">
+        <v>4</v>
+      </c>
+      <c r="AY52">
+        <v>16</v>
+      </c>
+      <c r="AZ52">
+        <v>9</v>
+      </c>
+      <c r="BA52">
+        <v>3</v>
+      </c>
+      <c r="BB52">
+        <v>3</v>
+      </c>
+      <c r="BC52">
+        <v>6</v>
+      </c>
+      <c r="BD52">
+        <v>1.88</v>
+      </c>
+      <c r="BE52">
+        <v>6.05</v>
+      </c>
+      <c r="BF52">
+        <v>2.38</v>
+      </c>
+      <c r="BG52">
+        <v>1.36</v>
+      </c>
+      <c r="BH52">
+        <v>2.69</v>
+      </c>
+      <c r="BI52">
+        <v>1.7</v>
+      </c>
+      <c r="BJ52">
+        <v>2.05</v>
+      </c>
+      <c r="BK52">
+        <v>1.95</v>
+      </c>
+      <c r="BL52">
+        <v>1.77</v>
+      </c>
+      <c r="BM52">
+        <v>2.88</v>
+      </c>
+      <c r="BN52">
+        <v>1.32</v>
+      </c>
+      <c r="BO52">
+        <v>3.22</v>
+      </c>
+      <c r="BP52">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="154">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>['36', '90+2']</t>
+  </si>
+  <si>
+    <t>['21', '52']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -834,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP52"/>
+  <dimension ref="A1:BP54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1090,7 +1093,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1171,7 +1174,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ2">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1296,7 +1299,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1374,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ3">
         <v>0.78</v>
@@ -1708,7 +1711,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1789,7 +1792,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1914,7 +1917,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2120,7 +2123,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2198,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ7">
         <v>2.56</v>
@@ -2326,7 +2329,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2532,7 +2535,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2610,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ9">
         <v>0.89</v>
@@ -2738,7 +2741,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2816,10 +2819,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -2944,7 +2947,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3356,7 +3359,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3434,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
         <v>1.89</v>
@@ -3643,7 +3646,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ14">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -3846,7 +3849,7 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ15">
         <v>0.5</v>
@@ -4055,7 +4058,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ16">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4180,7 +4183,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4261,7 +4264,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ17">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4386,7 +4389,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4876,7 +4879,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ20">
         <v>0.5</v>
@@ -5085,7 +5088,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ21">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5210,7 +5213,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5288,7 +5291,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>1.89</v>
@@ -5416,7 +5419,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5906,7 +5909,7 @@
         <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25">
         <v>0.89</v>
@@ -6034,7 +6037,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6321,7 +6324,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ27">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.17</v>
@@ -6446,7 +6449,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6652,7 +6655,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6730,10 +6733,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ29">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -6858,7 +6861,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7145,7 +7148,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ31">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR31">
         <v>1.72</v>
@@ -7270,7 +7273,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7351,7 +7354,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ32">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR32">
         <v>1.08</v>
@@ -7554,7 +7557,7 @@
         <v>1.2</v>
       </c>
       <c r="AP33">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
         <v>0.89</v>
@@ -7682,7 +7685,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7760,7 +7763,7 @@
         <v>0.2</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34">
         <v>0.5</v>
@@ -7888,7 +7891,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8094,7 +8097,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8175,7 +8178,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ36">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR36">
         <v>1.8</v>
@@ -8506,7 +8509,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8584,10 +8587,10 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR38">
         <v>1.26</v>
@@ -8793,7 +8796,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ39">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.59</v>
@@ -8918,7 +8921,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9330,7 +9333,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9536,7 +9539,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9614,7 +9617,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ43">
         <v>1.78</v>
@@ -9742,7 +9745,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9823,7 +9826,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ44">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -9948,7 +9951,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10154,7 +10157,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10235,7 +10238,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ46">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR46">
         <v>1.32</v>
@@ -10360,7 +10363,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10566,7 +10569,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -10644,7 +10647,7 @@
         <v>0.57</v>
       </c>
       <c r="AP48">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
         <v>0.5</v>
@@ -10850,7 +10853,7 @@
         <v>2.14</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ49">
         <v>1.78</v>
@@ -11390,7 +11393,7 @@
         <v>120</v>
       </c>
       <c r="P52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -11547,6 +11550,418 @@
       </c>
       <c r="BP52">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:68">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>7793140</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="2">
+        <v>45732.76041666666</v>
+      </c>
+      <c r="F53">
+        <v>9</v>
+      </c>
+      <c r="G53" t="s">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s">
+        <v>80</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>2</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>2</v>
+      </c>
+      <c r="O53" t="s">
+        <v>121</v>
+      </c>
+      <c r="P53" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q53">
+        <v>2.5</v>
+      </c>
+      <c r="R53">
+        <v>2.05</v>
+      </c>
+      <c r="S53">
+        <v>5.5</v>
+      </c>
+      <c r="T53">
+        <v>1.5</v>
+      </c>
+      <c r="U53">
+        <v>2.5</v>
+      </c>
+      <c r="V53">
+        <v>3.5</v>
+      </c>
+      <c r="W53">
+        <v>1.29</v>
+      </c>
+      <c r="X53">
+        <v>11</v>
+      </c>
+      <c r="Y53">
+        <v>1.05</v>
+      </c>
+      <c r="Z53">
+        <v>1.75</v>
+      </c>
+      <c r="AA53">
+        <v>3.47</v>
+      </c>
+      <c r="AB53">
+        <v>4.8</v>
+      </c>
+      <c r="AC53">
+        <v>1.07</v>
+      </c>
+      <c r="AD53">
+        <v>7.5</v>
+      </c>
+      <c r="AE53">
+        <v>1.42</v>
+      </c>
+      <c r="AF53">
+        <v>2.75</v>
+      </c>
+      <c r="AG53">
+        <v>2.25</v>
+      </c>
+      <c r="AH53">
+        <v>1.53</v>
+      </c>
+      <c r="AI53">
+        <v>2.2</v>
+      </c>
+      <c r="AJ53">
+        <v>1.62</v>
+      </c>
+      <c r="AK53">
+        <v>1.18</v>
+      </c>
+      <c r="AL53">
+        <v>1.3</v>
+      </c>
+      <c r="AM53">
+        <v>1.98</v>
+      </c>
+      <c r="AN53">
+        <v>1.38</v>
+      </c>
+      <c r="AO53">
+        <v>1.5</v>
+      </c>
+      <c r="AP53">
+        <v>1.56</v>
+      </c>
+      <c r="AQ53">
+        <v>1.33</v>
+      </c>
+      <c r="AR53">
+        <v>1.53</v>
+      </c>
+      <c r="AS53">
+        <v>1.25</v>
+      </c>
+      <c r="AT53">
+        <v>2.78</v>
+      </c>
+      <c r="AU53">
+        <v>4</v>
+      </c>
+      <c r="AV53">
+        <v>0</v>
+      </c>
+      <c r="AW53">
+        <v>4</v>
+      </c>
+      <c r="AX53">
+        <v>3</v>
+      </c>
+      <c r="AY53">
+        <v>8</v>
+      </c>
+      <c r="AZ53">
+        <v>3</v>
+      </c>
+      <c r="BA53">
+        <v>5</v>
+      </c>
+      <c r="BB53">
+        <v>2</v>
+      </c>
+      <c r="BC53">
+        <v>7</v>
+      </c>
+      <c r="BD53">
+        <v>1.48</v>
+      </c>
+      <c r="BE53">
+        <v>8.4</v>
+      </c>
+      <c r="BF53">
+        <v>3.1</v>
+      </c>
+      <c r="BG53">
+        <v>1.28</v>
+      </c>
+      <c r="BH53">
+        <v>3.05</v>
+      </c>
+      <c r="BI53">
+        <v>1.54</v>
+      </c>
+      <c r="BJ53">
+        <v>2.19</v>
+      </c>
+      <c r="BK53">
+        <v>1.95</v>
+      </c>
+      <c r="BL53">
+        <v>1.77</v>
+      </c>
+      <c r="BM53">
+        <v>2.52</v>
+      </c>
+      <c r="BN53">
+        <v>1.41</v>
+      </c>
+      <c r="BO53">
+        <v>3.5</v>
+      </c>
+      <c r="BP53">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:68">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>7793142</v>
+      </c>
+      <c r="C54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="2">
+        <v>45732.85416666666</v>
+      </c>
+      <c r="F54">
+        <v>9</v>
+      </c>
+      <c r="G54" t="s">
+        <v>77</v>
+      </c>
+      <c r="H54" t="s">
+        <v>71</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54" t="s">
+        <v>84</v>
+      </c>
+      <c r="P54" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q54">
+        <v>3</v>
+      </c>
+      <c r="R54">
+        <v>2.05</v>
+      </c>
+      <c r="S54">
+        <v>4</v>
+      </c>
+      <c r="T54">
+        <v>1.5</v>
+      </c>
+      <c r="U54">
+        <v>2.5</v>
+      </c>
+      <c r="V54">
+        <v>3.4</v>
+      </c>
+      <c r="W54">
+        <v>1.3</v>
+      </c>
+      <c r="X54">
+        <v>10</v>
+      </c>
+      <c r="Y54">
+        <v>1.06</v>
+      </c>
+      <c r="Z54">
+        <v>2.3</v>
+      </c>
+      <c r="AA54">
+        <v>3.16</v>
+      </c>
+      <c r="AB54">
+        <v>3.14</v>
+      </c>
+      <c r="AC54">
+        <v>1.07</v>
+      </c>
+      <c r="AD54">
+        <v>7.5</v>
+      </c>
+      <c r="AE54">
+        <v>1.4</v>
+      </c>
+      <c r="AF54">
+        <v>2.85</v>
+      </c>
+      <c r="AG54">
+        <v>2.1</v>
+      </c>
+      <c r="AH54">
+        <v>1.6</v>
+      </c>
+      <c r="AI54">
+        <v>1.83</v>
+      </c>
+      <c r="AJ54">
+        <v>1.83</v>
+      </c>
+      <c r="AK54">
+        <v>1.34</v>
+      </c>
+      <c r="AL54">
+        <v>1.33</v>
+      </c>
+      <c r="AM54">
+        <v>1.6</v>
+      </c>
+      <c r="AN54">
+        <v>1.38</v>
+      </c>
+      <c r="AO54">
+        <v>0.75</v>
+      </c>
+      <c r="AP54">
+        <v>1.22</v>
+      </c>
+      <c r="AQ54">
+        <v>1</v>
+      </c>
+      <c r="AR54">
+        <v>1.4</v>
+      </c>
+      <c r="AS54">
+        <v>1.61</v>
+      </c>
+      <c r="AT54">
+        <v>3.01</v>
+      </c>
+      <c r="AU54">
+        <v>7</v>
+      </c>
+      <c r="AV54">
+        <v>6</v>
+      </c>
+      <c r="AW54">
+        <v>6</v>
+      </c>
+      <c r="AX54">
+        <v>8</v>
+      </c>
+      <c r="AY54">
+        <v>13</v>
+      </c>
+      <c r="AZ54">
+        <v>14</v>
+      </c>
+      <c r="BA54">
+        <v>7</v>
+      </c>
+      <c r="BB54">
+        <v>2</v>
+      </c>
+      <c r="BC54">
+        <v>9</v>
+      </c>
+      <c r="BD54">
+        <v>1.91</v>
+      </c>
+      <c r="BE54">
+        <v>6.15</v>
+      </c>
+      <c r="BF54">
+        <v>2.32</v>
+      </c>
+      <c r="BG54">
+        <v>1.32</v>
+      </c>
+      <c r="BH54">
+        <v>2.88</v>
+      </c>
+      <c r="BI54">
+        <v>1.7</v>
+      </c>
+      <c r="BJ54">
+        <v>2.05</v>
+      </c>
+      <c r="BK54">
+        <v>2.04</v>
+      </c>
+      <c r="BL54">
+        <v>1.66</v>
+      </c>
+      <c r="BM54">
+        <v>2.69</v>
+      </c>
+      <c r="BN54">
+        <v>1.36</v>
+      </c>
+      <c r="BO54">
+        <v>3.75</v>
+      </c>
+      <c r="BP54">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="155">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -476,6 +476,9 @@
   </si>
   <si>
     <t>['3']</t>
+  </si>
+  <si>
+    <t>['88']</t>
   </si>
 </sst>
 </file>
@@ -837,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP54"/>
+  <dimension ref="A1:BP55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1171,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ2">
         <v>1.33</v>
@@ -1586,7 +1589,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2410,7 +2413,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -3025,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ11">
         <v>2.56</v>
@@ -3643,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -3852,7 +3855,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -4882,7 +4885,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR20">
         <v>1.3</v>
@@ -5085,7 +5088,7 @@
         <v>1.67</v>
       </c>
       <c r="AP21">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ21">
         <v>1.56</v>
@@ -6527,7 +6530,7 @@
         <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ28">
         <v>1.78</v>
@@ -6942,7 +6945,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR30">
         <v>1.83</v>
@@ -7766,7 +7769,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ34">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR34">
         <v>1.34</v>
@@ -8381,7 +8384,7 @@
         <v>1.4</v>
       </c>
       <c r="AP37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -9205,7 +9208,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ41">
         <v>0.78</v>
@@ -9414,7 +9417,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR42">
         <v>1.17</v>
@@ -10029,7 +10032,7 @@
         <v>2.71</v>
       </c>
       <c r="AP45">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ45">
         <v>2.56</v>
@@ -10650,7 +10653,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR48">
         <v>1.65</v>
@@ -11961,6 +11964,212 @@
         <v>3.75</v>
       </c>
       <c r="BP54">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:68">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>7793143</v>
+      </c>
+      <c r="C55" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="2">
+        <v>45733.85416666666</v>
+      </c>
+      <c r="F55">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s">
+        <v>78</v>
+      </c>
+      <c r="H55" t="s">
+        <v>70</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>2</v>
+      </c>
+      <c r="O55" t="s">
+        <v>102</v>
+      </c>
+      <c r="P55" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q55">
+        <v>2.78</v>
+      </c>
+      <c r="R55">
+        <v>1.95</v>
+      </c>
+      <c r="S55">
+        <v>4.1</v>
+      </c>
+      <c r="T55">
+        <v>1.47</v>
+      </c>
+      <c r="U55">
+        <v>2.49</v>
+      </c>
+      <c r="V55">
+        <v>3.14</v>
+      </c>
+      <c r="W55">
+        <v>1.31</v>
+      </c>
+      <c r="X55">
+        <v>7.7</v>
+      </c>
+      <c r="Y55">
+        <v>1.02</v>
+      </c>
+      <c r="Z55">
+        <v>2.19</v>
+      </c>
+      <c r="AA55">
+        <v>3.15</v>
+      </c>
+      <c r="AB55">
+        <v>3.37</v>
+      </c>
+      <c r="AC55">
+        <v>1.04</v>
+      </c>
+      <c r="AD55">
+        <v>7.1</v>
+      </c>
+      <c r="AE55">
+        <v>1.35</v>
+      </c>
+      <c r="AF55">
+        <v>2.74</v>
+      </c>
+      <c r="AG55">
+        <v>2.1</v>
+      </c>
+      <c r="AH55">
+        <v>1.6</v>
+      </c>
+      <c r="AI55">
+        <v>1.88</v>
+      </c>
+      <c r="AJ55">
+        <v>1.78</v>
+      </c>
+      <c r="AK55">
+        <v>1.28</v>
+      </c>
+      <c r="AL55">
+        <v>1.31</v>
+      </c>
+      <c r="AM55">
+        <v>1.61</v>
+      </c>
+      <c r="AN55">
+        <v>0.5</v>
+      </c>
+      <c r="AO55">
+        <v>1.25</v>
+      </c>
+      <c r="AP55">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ55">
+        <v>1.22</v>
+      </c>
+      <c r="AR55">
+        <v>1.34</v>
+      </c>
+      <c r="AS55">
+        <v>1.34</v>
+      </c>
+      <c r="AT55">
+        <v>2.68</v>
+      </c>
+      <c r="AU55">
+        <v>8</v>
+      </c>
+      <c r="AV55">
+        <v>7</v>
+      </c>
+      <c r="AW55">
+        <v>15</v>
+      </c>
+      <c r="AX55">
+        <v>10</v>
+      </c>
+      <c r="AY55">
+        <v>23</v>
+      </c>
+      <c r="AZ55">
+        <v>17</v>
+      </c>
+      <c r="BA55">
+        <v>4</v>
+      </c>
+      <c r="BB55">
+        <v>6</v>
+      </c>
+      <c r="BC55">
+        <v>10</v>
+      </c>
+      <c r="BD55">
+        <v>1.76</v>
+      </c>
+      <c r="BE55">
+        <v>6.25</v>
+      </c>
+      <c r="BF55">
+        <v>2.3</v>
+      </c>
+      <c r="BG55">
+        <v>1.46</v>
+      </c>
+      <c r="BH55">
+        <v>2.45</v>
+      </c>
+      <c r="BI55">
+        <v>1.78</v>
+      </c>
+      <c r="BJ55">
+        <v>1.88</v>
+      </c>
+      <c r="BK55">
+        <v>2.28</v>
+      </c>
+      <c r="BL55">
+        <v>1.53</v>
+      </c>
+      <c r="BM55">
+        <v>2.95</v>
+      </c>
+      <c r="BN55">
+        <v>1.33</v>
+      </c>
+      <c r="BO55">
+        <v>3.95</v>
+      </c>
+      <c r="BP55">
         <v>1.19</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="157">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -382,6 +382,9 @@
     <t>['21', '52']</t>
   </si>
   <si>
+    <t>['31']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -479,6 +482,9 @@
   </si>
   <si>
     <t>['88']</t>
+  </si>
+  <si>
+    <t>['22']</t>
   </si>
 </sst>
 </file>
@@ -840,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP55"/>
+  <dimension ref="A1:BP56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1096,7 +1102,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1174,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2">
         <v>1.33</v>
@@ -1302,7 +1308,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1714,7 +1720,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1795,7 +1801,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1920,7 +1926,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2126,7 +2132,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2332,7 +2338,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2413,7 +2419,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -2538,7 +2544,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2616,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ9">
         <v>0.89</v>
@@ -2744,7 +2750,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2950,7 +2956,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3362,7 +3368,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3646,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4186,7 +4192,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4267,7 +4273,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4392,7 +4398,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4882,7 +4888,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ20">
         <v>0.5600000000000001</v>
@@ -5088,7 +5094,7 @@
         <v>1.67</v>
       </c>
       <c r="AP21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ21">
         <v>1.56</v>
@@ -5216,7 +5222,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5422,7 +5428,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -6040,7 +6046,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6452,7 +6458,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6658,7 +6664,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6739,7 +6745,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ29">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -6864,7 +6870,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6945,7 +6951,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ30">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR30">
         <v>1.83</v>
@@ -7276,7 +7282,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7357,7 +7363,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR32">
         <v>1.08</v>
@@ -7688,7 +7694,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7894,7 +7900,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8100,7 +8106,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8384,7 +8390,7 @@
         <v>1.4</v>
       </c>
       <c r="AP37">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -8512,7 +8518,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8590,7 +8596,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ38">
         <v>1.33</v>
@@ -8924,7 +8930,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9336,7 +9342,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9417,7 +9423,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR42">
         <v>1.17</v>
@@ -9542,7 +9548,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9748,7 +9754,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9829,7 +9835,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -9954,7 +9960,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10032,7 +10038,7 @@
         <v>2.71</v>
       </c>
       <c r="AP45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ45">
         <v>2.56</v>
@@ -10160,7 +10166,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10366,7 +10372,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10572,7 +10578,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11396,7 +11402,7 @@
         <v>120</v>
       </c>
       <c r="P52" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -11808,7 +11814,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -11886,7 +11892,7 @@
         <v>0.75</v>
       </c>
       <c r="AP54">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12014,7 +12020,7 @@
         <v>102</v>
       </c>
       <c r="P55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q55">
         <v>2.78</v>
@@ -12095,7 +12101,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ55">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR55">
         <v>1.34</v>
@@ -12171,6 +12177,212 @@
       </c>
       <c r="BP55">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:68">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>7793149</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="2">
+        <v>45737.8125</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56" t="s">
+        <v>70</v>
+      </c>
+      <c r="H56" t="s">
+        <v>77</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>2</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>2</v>
+      </c>
+      <c r="O56" t="s">
+        <v>122</v>
+      </c>
+      <c r="P56" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q56">
+        <v>2.63</v>
+      </c>
+      <c r="R56">
+        <v>2.2</v>
+      </c>
+      <c r="S56">
+        <v>4</v>
+      </c>
+      <c r="T56">
+        <v>1.4</v>
+      </c>
+      <c r="U56">
+        <v>2.75</v>
+      </c>
+      <c r="V56">
+        <v>3</v>
+      </c>
+      <c r="W56">
+        <v>1.36</v>
+      </c>
+      <c r="X56">
+        <v>8</v>
+      </c>
+      <c r="Y56">
+        <v>1.08</v>
+      </c>
+      <c r="Z56">
+        <v>2.25</v>
+      </c>
+      <c r="AA56">
+        <v>3.2</v>
+      </c>
+      <c r="AB56">
+        <v>3.2</v>
+      </c>
+      <c r="AC56">
+        <v>1.06</v>
+      </c>
+      <c r="AD56">
+        <v>8</v>
+      </c>
+      <c r="AE56">
+        <v>1.33</v>
+      </c>
+      <c r="AF56">
+        <v>3.1</v>
+      </c>
+      <c r="AG56">
+        <v>1.91</v>
+      </c>
+      <c r="AH56">
+        <v>1.81</v>
+      </c>
+      <c r="AI56">
+        <v>1.73</v>
+      </c>
+      <c r="AJ56">
+        <v>2</v>
+      </c>
+      <c r="AK56">
+        <v>1.35</v>
+      </c>
+      <c r="AL56">
+        <v>1.31</v>
+      </c>
+      <c r="AM56">
+        <v>1.6</v>
+      </c>
+      <c r="AN56">
+        <v>1.22</v>
+      </c>
+      <c r="AO56">
+        <v>1.22</v>
+      </c>
+      <c r="AP56">
+        <v>1.2</v>
+      </c>
+      <c r="AQ56">
+        <v>1.2</v>
+      </c>
+      <c r="AR56">
+        <v>1.42</v>
+      </c>
+      <c r="AS56">
+        <v>1.47</v>
+      </c>
+      <c r="AT56">
+        <v>2.89</v>
+      </c>
+      <c r="AU56">
+        <v>6</v>
+      </c>
+      <c r="AV56">
+        <v>5</v>
+      </c>
+      <c r="AW56">
+        <v>5</v>
+      </c>
+      <c r="AX56">
+        <v>4</v>
+      </c>
+      <c r="AY56">
+        <v>11</v>
+      </c>
+      <c r="AZ56">
+        <v>9</v>
+      </c>
+      <c r="BA56">
+        <v>7</v>
+      </c>
+      <c r="BB56">
+        <v>11</v>
+      </c>
+      <c r="BC56">
+        <v>18</v>
+      </c>
+      <c r="BD56">
+        <v>1.64</v>
+      </c>
+      <c r="BE56">
+        <v>7.7</v>
+      </c>
+      <c r="BF56">
+        <v>2.64</v>
+      </c>
+      <c r="BG56">
+        <v>1.47</v>
+      </c>
+      <c r="BH56">
+        <v>2.35</v>
+      </c>
+      <c r="BI56">
+        <v>1.91</v>
+      </c>
+      <c r="BJ56">
+        <v>1.8</v>
+      </c>
+      <c r="BK56">
+        <v>2.42</v>
+      </c>
+      <c r="BL56">
+        <v>1.44</v>
+      </c>
+      <c r="BM56">
+        <v>3.34</v>
+      </c>
+      <c r="BN56">
+        <v>1.24</v>
+      </c>
+      <c r="BO56">
+        <v>3.65</v>
+      </c>
+      <c r="BP56">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="159">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -485,6 +485,12 @@
   </si>
   <si>
     <t>['22']</t>
+  </si>
+  <si>
+    <t>['2', '28', '43', '54', '63']</t>
+  </si>
+  <si>
+    <t>['45']</t>
   </si>
 </sst>
 </file>
@@ -846,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP56"/>
+  <dimension ref="A1:BP58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1595,7 +1601,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ4">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1798,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5">
         <v>1.2</v>
@@ -2004,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ6">
         <v>1.78</v>
@@ -2213,7 +2219,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ7">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3034,10 +3040,10 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ11">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3243,7 +3249,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3449,7 +3455,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -3861,7 +3867,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ15">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -4064,7 +4070,7 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ16">
         <v>1.33</v>
@@ -4270,7 +4276,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ17">
         <v>1.2</v>
@@ -4682,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ19">
         <v>0.78</v>
@@ -4891,7 +4897,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ20">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR20">
         <v>1.3</v>
@@ -5303,7 +5309,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5509,7 +5515,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ23">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AR23">
         <v>1.04</v>
@@ -5715,7 +5721,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -6330,7 +6336,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6536,7 +6542,7 @@
         <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ28">
         <v>1.78</v>
@@ -6948,7 +6954,7 @@
         <v>1.75</v>
       </c>
       <c r="AP30">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ30">
         <v>1.2</v>
@@ -7154,7 +7160,7 @@
         <v>1.25</v>
       </c>
       <c r="AP31">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ31">
         <v>1.33</v>
@@ -7775,7 +7781,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ34">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR34">
         <v>1.34</v>
@@ -7981,7 +7987,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ35">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AR35">
         <v>1.46</v>
@@ -8184,7 +8190,7 @@
         <v>1.6</v>
       </c>
       <c r="AP36">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ36">
         <v>1.56</v>
@@ -8393,7 +8399,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR37">
         <v>1.52</v>
@@ -8802,7 +8808,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9008,10 +9014,10 @@
         <v>2.17</v>
       </c>
       <c r="AP40">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ40">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -9214,7 +9220,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ41">
         <v>0.78</v>
@@ -10041,7 +10047,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ45">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AR45">
         <v>1.43</v>
@@ -10244,7 +10250,7 @@
         <v>1.14</v>
       </c>
       <c r="AP46">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ46">
         <v>1.56</v>
@@ -10450,7 +10456,7 @@
         <v>1.14</v>
       </c>
       <c r="AP47">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ47">
         <v>0.89</v>
@@ -10659,7 +10665,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR48">
         <v>1.65</v>
@@ -11071,7 +11077,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR50">
         <v>1.1</v>
@@ -11480,10 +11486,10 @@
         <v>2.13</v>
       </c>
       <c r="AP52">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ52">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR52">
         <v>1.57</v>
@@ -12098,7 +12104,7 @@
         <v>1.25</v>
       </c>
       <c r="AP55">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ55">
         <v>1.2</v>
@@ -12383,6 +12389,418 @@
       </c>
       <c r="BP56">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:68">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>7793147</v>
+      </c>
+      <c r="C57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="2">
+        <v>45738.76041666666</v>
+      </c>
+      <c r="F57">
+        <v>10</v>
+      </c>
+      <c r="G57" t="s">
+        <v>73</v>
+      </c>
+      <c r="H57" t="s">
+        <v>81</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3</v>
+      </c>
+      <c r="K57">
+        <v>3</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>5</v>
+      </c>
+      <c r="N57">
+        <v>5</v>
+      </c>
+      <c r="O57" t="s">
+        <v>84</v>
+      </c>
+      <c r="P57" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q57">
+        <v>4.75</v>
+      </c>
+      <c r="R57">
+        <v>2.1</v>
+      </c>
+      <c r="S57">
+        <v>2.5</v>
+      </c>
+      <c r="T57">
+        <v>1.44</v>
+      </c>
+      <c r="U57">
+        <v>2.63</v>
+      </c>
+      <c r="V57">
+        <v>3.25</v>
+      </c>
+      <c r="W57">
+        <v>1.33</v>
+      </c>
+      <c r="X57">
+        <v>9</v>
+      </c>
+      <c r="Y57">
+        <v>1.07</v>
+      </c>
+      <c r="Z57">
+        <v>4</v>
+      </c>
+      <c r="AA57">
+        <v>3.4</v>
+      </c>
+      <c r="AB57">
+        <v>1.9</v>
+      </c>
+      <c r="AC57">
+        <v>1.03</v>
+      </c>
+      <c r="AD57">
+        <v>10.5</v>
+      </c>
+      <c r="AE57">
+        <v>1.3</v>
+      </c>
+      <c r="AF57">
+        <v>3.35</v>
+      </c>
+      <c r="AG57">
+        <v>1.95</v>
+      </c>
+      <c r="AH57">
+        <v>1.7</v>
+      </c>
+      <c r="AI57">
+        <v>1.88</v>
+      </c>
+      <c r="AJ57">
+        <v>1.82</v>
+      </c>
+      <c r="AK57">
+        <v>1.8</v>
+      </c>
+      <c r="AL57">
+        <v>1.22</v>
+      </c>
+      <c r="AM57">
+        <v>1.2</v>
+      </c>
+      <c r="AN57">
+        <v>1.33</v>
+      </c>
+      <c r="AO57">
+        <v>2.56</v>
+      </c>
+      <c r="AP57">
+        <v>1.2</v>
+      </c>
+      <c r="AQ57">
+        <v>2.6</v>
+      </c>
+      <c r="AR57">
+        <v>1.3</v>
+      </c>
+      <c r="AS57">
+        <v>1.57</v>
+      </c>
+      <c r="AT57">
+        <v>2.87</v>
+      </c>
+      <c r="AU57">
+        <v>4</v>
+      </c>
+      <c r="AV57">
+        <v>9</v>
+      </c>
+      <c r="AW57">
+        <v>3</v>
+      </c>
+      <c r="AX57">
+        <v>12</v>
+      </c>
+      <c r="AY57">
+        <v>7</v>
+      </c>
+      <c r="AZ57">
+        <v>21</v>
+      </c>
+      <c r="BA57">
+        <v>2</v>
+      </c>
+      <c r="BB57">
+        <v>4</v>
+      </c>
+      <c r="BC57">
+        <v>6</v>
+      </c>
+      <c r="BD57">
+        <v>3.04</v>
+      </c>
+      <c r="BE57">
+        <v>6.25</v>
+      </c>
+      <c r="BF57">
+        <v>1.59</v>
+      </c>
+      <c r="BG57">
+        <v>1.47</v>
+      </c>
+      <c r="BH57">
+        <v>2.35</v>
+      </c>
+      <c r="BI57">
+        <v>1.95</v>
+      </c>
+      <c r="BJ57">
+        <v>1.85</v>
+      </c>
+      <c r="BK57">
+        <v>2.43</v>
+      </c>
+      <c r="BL57">
+        <v>1.44</v>
+      </c>
+      <c r="BM57">
+        <v>3.34</v>
+      </c>
+      <c r="BN57">
+        <v>1.24</v>
+      </c>
+      <c r="BO57">
+        <v>4.33</v>
+      </c>
+      <c r="BP57">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:68">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>7793148</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="2">
+        <v>45738.85416666666</v>
+      </c>
+      <c r="F58">
+        <v>10</v>
+      </c>
+      <c r="G58" t="s">
+        <v>74</v>
+      </c>
+      <c r="H58" t="s">
+        <v>78</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="O58" t="s">
+        <v>84</v>
+      </c>
+      <c r="P58" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q58">
+        <v>2.69</v>
+      </c>
+      <c r="R58">
+        <v>2.18</v>
+      </c>
+      <c r="S58">
+        <v>4.11</v>
+      </c>
+      <c r="T58">
+        <v>1.43</v>
+      </c>
+      <c r="U58">
+        <v>2.71</v>
+      </c>
+      <c r="V58">
+        <v>3.35</v>
+      </c>
+      <c r="W58">
+        <v>1.3</v>
+      </c>
+      <c r="X58">
+        <v>9</v>
+      </c>
+      <c r="Y58">
+        <v>1.01</v>
+      </c>
+      <c r="Z58">
+        <v>1.91</v>
+      </c>
+      <c r="AA58">
+        <v>3.25</v>
+      </c>
+      <c r="AB58">
+        <v>4.2</v>
+      </c>
+      <c r="AC58">
+        <v>1.02</v>
+      </c>
+      <c r="AD58">
+        <v>8.1</v>
+      </c>
+      <c r="AE58">
+        <v>1.4</v>
+      </c>
+      <c r="AF58">
+        <v>2.81</v>
+      </c>
+      <c r="AG58">
+        <v>2.2</v>
+      </c>
+      <c r="AH58">
+        <v>1.55</v>
+      </c>
+      <c r="AI58">
+        <v>2</v>
+      </c>
+      <c r="AJ58">
+        <v>1.67</v>
+      </c>
+      <c r="AK58">
+        <v>1.18</v>
+      </c>
+      <c r="AL58">
+        <v>1.28</v>
+      </c>
+      <c r="AM58">
+        <v>1.91</v>
+      </c>
+      <c r="AN58">
+        <v>1.89</v>
+      </c>
+      <c r="AO58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP58">
+        <v>1.7</v>
+      </c>
+      <c r="AQ58">
+        <v>0.8</v>
+      </c>
+      <c r="AR58">
+        <v>1.71</v>
+      </c>
+      <c r="AS58">
+        <v>1.46</v>
+      </c>
+      <c r="AT58">
+        <v>3.17</v>
+      </c>
+      <c r="AU58">
+        <v>3</v>
+      </c>
+      <c r="AV58">
+        <v>4</v>
+      </c>
+      <c r="AW58">
+        <v>7</v>
+      </c>
+      <c r="AX58">
+        <v>7</v>
+      </c>
+      <c r="AY58">
+        <v>10</v>
+      </c>
+      <c r="AZ58">
+        <v>11</v>
+      </c>
+      <c r="BA58">
+        <v>3</v>
+      </c>
+      <c r="BB58">
+        <v>6</v>
+      </c>
+      <c r="BC58">
+        <v>9</v>
+      </c>
+      <c r="BD58">
+        <v>1.65</v>
+      </c>
+      <c r="BE58">
+        <v>6.25</v>
+      </c>
+      <c r="BF58">
+        <v>2.55</v>
+      </c>
+      <c r="BG58">
+        <v>1.5</v>
+      </c>
+      <c r="BH58">
+        <v>2.33</v>
+      </c>
+      <c r="BI58">
+        <v>1.85</v>
+      </c>
+      <c r="BJ58">
+        <v>1.81</v>
+      </c>
+      <c r="BK58">
+        <v>2.35</v>
+      </c>
+      <c r="BL58">
+        <v>1.5</v>
+      </c>
+      <c r="BM58">
+        <v>3.05</v>
+      </c>
+      <c r="BN58">
+        <v>1.3</v>
+      </c>
+      <c r="BO58">
+        <v>4.1</v>
+      </c>
+      <c r="BP58">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="160">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -385,6 +385,9 @@
     <t>['31']</t>
   </si>
   <si>
+    <t>['3']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -478,9 +481,6 @@
     <t>['39']</t>
   </si>
   <si>
-    <t>['3']</t>
-  </si>
-  <si>
     <t>['88']</t>
   </si>
   <si>
@@ -491,6 +491,9 @@
   </si>
   <si>
     <t>['45']</t>
+  </si>
+  <si>
+    <t>['29']</t>
   </si>
 </sst>
 </file>
@@ -852,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP58"/>
+  <dimension ref="A1:BP60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1108,7 +1111,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1314,7 +1317,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1392,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ3">
         <v>0.78</v>
@@ -1598,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ4">
         <v>0.8</v>
@@ -1726,7 +1729,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1932,7 +1935,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2013,7 +2016,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ6">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2138,7 +2141,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2216,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
         <v>2.6</v>
@@ -2344,7 +2347,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2550,7 +2553,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2631,7 +2634,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ9">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2756,7 +2759,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2834,10 +2837,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ10">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -2962,7 +2965,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3246,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="AP12">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ12">
         <v>1.2</v>
@@ -3374,7 +3377,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3661,7 +3664,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -3864,7 +3867,7 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15">
         <v>0.8</v>
@@ -4198,7 +4201,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4404,7 +4407,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4482,10 +4485,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ18">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR18">
         <v>1.16</v>
@@ -5103,7 +5106,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ21">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5228,7 +5231,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5306,7 +5309,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ22">
         <v>1.7</v>
@@ -5434,7 +5437,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5512,7 +5515,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ23">
         <v>2.6</v>
@@ -5927,7 +5930,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -6052,7 +6055,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6130,7 +6133,7 @@
         <v>1.25</v>
       </c>
       <c r="AP26">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ26">
         <v>0.78</v>
@@ -6339,7 +6342,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR27">
         <v>1.17</v>
@@ -6464,7 +6467,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6545,7 +6548,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ28">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR28">
         <v>1.14</v>
@@ -6670,7 +6673,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6748,7 +6751,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>1.2</v>
@@ -6876,7 +6879,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7288,7 +7291,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7366,7 +7369,7 @@
         <v>0.8</v>
       </c>
       <c r="AP32">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ32">
         <v>1.2</v>
@@ -7572,10 +7575,10 @@
         <v>1.2</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ33">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR33">
         <v>1.83</v>
@@ -7700,7 +7703,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7906,7 +7909,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8112,7 +8115,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8193,7 +8196,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ36">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR36">
         <v>1.8</v>
@@ -8524,7 +8527,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8811,7 +8814,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR39">
         <v>1.59</v>
@@ -8936,7 +8939,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9348,7 +9351,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9426,7 +9429,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ42">
         <v>1.2</v>
@@ -9554,7 +9557,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9632,10 +9635,10 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ43">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR43">
         <v>1.5</v>
@@ -9760,7 +9763,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9966,7 +9969,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10172,7 +10175,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10253,7 +10256,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ46">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR46">
         <v>1.32</v>
@@ -10378,7 +10381,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10459,7 +10462,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ47">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -10584,7 +10587,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -10662,7 +10665,7 @@
         <v>0.57</v>
       </c>
       <c r="AP48">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ48">
         <v>0.8</v>
@@ -10871,7 +10874,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ49">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR49">
         <v>1.28</v>
@@ -11074,7 +11077,7 @@
         <v>1.13</v>
       </c>
       <c r="AP50">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ50">
         <v>1.2</v>
@@ -11280,7 +11283,7 @@
         <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ51">
         <v>0.78</v>
@@ -11408,7 +11411,7 @@
         <v>120</v>
       </c>
       <c r="P52" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -11692,7 +11695,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -11820,7 +11823,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -11901,7 +11904,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR54">
         <v>1.4</v>
@@ -12801,6 +12804,418 @@
       </c>
       <c r="BP58">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:68">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>7793146</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="2">
+        <v>45739.66666666666</v>
+      </c>
+      <c r="F59">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
+        <v>72</v>
+      </c>
+      <c r="H59" t="s">
+        <v>75</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>2</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>1</v>
+      </c>
+      <c r="N59">
+        <v>2</v>
+      </c>
+      <c r="O59" t="s">
+        <v>123</v>
+      </c>
+      <c r="P59" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q59">
+        <v>4.96</v>
+      </c>
+      <c r="R59">
+        <v>2.02</v>
+      </c>
+      <c r="S59">
+        <v>2.65</v>
+      </c>
+      <c r="T59">
+        <v>1.51</v>
+      </c>
+      <c r="U59">
+        <v>2.47</v>
+      </c>
+      <c r="V59">
+        <v>3.48</v>
+      </c>
+      <c r="W59">
+        <v>1.26</v>
+      </c>
+      <c r="X59">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y59">
+        <v>1</v>
+      </c>
+      <c r="Z59">
+        <v>3.8</v>
+      </c>
+      <c r="AA59">
+        <v>3</v>
+      </c>
+      <c r="AB59">
+        <v>2.05</v>
+      </c>
+      <c r="AC59">
+        <v>1.07</v>
+      </c>
+      <c r="AD59">
+        <v>7</v>
+      </c>
+      <c r="AE59">
+        <v>1.46</v>
+      </c>
+      <c r="AF59">
+        <v>2.63</v>
+      </c>
+      <c r="AG59">
+        <v>2.25</v>
+      </c>
+      <c r="AH59">
+        <v>1.53</v>
+      </c>
+      <c r="AI59">
+        <v>2.1</v>
+      </c>
+      <c r="AJ59">
+        <v>1.73</v>
+      </c>
+      <c r="AK59">
+        <v>1.75</v>
+      </c>
+      <c r="AL59">
+        <v>1.32</v>
+      </c>
+      <c r="AM59">
+        <v>1.21</v>
+      </c>
+      <c r="AN59">
+        <v>0.89</v>
+      </c>
+      <c r="AO59">
+        <v>1.56</v>
+      </c>
+      <c r="AP59">
+        <v>0.9</v>
+      </c>
+      <c r="AQ59">
+        <v>1.5</v>
+      </c>
+      <c r="AR59">
+        <v>1.21</v>
+      </c>
+      <c r="AS59">
+        <v>1.49</v>
+      </c>
+      <c r="AT59">
+        <v>2.7</v>
+      </c>
+      <c r="AU59">
+        <v>5</v>
+      </c>
+      <c r="AV59">
+        <v>3</v>
+      </c>
+      <c r="AW59">
+        <v>7</v>
+      </c>
+      <c r="AX59">
+        <v>6</v>
+      </c>
+      <c r="AY59">
+        <v>12</v>
+      </c>
+      <c r="AZ59">
+        <v>9</v>
+      </c>
+      <c r="BA59">
+        <v>4</v>
+      </c>
+      <c r="BB59">
+        <v>3</v>
+      </c>
+      <c r="BC59">
+        <v>7</v>
+      </c>
+      <c r="BD59">
+        <v>2.8</v>
+      </c>
+      <c r="BE59">
+        <v>6.4</v>
+      </c>
+      <c r="BF59">
+        <v>1.52</v>
+      </c>
+      <c r="BG59">
+        <v>1.45</v>
+      </c>
+      <c r="BH59">
+        <v>2.48</v>
+      </c>
+      <c r="BI59">
+        <v>1.74</v>
+      </c>
+      <c r="BJ59">
+        <v>1.93</v>
+      </c>
+      <c r="BK59">
+        <v>2.2</v>
+      </c>
+      <c r="BL59">
+        <v>1.57</v>
+      </c>
+      <c r="BM59">
+        <v>2.85</v>
+      </c>
+      <c r="BN59">
+        <v>1.35</v>
+      </c>
+      <c r="BO59">
+        <v>3.8</v>
+      </c>
+      <c r="BP59">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:68">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>7793150</v>
+      </c>
+      <c r="C60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="2">
+        <v>45739.8125</v>
+      </c>
+      <c r="F60">
+        <v>10</v>
+      </c>
+      <c r="G60" t="s">
+        <v>71</v>
+      </c>
+      <c r="H60" t="s">
+        <v>79</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+      <c r="O60" t="s">
+        <v>84</v>
+      </c>
+      <c r="P60" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q60">
+        <v>3.5</v>
+      </c>
+      <c r="R60">
+        <v>1.83</v>
+      </c>
+      <c r="S60">
+        <v>3.4</v>
+      </c>
+      <c r="T60">
+        <v>1.55</v>
+      </c>
+      <c r="U60">
+        <v>2.47</v>
+      </c>
+      <c r="V60">
+        <v>3.48</v>
+      </c>
+      <c r="W60">
+        <v>1.24</v>
+      </c>
+      <c r="X60">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y60">
+        <v>1.02</v>
+      </c>
+      <c r="Z60">
+        <v>2.8</v>
+      </c>
+      <c r="AA60">
+        <v>2.88</v>
+      </c>
+      <c r="AB60">
+        <v>2.62</v>
+      </c>
+      <c r="AC60">
+        <v>1.07</v>
+      </c>
+      <c r="AD60">
+        <v>7</v>
+      </c>
+      <c r="AE60">
+        <v>1.48</v>
+      </c>
+      <c r="AF60">
+        <v>2.4</v>
+      </c>
+      <c r="AG60">
+        <v>2.5</v>
+      </c>
+      <c r="AH60">
+        <v>1.49</v>
+      </c>
+      <c r="AI60">
+        <v>2.05</v>
+      </c>
+      <c r="AJ60">
+        <v>1.75</v>
+      </c>
+      <c r="AK60">
+        <v>1.44</v>
+      </c>
+      <c r="AL60">
+        <v>1.34</v>
+      </c>
+      <c r="AM60">
+        <v>1.39</v>
+      </c>
+      <c r="AN60">
+        <v>1</v>
+      </c>
+      <c r="AO60">
+        <v>1.78</v>
+      </c>
+      <c r="AP60">
+        <v>0.9</v>
+      </c>
+      <c r="AQ60">
+        <v>1.9</v>
+      </c>
+      <c r="AR60">
+        <v>1.65</v>
+      </c>
+      <c r="AS60">
+        <v>1.14</v>
+      </c>
+      <c r="AT60">
+        <v>2.79</v>
+      </c>
+      <c r="AU60">
+        <v>3</v>
+      </c>
+      <c r="AV60">
+        <v>5</v>
+      </c>
+      <c r="AW60">
+        <v>8</v>
+      </c>
+      <c r="AX60">
+        <v>11</v>
+      </c>
+      <c r="AY60">
+        <v>11</v>
+      </c>
+      <c r="AZ60">
+        <v>16</v>
+      </c>
+      <c r="BA60">
+        <v>5</v>
+      </c>
+      <c r="BB60">
+        <v>4</v>
+      </c>
+      <c r="BC60">
+        <v>9</v>
+      </c>
+      <c r="BD60">
+        <v>2.08</v>
+      </c>
+      <c r="BE60">
+        <v>6.1</v>
+      </c>
+      <c r="BF60">
+        <v>1.94</v>
+      </c>
+      <c r="BG60">
+        <v>1.58</v>
+      </c>
+      <c r="BH60">
+        <v>2.18</v>
+      </c>
+      <c r="BI60">
+        <v>1.97</v>
+      </c>
+      <c r="BJ60">
+        <v>1.7</v>
+      </c>
+      <c r="BK60">
+        <v>2.55</v>
+      </c>
+      <c r="BL60">
+        <v>1.43</v>
+      </c>
+      <c r="BM60">
+        <v>3.4</v>
+      </c>
+      <c r="BN60">
+        <v>1.25</v>
+      </c>
+      <c r="BO60">
+        <v>4.6</v>
+      </c>
+      <c r="BP60">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="161">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>['3']</t>
+  </si>
+  <si>
+    <t>['46']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -855,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP60"/>
+  <dimension ref="A1:BP61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1111,7 +1114,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1192,7 +1195,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1317,7 +1320,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1398,7 +1401,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ3">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1729,7 +1732,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1935,7 +1938,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2141,7 +2144,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2347,7 +2350,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2425,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>1.2</v>
@@ -2553,7 +2556,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2759,7 +2762,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2965,7 +2968,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3377,7 +3380,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3455,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13">
         <v>1.7</v>
@@ -4076,7 +4079,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4201,7 +4204,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4407,7 +4410,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4694,7 +4697,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ19">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -5231,7 +5234,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5437,7 +5440,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5721,7 +5724,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.2</v>
@@ -5927,7 +5930,7 @@
         <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25">
         <v>0.9</v>
@@ -6055,7 +6058,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6136,7 +6139,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ26">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>1.14</v>
@@ -6467,7 +6470,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6673,7 +6676,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6879,7 +6882,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7166,7 +7169,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR31">
         <v>1.72</v>
@@ -7291,7 +7294,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7703,7 +7706,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7781,7 +7784,7 @@
         <v>0.2</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ34">
         <v>0.8</v>
@@ -7909,7 +7912,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -7987,7 +7990,7 @@
         <v>2.6</v>
       </c>
       <c r="AP35">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ35">
         <v>2.6</v>
@@ -8115,7 +8118,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8527,7 +8530,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8608,7 +8611,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ38">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR38">
         <v>1.26</v>
@@ -8939,7 +8942,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9226,7 +9229,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ41">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>1.17</v>
@@ -9351,7 +9354,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9557,7 +9560,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9763,7 +9766,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9841,7 +9844,7 @@
         <v>1.14</v>
       </c>
       <c r="AP44">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>1.2</v>
@@ -9969,7 +9972,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10175,7 +10178,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10381,7 +10384,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10587,7 +10590,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -10871,7 +10874,7 @@
         <v>2.14</v>
       </c>
       <c r="AP49">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ49">
         <v>1.9</v>
@@ -11286,7 +11289,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ51">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.14</v>
@@ -11698,7 +11701,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR53">
         <v>1.53</v>
@@ -11823,7 +11826,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12029,7 +12032,7 @@
         <v>102</v>
       </c>
       <c r="P55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q55">
         <v>2.78</v>
@@ -12235,7 +12238,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q56">
         <v>2.63</v>
@@ -12441,7 +12444,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -12647,7 +12650,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q58">
         <v>2.69</v>
@@ -12853,7 +12856,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -13059,7 +13062,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13216,6 +13219,212 @@
       </c>
       <c r="BP60">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:68">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>7793151</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="2">
+        <v>45740.8125</v>
+      </c>
+      <c r="F61">
+        <v>10</v>
+      </c>
+      <c r="G61" t="s">
+        <v>76</v>
+      </c>
+      <c r="H61" t="s">
+        <v>80</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
+      </c>
+      <c r="O61" t="s">
+        <v>124</v>
+      </c>
+      <c r="P61" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q61">
+        <v>3.25</v>
+      </c>
+      <c r="R61">
+        <v>1.98</v>
+      </c>
+      <c r="S61">
+        <v>3.2</v>
+      </c>
+      <c r="T61">
+        <v>1.47</v>
+      </c>
+      <c r="U61">
+        <v>2.5</v>
+      </c>
+      <c r="V61">
+        <v>3.2</v>
+      </c>
+      <c r="W61">
+        <v>1.3</v>
+      </c>
+      <c r="X61">
+        <v>8.75</v>
+      </c>
+      <c r="Y61">
+        <v>1.06</v>
+      </c>
+      <c r="Z61">
+        <v>2.78</v>
+      </c>
+      <c r="AA61">
+        <v>2.96</v>
+      </c>
+      <c r="AB61">
+        <v>2.69</v>
+      </c>
+      <c r="AC61">
+        <v>1.01</v>
+      </c>
+      <c r="AD61">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE61">
+        <v>1.33</v>
+      </c>
+      <c r="AF61">
+        <v>2.81</v>
+      </c>
+      <c r="AG61">
+        <v>2.1</v>
+      </c>
+      <c r="AH61">
+        <v>1.6</v>
+      </c>
+      <c r="AI61">
+        <v>1.93</v>
+      </c>
+      <c r="AJ61">
+        <v>1.75</v>
+      </c>
+      <c r="AK61">
+        <v>1.46</v>
+      </c>
+      <c r="AL61">
+        <v>1.33</v>
+      </c>
+      <c r="AM61">
+        <v>1.46</v>
+      </c>
+      <c r="AN61">
+        <v>0.78</v>
+      </c>
+      <c r="AO61">
+        <v>1.33</v>
+      </c>
+      <c r="AP61">
+        <v>1</v>
+      </c>
+      <c r="AQ61">
+        <v>1.2</v>
+      </c>
+      <c r="AR61">
+        <v>1.44</v>
+      </c>
+      <c r="AS61">
+        <v>1.17</v>
+      </c>
+      <c r="AT61">
+        <v>2.61</v>
+      </c>
+      <c r="AU61">
+        <v>3</v>
+      </c>
+      <c r="AV61">
+        <v>4</v>
+      </c>
+      <c r="AW61">
+        <v>0</v>
+      </c>
+      <c r="AX61">
+        <v>2</v>
+      </c>
+      <c r="AY61">
+        <v>3</v>
+      </c>
+      <c r="AZ61">
+        <v>6</v>
+      </c>
+      <c r="BA61">
+        <v>2</v>
+      </c>
+      <c r="BB61">
+        <v>3</v>
+      </c>
+      <c r="BC61">
+        <v>5</v>
+      </c>
+      <c r="BD61">
+        <v>2.05</v>
+      </c>
+      <c r="BE61">
+        <v>6.1</v>
+      </c>
+      <c r="BF61">
+        <v>1.98</v>
+      </c>
+      <c r="BG61">
+        <v>1.5</v>
+      </c>
+      <c r="BH61">
+        <v>2.33</v>
+      </c>
+      <c r="BI61">
+        <v>1.85</v>
+      </c>
+      <c r="BJ61">
+        <v>1.82</v>
+      </c>
+      <c r="BK61">
+        <v>2.38</v>
+      </c>
+      <c r="BL61">
+        <v>1.49</v>
+      </c>
+      <c r="BM61">
+        <v>3.15</v>
+      </c>
+      <c r="BN61">
+        <v>1.29</v>
+      </c>
+      <c r="BO61">
+        <v>4.3</v>
+      </c>
+      <c r="BP61">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="167">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -394,6 +394,15 @@
     <t>['45+4']</t>
   </si>
   <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['19', '38']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -503,6 +512,9 @@
   </si>
   <si>
     <t>['1', '10', '90+2']</t>
+  </si>
+  <si>
+    <t>['18', '61']</t>
   </si>
 </sst>
 </file>
@@ -864,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP62"/>
+  <dimension ref="A1:BP65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1120,7 +1132,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1201,7 +1213,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ2">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1326,7 +1338,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1404,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1610,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ4">
         <v>0.8</v>
@@ -1738,7 +1750,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1944,7 +1956,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2150,7 +2162,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2228,10 +2240,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ7">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2356,7 +2368,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2434,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ8">
         <v>1.36</v>
@@ -2562,7 +2574,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2643,7 +2655,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ9">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2768,7 +2780,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2846,10 +2858,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ10">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -2974,7 +2986,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3055,7 +3067,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ11">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3386,7 +3398,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3464,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ13">
         <v>1.7</v>
@@ -3673,7 +3685,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ14">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -3876,7 +3888,7 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ15">
         <v>0.8</v>
@@ -4085,7 +4097,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ16">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4210,7 +4222,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4288,7 +4300,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AQ17">
         <v>1.2</v>
@@ -4416,7 +4428,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4494,7 +4506,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ18">
         <v>1.73</v>
@@ -4703,7 +4715,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -5115,7 +5127,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5240,7 +5252,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5318,7 +5330,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ22">
         <v>1.7</v>
@@ -5446,7 +5458,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5527,7 +5539,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ23">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR23">
         <v>1.04</v>
@@ -5730,7 +5742,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ24">
         <v>1.2</v>
@@ -5936,10 +5948,10 @@
         <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -6064,7 +6076,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6142,10 +6154,10 @@
         <v>1.25</v>
       </c>
       <c r="AP26">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR26">
         <v>1.14</v>
@@ -6351,7 +6363,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR27">
         <v>1.17</v>
@@ -6476,7 +6488,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6682,7 +6694,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6760,7 +6772,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ29">
         <v>1.2</v>
@@ -6888,7 +6900,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7172,10 +7184,10 @@
         <v>1.25</v>
       </c>
       <c r="AP31">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AQ31">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR31">
         <v>1.72</v>
@@ -7300,7 +7312,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7584,10 +7596,10 @@
         <v>1.2</v>
       </c>
       <c r="AP33">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ33">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR33">
         <v>1.83</v>
@@ -7712,7 +7724,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7790,7 +7802,7 @@
         <v>0.2</v>
       </c>
       <c r="AP34">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ34">
         <v>0.8</v>
@@ -7918,7 +7930,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -7996,10 +8008,10 @@
         <v>2.6</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ35">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR35">
         <v>1.46</v>
@@ -8124,7 +8136,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8205,7 +8217,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ36">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR36">
         <v>1.8</v>
@@ -8536,7 +8548,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8617,7 +8629,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR38">
         <v>1.26</v>
@@ -8820,10 +8832,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AQ39">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR39">
         <v>1.59</v>
@@ -8948,7 +8960,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9235,7 +9247,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR41">
         <v>1.17</v>
@@ -9360,7 +9372,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9438,7 +9450,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ42">
         <v>1.36</v>
@@ -9566,7 +9578,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9644,7 +9656,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ43">
         <v>1.73</v>
@@ -9772,7 +9784,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9850,7 +9862,7 @@
         <v>1.14</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ44">
         <v>1.2</v>
@@ -9978,7 +9990,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10059,7 +10071,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ45">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR45">
         <v>1.43</v>
@@ -10184,7 +10196,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10265,7 +10277,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ46">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR46">
         <v>1.32</v>
@@ -10390,7 +10402,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10471,7 +10483,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ47">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -10596,7 +10608,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -10674,7 +10686,7 @@
         <v>0.57</v>
       </c>
       <c r="AP48">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ48">
         <v>0.8</v>
@@ -10880,7 +10892,7 @@
         <v>2.14</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49">
         <v>1.73</v>
@@ -11086,7 +11098,7 @@
         <v>1.13</v>
       </c>
       <c r="AP50">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ50">
         <v>1.2</v>
@@ -11295,7 +11307,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR51">
         <v>1.14</v>
@@ -11498,7 +11510,7 @@
         <v>2.13</v>
       </c>
       <c r="AP52">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AQ52">
         <v>1.7</v>
@@ -11704,10 +11716,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ53">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR53">
         <v>1.53</v>
@@ -11832,7 +11844,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -11913,7 +11925,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ54">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR54">
         <v>1.4</v>
@@ -12038,7 +12050,7 @@
         <v>102</v>
       </c>
       <c r="P55" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q55">
         <v>2.78</v>
@@ -12244,7 +12256,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q56">
         <v>2.63</v>
@@ -12450,7 +12462,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -12531,7 +12543,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ57">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR57">
         <v>1.3</v>
@@ -12656,7 +12668,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q58">
         <v>2.69</v>
@@ -12862,7 +12874,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -12940,10 +12952,10 @@
         <v>1.56</v>
       </c>
       <c r="AP59">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR59">
         <v>1.21</v>
@@ -13068,7 +13080,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13146,7 +13158,7 @@
         <v>1.78</v>
       </c>
       <c r="AP60">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ60">
         <v>1.73</v>
@@ -13352,10 +13364,10 @@
         <v>1.33</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ61">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR61">
         <v>1.44</v>
@@ -13480,7 +13492,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -13637,6 +13649,624 @@
       </c>
       <c r="BP62">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:68">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>7793157</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="2">
+        <v>45744.76041666666</v>
+      </c>
+      <c r="F63">
+        <v>11</v>
+      </c>
+      <c r="G63" t="s">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s">
+        <v>72</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+      <c r="N63">
+        <v>2</v>
+      </c>
+      <c r="O63" t="s">
+        <v>126</v>
+      </c>
+      <c r="P63" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q63">
+        <v>2.25</v>
+      </c>
+      <c r="R63">
+        <v>2</v>
+      </c>
+      <c r="S63">
+        <v>6</v>
+      </c>
+      <c r="T63">
+        <v>1.44</v>
+      </c>
+      <c r="U63">
+        <v>2.67</v>
+      </c>
+      <c r="V63">
+        <v>3.26</v>
+      </c>
+      <c r="W63">
+        <v>1.31</v>
+      </c>
+      <c r="X63">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y63">
+        <v>1.02</v>
+      </c>
+      <c r="Z63">
+        <v>1.6</v>
+      </c>
+      <c r="AA63">
+        <v>3.72</v>
+      </c>
+      <c r="AB63">
+        <v>5.6</v>
+      </c>
+      <c r="AC63">
+        <v>1.05</v>
+      </c>
+      <c r="AD63">
+        <v>8</v>
+      </c>
+      <c r="AE63">
+        <v>1.36</v>
+      </c>
+      <c r="AF63">
+        <v>2.88</v>
+      </c>
+      <c r="AG63">
+        <v>2.1</v>
+      </c>
+      <c r="AH63">
+        <v>1.6</v>
+      </c>
+      <c r="AI63">
+        <v>2.2</v>
+      </c>
+      <c r="AJ63">
+        <v>1.65</v>
+      </c>
+      <c r="AK63">
+        <v>1.14</v>
+      </c>
+      <c r="AL63">
+        <v>1.27</v>
+      </c>
+      <c r="AM63">
+        <v>2.04</v>
+      </c>
+      <c r="AN63">
+        <v>2.6</v>
+      </c>
+      <c r="AO63">
+        <v>0.9</v>
+      </c>
+      <c r="AP63">
+        <v>2.45</v>
+      </c>
+      <c r="AQ63">
+        <v>0.91</v>
+      </c>
+      <c r="AR63">
+        <v>1.64</v>
+      </c>
+      <c r="AS63">
+        <v>1.23</v>
+      </c>
+      <c r="AT63">
+        <v>2.87</v>
+      </c>
+      <c r="AU63">
+        <v>5</v>
+      </c>
+      <c r="AV63">
+        <v>2</v>
+      </c>
+      <c r="AW63">
+        <v>6</v>
+      </c>
+      <c r="AX63">
+        <v>8</v>
+      </c>
+      <c r="AY63">
+        <v>11</v>
+      </c>
+      <c r="AZ63">
+        <v>10</v>
+      </c>
+      <c r="BA63">
+        <v>4</v>
+      </c>
+      <c r="BB63">
+        <v>1</v>
+      </c>
+      <c r="BC63">
+        <v>5</v>
+      </c>
+      <c r="BD63">
+        <v>1.62</v>
+      </c>
+      <c r="BE63">
+        <v>8</v>
+      </c>
+      <c r="BF63">
+        <v>2.75</v>
+      </c>
+      <c r="BG63">
+        <v>1.39</v>
+      </c>
+      <c r="BH63">
+        <v>2.77</v>
+      </c>
+      <c r="BI63">
+        <v>1.68</v>
+      </c>
+      <c r="BJ63">
+        <v>2.11</v>
+      </c>
+      <c r="BK63">
+        <v>2.11</v>
+      </c>
+      <c r="BL63">
+        <v>1.68</v>
+      </c>
+      <c r="BM63">
+        <v>2.7</v>
+      </c>
+      <c r="BN63">
+        <v>1.41</v>
+      </c>
+      <c r="BO63">
+        <v>3.65</v>
+      </c>
+      <c r="BP63">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:68">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>7793152</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45744.85416666666</v>
+      </c>
+      <c r="F64">
+        <v>11</v>
+      </c>
+      <c r="G64" t="s">
+        <v>75</v>
+      </c>
+      <c r="H64" t="s">
+        <v>76</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
+        <v>127</v>
+      </c>
+      <c r="P64" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q64">
+        <v>2.5</v>
+      </c>
+      <c r="R64">
+        <v>2.05</v>
+      </c>
+      <c r="S64">
+        <v>5</v>
+      </c>
+      <c r="T64">
+        <v>1.45</v>
+      </c>
+      <c r="U64">
+        <v>2.55</v>
+      </c>
+      <c r="V64">
+        <v>3.05</v>
+      </c>
+      <c r="W64">
+        <v>1.3</v>
+      </c>
+      <c r="X64">
+        <v>7.5</v>
+      </c>
+      <c r="Y64">
+        <v>1.05</v>
+      </c>
+      <c r="Z64">
+        <v>1.75</v>
+      </c>
+      <c r="AA64">
+        <v>3.74</v>
+      </c>
+      <c r="AB64">
+        <v>4.33</v>
+      </c>
+      <c r="AC64">
+        <v>1.04</v>
+      </c>
+      <c r="AD64">
+        <v>10.5</v>
+      </c>
+      <c r="AE64">
+        <v>1.33</v>
+      </c>
+      <c r="AF64">
+        <v>3.15</v>
+      </c>
+      <c r="AG64">
+        <v>1.92</v>
+      </c>
+      <c r="AH64">
+        <v>1.82</v>
+      </c>
+      <c r="AI64">
+        <v>2</v>
+      </c>
+      <c r="AJ64">
+        <v>1.73</v>
+      </c>
+      <c r="AK64">
+        <v>1.25</v>
+      </c>
+      <c r="AL64">
+        <v>1.29</v>
+      </c>
+      <c r="AM64">
+        <v>1.85</v>
+      </c>
+      <c r="AN64">
+        <v>1.5</v>
+      </c>
+      <c r="AO64">
+        <v>1</v>
+      </c>
+      <c r="AP64">
+        <v>1.64</v>
+      </c>
+      <c r="AQ64">
+        <v>0.91</v>
+      </c>
+      <c r="AR64">
+        <v>1.44</v>
+      </c>
+      <c r="AS64">
+        <v>1.37</v>
+      </c>
+      <c r="AT64">
+        <v>2.81</v>
+      </c>
+      <c r="AU64">
+        <v>3</v>
+      </c>
+      <c r="AV64">
+        <v>0</v>
+      </c>
+      <c r="AW64">
+        <v>4</v>
+      </c>
+      <c r="AX64">
+        <v>5</v>
+      </c>
+      <c r="AY64">
+        <v>7</v>
+      </c>
+      <c r="AZ64">
+        <v>5</v>
+      </c>
+      <c r="BA64">
+        <v>4</v>
+      </c>
+      <c r="BB64">
+        <v>5</v>
+      </c>
+      <c r="BC64">
+        <v>9</v>
+      </c>
+      <c r="BD64">
+        <v>1.49</v>
+      </c>
+      <c r="BE64">
+        <v>6.75</v>
+      </c>
+      <c r="BF64">
+        <v>2.9</v>
+      </c>
+      <c r="BG64">
+        <v>1.36</v>
+      </c>
+      <c r="BH64">
+        <v>2.8</v>
+      </c>
+      <c r="BI64">
+        <v>1.62</v>
+      </c>
+      <c r="BJ64">
+        <v>2.1</v>
+      </c>
+      <c r="BK64">
+        <v>2</v>
+      </c>
+      <c r="BL64">
+        <v>1.68</v>
+      </c>
+      <c r="BM64">
+        <v>2.55</v>
+      </c>
+      <c r="BN64">
+        <v>1.42</v>
+      </c>
+      <c r="BO64">
+        <v>3.4</v>
+      </c>
+      <c r="BP64">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:68">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>7793153</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="2">
+        <v>45745.76041666666</v>
+      </c>
+      <c r="F65">
+        <v>11</v>
+      </c>
+      <c r="G65" t="s">
+        <v>80</v>
+      </c>
+      <c r="H65" t="s">
+        <v>71</v>
+      </c>
+      <c r="I65">
+        <v>2</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>3</v>
+      </c>
+      <c r="L65">
+        <v>2</v>
+      </c>
+      <c r="M65">
+        <v>2</v>
+      </c>
+      <c r="N65">
+        <v>4</v>
+      </c>
+      <c r="O65" t="s">
+        <v>128</v>
+      </c>
+      <c r="P65" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q65">
+        <v>2.95</v>
+      </c>
+      <c r="R65">
+        <v>2.07</v>
+      </c>
+      <c r="S65">
+        <v>3.55</v>
+      </c>
+      <c r="T65">
+        <v>1.46</v>
+      </c>
+      <c r="U65">
+        <v>2.6</v>
+      </c>
+      <c r="V65">
+        <v>3.15</v>
+      </c>
+      <c r="W65">
+        <v>1.3</v>
+      </c>
+      <c r="X65">
+        <v>7.5</v>
+      </c>
+      <c r="Y65">
+        <v>1.05</v>
+      </c>
+      <c r="Z65">
+        <v>2.45</v>
+      </c>
+      <c r="AA65">
+        <v>3.09</v>
+      </c>
+      <c r="AB65">
+        <v>2.95</v>
+      </c>
+      <c r="AC65">
+        <v>1.06</v>
+      </c>
+      <c r="AD65">
+        <v>7.5</v>
+      </c>
+      <c r="AE65">
+        <v>1.36</v>
+      </c>
+      <c r="AF65">
+        <v>2.88</v>
+      </c>
+      <c r="AG65">
+        <v>2.25</v>
+      </c>
+      <c r="AH65">
+        <v>1.53</v>
+      </c>
+      <c r="AI65">
+        <v>1.91</v>
+      </c>
+      <c r="AJ65">
+        <v>1.79</v>
+      </c>
+      <c r="AK65">
+        <v>1.37</v>
+      </c>
+      <c r="AL65">
+        <v>1.33</v>
+      </c>
+      <c r="AM65">
+        <v>1.58</v>
+      </c>
+      <c r="AN65">
+        <v>1.2</v>
+      </c>
+      <c r="AO65">
+        <v>0.9</v>
+      </c>
+      <c r="AP65">
+        <v>1.18</v>
+      </c>
+      <c r="AQ65">
+        <v>0.91</v>
+      </c>
+      <c r="AR65">
+        <v>1.17</v>
+      </c>
+      <c r="AS65">
+        <v>1.61</v>
+      </c>
+      <c r="AT65">
+        <v>2.78</v>
+      </c>
+      <c r="AU65">
+        <v>6</v>
+      </c>
+      <c r="AV65">
+        <v>4</v>
+      </c>
+      <c r="AW65">
+        <v>10</v>
+      </c>
+      <c r="AX65">
+        <v>2</v>
+      </c>
+      <c r="AY65">
+        <v>16</v>
+      </c>
+      <c r="AZ65">
+        <v>6</v>
+      </c>
+      <c r="BA65">
+        <v>4</v>
+      </c>
+      <c r="BB65">
+        <v>3</v>
+      </c>
+      <c r="BC65">
+        <v>7</v>
+      </c>
+      <c r="BD65">
+        <v>1.78</v>
+      </c>
+      <c r="BE65">
+        <v>6.1</v>
+      </c>
+      <c r="BF65">
+        <v>2.3</v>
+      </c>
+      <c r="BG65">
+        <v>1.52</v>
+      </c>
+      <c r="BH65">
+        <v>2.28</v>
+      </c>
+      <c r="BI65">
+        <v>1.88</v>
+      </c>
+      <c r="BJ65">
+        <v>1.78</v>
+      </c>
+      <c r="BK65">
+        <v>2.4</v>
+      </c>
+      <c r="BL65">
+        <v>1.47</v>
+      </c>
+      <c r="BM65">
+        <v>3.2</v>
+      </c>
+      <c r="BN65">
+        <v>1.28</v>
+      </c>
+      <c r="BO65">
+        <v>4.35</v>
+      </c>
+      <c r="BP65">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="168">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>['19', '38']</t>
+  </si>
+  <si>
+    <t>['49']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -876,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP65"/>
+  <dimension ref="A1:BP66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1132,7 +1135,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1338,7 +1341,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1750,7 +1753,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1831,7 +1834,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1956,7 +1959,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2034,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ6">
         <v>1.73</v>
@@ -2162,7 +2165,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2368,7 +2371,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2574,7 +2577,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2652,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ9">
         <v>0.91</v>
@@ -2780,7 +2783,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2986,7 +2989,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3398,7 +3401,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3479,7 +3482,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ13">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -4222,7 +4225,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4303,7 +4306,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ17">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4428,7 +4431,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4712,7 +4715,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ19">
         <v>0.91</v>
@@ -4918,7 +4921,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20">
         <v>0.8</v>
@@ -5252,7 +5255,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5333,7 +5336,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ22">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5458,7 +5461,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -6076,7 +6079,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6488,7 +6491,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6694,7 +6697,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6775,7 +6778,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -6900,7 +6903,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6978,7 +6981,7 @@
         <v>1.75</v>
       </c>
       <c r="AP30">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ30">
         <v>1.36</v>
@@ -7312,7 +7315,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7393,7 +7396,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ32">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR32">
         <v>1.08</v>
@@ -7724,7 +7727,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7930,7 +7933,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8136,7 +8139,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8214,7 +8217,7 @@
         <v>1.6</v>
       </c>
       <c r="AP36">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ36">
         <v>1.64</v>
@@ -8548,7 +8551,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8626,7 +8629,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ38">
         <v>1.18</v>
@@ -8960,7 +8963,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9041,7 +9044,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ40">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -9372,7 +9375,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9578,7 +9581,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9784,7 +9787,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9865,7 +9868,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ44">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -9990,7 +9993,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10196,7 +10199,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10402,7 +10405,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10480,7 +10483,7 @@
         <v>1.14</v>
       </c>
       <c r="AP47">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ47">
         <v>0.91</v>
@@ -10608,7 +10611,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11513,7 +11516,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ52">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR52">
         <v>1.57</v>
@@ -11844,7 +11847,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -11922,7 +11925,7 @@
         <v>0.75</v>
       </c>
       <c r="AP54">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ54">
         <v>0.91</v>
@@ -12050,7 +12053,7 @@
         <v>102</v>
       </c>
       <c r="P55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q55">
         <v>2.78</v>
@@ -12256,7 +12259,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q56">
         <v>2.63</v>
@@ -12337,7 +12340,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ56">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR56">
         <v>1.42</v>
@@ -12462,7 +12465,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -12668,7 +12671,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q58">
         <v>2.69</v>
@@ -12746,7 +12749,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP58">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ58">
         <v>0.8</v>
@@ -12874,7 +12877,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -13080,7 +13083,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13492,7 +13495,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -14110,7 +14113,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14267,6 +14270,212 @@
       </c>
       <c r="BP65">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:68">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7793155</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45745.85416666666</v>
+      </c>
+      <c r="F66">
+        <v>11</v>
+      </c>
+      <c r="G66" t="s">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s">
+        <v>74</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+      <c r="N66">
+        <v>2</v>
+      </c>
+      <c r="O66" t="s">
+        <v>129</v>
+      </c>
+      <c r="P66" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q66">
+        <v>5</v>
+      </c>
+      <c r="R66">
+        <v>2.2</v>
+      </c>
+      <c r="S66">
+        <v>2.38</v>
+      </c>
+      <c r="T66">
+        <v>1.4</v>
+      </c>
+      <c r="U66">
+        <v>2.75</v>
+      </c>
+      <c r="V66">
+        <v>3</v>
+      </c>
+      <c r="W66">
+        <v>1.36</v>
+      </c>
+      <c r="X66">
+        <v>8</v>
+      </c>
+      <c r="Y66">
+        <v>1.08</v>
+      </c>
+      <c r="Z66">
+        <v>4.5</v>
+      </c>
+      <c r="AA66">
+        <v>3.7</v>
+      </c>
+      <c r="AB66">
+        <v>1.73</v>
+      </c>
+      <c r="AC66">
+        <v>1.01</v>
+      </c>
+      <c r="AD66">
+        <v>9.15</v>
+      </c>
+      <c r="AE66">
+        <v>1.3</v>
+      </c>
+      <c r="AF66">
+        <v>3.37</v>
+      </c>
+      <c r="AG66">
+        <v>1.93</v>
+      </c>
+      <c r="AH66">
+        <v>1.77</v>
+      </c>
+      <c r="AI66">
+        <v>1.83</v>
+      </c>
+      <c r="AJ66">
+        <v>1.83</v>
+      </c>
+      <c r="AK66">
+        <v>2.05</v>
+      </c>
+      <c r="AL66">
+        <v>1.26</v>
+      </c>
+      <c r="AM66">
+        <v>1.2</v>
+      </c>
+      <c r="AN66">
+        <v>1.2</v>
+      </c>
+      <c r="AO66">
+        <v>1.7</v>
+      </c>
+      <c r="AP66">
+        <v>1.18</v>
+      </c>
+      <c r="AQ66">
+        <v>1.64</v>
+      </c>
+      <c r="AR66">
+        <v>1.47</v>
+      </c>
+      <c r="AS66">
+        <v>1.65</v>
+      </c>
+      <c r="AT66">
+        <v>3.12</v>
+      </c>
+      <c r="AU66">
+        <v>3</v>
+      </c>
+      <c r="AV66">
+        <v>6</v>
+      </c>
+      <c r="AW66">
+        <v>6</v>
+      </c>
+      <c r="AX66">
+        <v>3</v>
+      </c>
+      <c r="AY66">
+        <v>9</v>
+      </c>
+      <c r="AZ66">
+        <v>9</v>
+      </c>
+      <c r="BA66">
+        <v>0</v>
+      </c>
+      <c r="BB66">
+        <v>10</v>
+      </c>
+      <c r="BC66">
+        <v>10</v>
+      </c>
+      <c r="BD66">
+        <v>2.88</v>
+      </c>
+      <c r="BE66">
+        <v>6.35</v>
+      </c>
+      <c r="BF66">
+        <v>1.63</v>
+      </c>
+      <c r="BG66">
+        <v>1.36</v>
+      </c>
+      <c r="BH66">
+        <v>2.7</v>
+      </c>
+      <c r="BI66">
+        <v>1.7</v>
+      </c>
+      <c r="BJ66">
+        <v>2.05</v>
+      </c>
+      <c r="BK66">
+        <v>2.12</v>
+      </c>
+      <c r="BL66">
+        <v>1.58</v>
+      </c>
+      <c r="BM66">
+        <v>2.83</v>
+      </c>
+      <c r="BN66">
+        <v>1.33</v>
+      </c>
+      <c r="BO66">
+        <v>3.7</v>
+      </c>
+      <c r="BP66">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="169">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>['49']</t>
+  </si>
+  <si>
+    <t>['37']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -879,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP66"/>
+  <dimension ref="A1:BP67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1135,7 +1138,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1341,7 +1344,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1628,7 +1631,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1753,7 +1756,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1831,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ5">
         <v>1.18</v>
@@ -1959,7 +1962,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2165,7 +2168,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2371,7 +2374,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2577,7 +2580,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2783,7 +2786,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2989,7 +2992,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3067,7 +3070,7 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ11">
         <v>2.45</v>
@@ -3276,7 +3279,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3401,7 +3404,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3894,7 +3897,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ15">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -4097,7 +4100,7 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ16">
         <v>1.18</v>
@@ -4225,7 +4228,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4431,7 +4434,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4924,7 +4927,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ20">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>1.3</v>
@@ -5255,7 +5258,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5461,7 +5464,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5748,7 +5751,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ24">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -6079,7 +6082,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6363,7 +6366,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ27">
         <v>0.91</v>
@@ -6491,7 +6494,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6569,7 +6572,7 @@
         <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
         <v>1.73</v>
@@ -6697,7 +6700,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6903,7 +6906,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7315,7 +7318,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7727,7 +7730,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7808,7 +7811,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ34">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.34</v>
@@ -7933,7 +7936,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8139,7 +8142,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8426,7 +8429,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ37">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR37">
         <v>1.52</v>
@@ -8551,7 +8554,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8963,7 +8966,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9041,7 +9044,7 @@
         <v>2.17</v>
       </c>
       <c r="AP40">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ40">
         <v>1.64</v>
@@ -9247,7 +9250,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>0.91</v>
@@ -9375,7 +9378,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9581,7 +9584,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9787,7 +9790,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9993,7 +9996,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10199,7 +10202,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10277,7 +10280,7 @@
         <v>1.14</v>
       </c>
       <c r="AP46">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ46">
         <v>1.64</v>
@@ -10405,7 +10408,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10611,7 +10614,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -10692,7 +10695,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ48">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.65</v>
@@ -11104,7 +11107,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ50">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR50">
         <v>1.1</v>
@@ -11847,7 +11850,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12053,7 +12056,7 @@
         <v>102</v>
       </c>
       <c r="P55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q55">
         <v>2.78</v>
@@ -12131,7 +12134,7 @@
         <v>1.25</v>
       </c>
       <c r="AP55">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
         <v>1.36</v>
@@ -12259,7 +12262,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q56">
         <v>2.63</v>
@@ -12465,7 +12468,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -12543,7 +12546,7 @@
         <v>2.56</v>
       </c>
       <c r="AP57">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ57">
         <v>2.45</v>
@@ -12671,7 +12674,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q58">
         <v>2.69</v>
@@ -12752,7 +12755,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ58">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>1.71</v>
@@ -12877,7 +12880,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -13083,7 +13086,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13495,7 +13498,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -14113,7 +14116,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14476,6 +14479,212 @@
       </c>
       <c r="BP66">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:68">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>7793156</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45746.77083333334</v>
+      </c>
+      <c r="F67">
+        <v>11</v>
+      </c>
+      <c r="G67" t="s">
+        <v>78</v>
+      </c>
+      <c r="H67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>130</v>
+      </c>
+      <c r="P67" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q67">
+        <v>2.78</v>
+      </c>
+      <c r="R67">
+        <v>1.88</v>
+      </c>
+      <c r="S67">
+        <v>4.45</v>
+      </c>
+      <c r="T67">
+        <v>1.53</v>
+      </c>
+      <c r="U67">
+        <v>2.34</v>
+      </c>
+      <c r="V67">
+        <v>3.48</v>
+      </c>
+      <c r="W67">
+        <v>1.26</v>
+      </c>
+      <c r="X67">
+        <v>9.1</v>
+      </c>
+      <c r="Y67">
+        <v>1</v>
+      </c>
+      <c r="Z67">
+        <v>2.12</v>
+      </c>
+      <c r="AA67">
+        <v>3.09</v>
+      </c>
+      <c r="AB67">
+        <v>3.64</v>
+      </c>
+      <c r="AC67">
+        <v>1.08</v>
+      </c>
+      <c r="AD67">
+        <v>6.5</v>
+      </c>
+      <c r="AE67">
+        <v>1.44</v>
+      </c>
+      <c r="AF67">
+        <v>2.6</v>
+      </c>
+      <c r="AG67">
+        <v>2.3</v>
+      </c>
+      <c r="AH67">
+        <v>1.5</v>
+      </c>
+      <c r="AI67">
+        <v>2.05</v>
+      </c>
+      <c r="AJ67">
+        <v>1.75</v>
+      </c>
+      <c r="AK67">
+        <v>1.25</v>
+      </c>
+      <c r="AL67">
+        <v>1.33</v>
+      </c>
+      <c r="AM67">
+        <v>1.66</v>
+      </c>
+      <c r="AN67">
+        <v>0.8</v>
+      </c>
+      <c r="AO67">
+        <v>1.2</v>
+      </c>
+      <c r="AP67">
+        <v>1</v>
+      </c>
+      <c r="AQ67">
+        <v>1.09</v>
+      </c>
+      <c r="AR67">
+        <v>1.43</v>
+      </c>
+      <c r="AS67">
+        <v>1.26</v>
+      </c>
+      <c r="AT67">
+        <v>2.69</v>
+      </c>
+      <c r="AU67">
+        <v>7</v>
+      </c>
+      <c r="AV67">
+        <v>5</v>
+      </c>
+      <c r="AW67">
+        <v>7</v>
+      </c>
+      <c r="AX67">
+        <v>11</v>
+      </c>
+      <c r="AY67">
+        <v>14</v>
+      </c>
+      <c r="AZ67">
+        <v>16</v>
+      </c>
+      <c r="BA67">
+        <v>2</v>
+      </c>
+      <c r="BB67">
+        <v>3</v>
+      </c>
+      <c r="BC67">
+        <v>5</v>
+      </c>
+      <c r="BD67">
+        <v>1.67</v>
+      </c>
+      <c r="BE67">
+        <v>7.5</v>
+      </c>
+      <c r="BF67">
+        <v>2.6</v>
+      </c>
+      <c r="BG67">
+        <v>1.47</v>
+      </c>
+      <c r="BH67">
+        <v>2.5</v>
+      </c>
+      <c r="BI67">
+        <v>1.82</v>
+      </c>
+      <c r="BJ67">
+        <v>1.93</v>
+      </c>
+      <c r="BK67">
+        <v>2.34</v>
+      </c>
+      <c r="BL67">
+        <v>1.56</v>
+      </c>
+      <c r="BM67">
+        <v>3.02</v>
+      </c>
+      <c r="BN67">
+        <v>1.33</v>
+      </c>
+      <c r="BO67">
+        <v>4.2</v>
+      </c>
+      <c r="BP67">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="171">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -409,6 +409,9 @@
     <t>['37']</t>
   </si>
   <si>
+    <t>['40', '74', '90']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -521,6 +524,9 @@
   </si>
   <si>
     <t>['18', '61']</t>
+  </si>
+  <si>
+    <t>['57']</t>
   </si>
 </sst>
 </file>
@@ -882,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP67"/>
+  <dimension ref="A1:BP69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1138,7 +1144,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1216,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1344,7 +1350,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1756,7 +1762,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1834,10 +1840,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1962,7 +1968,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2168,7 +2174,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2374,7 +2380,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2455,7 +2461,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ8">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -2580,7 +2586,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2658,7 +2664,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9">
         <v>0.91</v>
@@ -2786,7 +2792,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2992,7 +2998,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3279,7 +3285,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3404,7 +3410,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3482,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ13">
         <v>1.64</v>
@@ -3688,7 +3694,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14">
         <v>0.91</v>
@@ -4100,10 +4106,10 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4228,7 +4234,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4309,7 +4315,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ17">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4434,7 +4440,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4924,7 +4930,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5130,7 +5136,7 @@
         <v>1.67</v>
       </c>
       <c r="AP21">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21">
         <v>1.64</v>
@@ -5258,7 +5264,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5464,7 +5470,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5751,7 +5757,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ24">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -5954,7 +5960,7 @@
         <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ25">
         <v>0.91</v>
@@ -6082,7 +6088,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6366,7 +6372,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>0.91</v>
@@ -6494,7 +6500,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6700,7 +6706,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6781,7 +6787,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -6906,7 +6912,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6987,7 +6993,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ30">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>1.83</v>
@@ -7193,7 +7199,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ31">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR31">
         <v>1.72</v>
@@ -7318,7 +7324,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7399,7 +7405,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ32">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR32">
         <v>1.08</v>
@@ -7730,7 +7736,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7808,7 +7814,7 @@
         <v>0.2</v>
       </c>
       <c r="AP34">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -7936,7 +7942,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8142,7 +8148,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8426,10 +8432,10 @@
         <v>1.4</v>
       </c>
       <c r="AP37">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>1.52</v>
@@ -8554,7 +8560,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8632,10 +8638,10 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR38">
         <v>1.26</v>
@@ -8966,7 +8972,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9044,7 +9050,7 @@
         <v>2.17</v>
       </c>
       <c r="AP40">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ40">
         <v>1.64</v>
@@ -9378,7 +9384,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9459,7 +9465,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ42">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR42">
         <v>1.17</v>
@@ -9584,7 +9590,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9790,7 +9796,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9871,7 +9877,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ44">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -9996,7 +10002,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10074,7 +10080,7 @@
         <v>2.71</v>
       </c>
       <c r="AP45">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45">
         <v>2.45</v>
@@ -10202,7 +10208,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10280,7 +10286,7 @@
         <v>1.14</v>
       </c>
       <c r="AP46">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ46">
         <v>1.64</v>
@@ -10408,7 +10414,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10614,7 +10620,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -10898,7 +10904,7 @@
         <v>2.14</v>
       </c>
       <c r="AP49">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ49">
         <v>1.73</v>
@@ -11107,7 +11113,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ50">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.1</v>
@@ -11725,7 +11731,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ53">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR53">
         <v>1.53</v>
@@ -11850,7 +11856,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -11928,7 +11934,7 @@
         <v>0.75</v>
       </c>
       <c r="AP54">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
         <v>0.91</v>
@@ -12056,7 +12062,7 @@
         <v>102</v>
       </c>
       <c r="P55" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q55">
         <v>2.78</v>
@@ -12137,7 +12143,7 @@
         <v>1</v>
       </c>
       <c r="AQ55">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR55">
         <v>1.34</v>
@@ -12262,7 +12268,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q56">
         <v>2.63</v>
@@ -12340,10 +12346,10 @@
         <v>1.22</v>
       </c>
       <c r="AP56">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
         <v>1.42</v>
@@ -12468,7 +12474,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -12546,7 +12552,7 @@
         <v>2.56</v>
       </c>
       <c r="AP57">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ57">
         <v>2.45</v>
@@ -12674,7 +12680,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q58">
         <v>2.69</v>
@@ -12880,7 +12886,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -13086,7 +13092,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13373,7 +13379,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ61">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR61">
         <v>1.44</v>
@@ -13498,7 +13504,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -13579,7 +13585,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ62">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR62">
         <v>1.2</v>
@@ -14116,7 +14122,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14194,7 +14200,7 @@
         <v>0.9</v>
       </c>
       <c r="AP65">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ65">
         <v>0.91</v>
@@ -14400,7 +14406,7 @@
         <v>1.7</v>
       </c>
       <c r="AP66">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ66">
         <v>1.64</v>
@@ -14609,7 +14615,7 @@
         <v>1</v>
       </c>
       <c r="AQ67">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>1.43</v>
@@ -14685,6 +14691,418 @@
       </c>
       <c r="BP67">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:68">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>7793160</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45751.76041666666</v>
+      </c>
+      <c r="F68">
+        <v>12</v>
+      </c>
+      <c r="G68" t="s">
+        <v>77</v>
+      </c>
+      <c r="H68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>3</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>4</v>
+      </c>
+      <c r="O68" t="s">
+        <v>131</v>
+      </c>
+      <c r="P68" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q68">
+        <v>3.4</v>
+      </c>
+      <c r="R68">
+        <v>2</v>
+      </c>
+      <c r="S68">
+        <v>3.4</v>
+      </c>
+      <c r="T68">
+        <v>1.5</v>
+      </c>
+      <c r="U68">
+        <v>2.5</v>
+      </c>
+      <c r="V68">
+        <v>3.4</v>
+      </c>
+      <c r="W68">
+        <v>1.3</v>
+      </c>
+      <c r="X68">
+        <v>10</v>
+      </c>
+      <c r="Y68">
+        <v>1.06</v>
+      </c>
+      <c r="Z68">
+        <v>2.59</v>
+      </c>
+      <c r="AA68">
+        <v>3.07</v>
+      </c>
+      <c r="AB68">
+        <v>2.79</v>
+      </c>
+      <c r="AC68">
+        <v>1.06</v>
+      </c>
+      <c r="AD68">
+        <v>8.5</v>
+      </c>
+      <c r="AE68">
+        <v>1.38</v>
+      </c>
+      <c r="AF68">
+        <v>3.01</v>
+      </c>
+      <c r="AG68">
+        <v>2.25</v>
+      </c>
+      <c r="AH68">
+        <v>1.53</v>
+      </c>
+      <c r="AI68">
+        <v>1.91</v>
+      </c>
+      <c r="AJ68">
+        <v>1.8</v>
+      </c>
+      <c r="AK68">
+        <v>1.38</v>
+      </c>
+      <c r="AL68">
+        <v>1.34</v>
+      </c>
+      <c r="AM68">
+        <v>1.53</v>
+      </c>
+      <c r="AN68">
+        <v>1.18</v>
+      </c>
+      <c r="AO68">
+        <v>1.09</v>
+      </c>
+      <c r="AP68">
+        <v>1.33</v>
+      </c>
+      <c r="AQ68">
+        <v>1</v>
+      </c>
+      <c r="AR68">
+        <v>1.43</v>
+      </c>
+      <c r="AS68">
+        <v>1.29</v>
+      </c>
+      <c r="AT68">
+        <v>2.72</v>
+      </c>
+      <c r="AU68">
+        <v>6</v>
+      </c>
+      <c r="AV68">
+        <v>3</v>
+      </c>
+      <c r="AW68">
+        <v>4</v>
+      </c>
+      <c r="AX68">
+        <v>5</v>
+      </c>
+      <c r="AY68">
+        <v>10</v>
+      </c>
+      <c r="AZ68">
+        <v>8</v>
+      </c>
+      <c r="BA68">
+        <v>2</v>
+      </c>
+      <c r="BB68">
+        <v>3</v>
+      </c>
+      <c r="BC68">
+        <v>5</v>
+      </c>
+      <c r="BD68">
+        <v>1.67</v>
+      </c>
+      <c r="BE68">
+        <v>6.25</v>
+      </c>
+      <c r="BF68">
+        <v>2.78</v>
+      </c>
+      <c r="BG68">
+        <v>1.35</v>
+      </c>
+      <c r="BH68">
+        <v>2.74</v>
+      </c>
+      <c r="BI68">
+        <v>1.7</v>
+      </c>
+      <c r="BJ68">
+        <v>2.05</v>
+      </c>
+      <c r="BK68">
+        <v>2.1</v>
+      </c>
+      <c r="BL68">
+        <v>1.59</v>
+      </c>
+      <c r="BM68">
+        <v>2.83</v>
+      </c>
+      <c r="BN68">
+        <v>1.33</v>
+      </c>
+      <c r="BO68">
+        <v>3.8</v>
+      </c>
+      <c r="BP68">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:68">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>7793162</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45751.85416666666</v>
+      </c>
+      <c r="F69">
+        <v>12</v>
+      </c>
+      <c r="G69" t="s">
+        <v>80</v>
+      </c>
+      <c r="H69" t="s">
+        <v>70</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69" t="s">
+        <v>84</v>
+      </c>
+      <c r="P69" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q69">
+        <v>3.2</v>
+      </c>
+      <c r="R69">
+        <v>1.9</v>
+      </c>
+      <c r="S69">
+        <v>3.5</v>
+      </c>
+      <c r="T69">
+        <v>1.51</v>
+      </c>
+      <c r="U69">
+        <v>2.35</v>
+      </c>
+      <c r="V69">
+        <v>3.3</v>
+      </c>
+      <c r="W69">
+        <v>1.28</v>
+      </c>
+      <c r="X69">
+        <v>9.25</v>
+      </c>
+      <c r="Y69">
+        <v>1.05</v>
+      </c>
+      <c r="Z69">
+        <v>2.63</v>
+      </c>
+      <c r="AA69">
+        <v>2.96</v>
+      </c>
+      <c r="AB69">
+        <v>2.85</v>
+      </c>
+      <c r="AC69">
+        <v>1.09</v>
+      </c>
+      <c r="AD69">
+        <v>6.5</v>
+      </c>
+      <c r="AE69">
+        <v>1.45</v>
+      </c>
+      <c r="AF69">
+        <v>2.6</v>
+      </c>
+      <c r="AG69">
+        <v>2.3</v>
+      </c>
+      <c r="AH69">
+        <v>1.5</v>
+      </c>
+      <c r="AI69">
+        <v>1.98</v>
+      </c>
+      <c r="AJ69">
+        <v>1.71</v>
+      </c>
+      <c r="AK69">
+        <v>1.4</v>
+      </c>
+      <c r="AL69">
+        <v>1.36</v>
+      </c>
+      <c r="AM69">
+        <v>1.47</v>
+      </c>
+      <c r="AN69">
+        <v>1.18</v>
+      </c>
+      <c r="AO69">
+        <v>1.36</v>
+      </c>
+      <c r="AP69">
+        <v>1.08</v>
+      </c>
+      <c r="AQ69">
+        <v>1.5</v>
+      </c>
+      <c r="AR69">
+        <v>1.22</v>
+      </c>
+      <c r="AS69">
+        <v>1.45</v>
+      </c>
+      <c r="AT69">
+        <v>2.67</v>
+      </c>
+      <c r="AU69">
+        <v>5</v>
+      </c>
+      <c r="AV69">
+        <v>4</v>
+      </c>
+      <c r="AW69">
+        <v>8</v>
+      </c>
+      <c r="AX69">
+        <v>9</v>
+      </c>
+      <c r="AY69">
+        <v>13</v>
+      </c>
+      <c r="AZ69">
+        <v>13</v>
+      </c>
+      <c r="BA69">
+        <v>10</v>
+      </c>
+      <c r="BB69">
+        <v>0</v>
+      </c>
+      <c r="BC69">
+        <v>10</v>
+      </c>
+      <c r="BD69">
+        <v>1.86</v>
+      </c>
+      <c r="BE69">
+        <v>6.1</v>
+      </c>
+      <c r="BF69">
+        <v>2.17</v>
+      </c>
+      <c r="BG69">
+        <v>1.46</v>
+      </c>
+      <c r="BH69">
+        <v>2.45</v>
+      </c>
+      <c r="BI69">
+        <v>1.79</v>
+      </c>
+      <c r="BJ69">
+        <v>1.88</v>
+      </c>
+      <c r="BK69">
+        <v>2.28</v>
+      </c>
+      <c r="BL69">
+        <v>1.53</v>
+      </c>
+      <c r="BM69">
+        <v>3</v>
+      </c>
+      <c r="BN69">
+        <v>1.32</v>
+      </c>
+      <c r="BO69">
+        <v>4</v>
+      </c>
+      <c r="BP69">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="171">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -888,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP69"/>
+  <dimension ref="A1:BP70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ3">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ8">
         <v>1.5</v>
@@ -2870,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ10">
         <v>1.64</v>
@@ -3697,7 +3697,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -4727,7 +4727,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ19">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -5342,7 +5342,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ22">
         <v>1.64</v>
@@ -5754,7 +5754,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6169,7 +6169,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ26">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR26">
         <v>1.14</v>
@@ -6375,7 +6375,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR27">
         <v>1.17</v>
@@ -7608,7 +7608,7 @@
         <v>1.2</v>
       </c>
       <c r="AP33">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ33">
         <v>0.91</v>
@@ -8020,7 +8020,7 @@
         <v>2.6</v>
       </c>
       <c r="AP35">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ35">
         <v>2.45</v>
@@ -8847,7 +8847,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ39">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR39">
         <v>1.59</v>
@@ -9259,7 +9259,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR41">
         <v>1.17</v>
@@ -9874,7 +9874,7 @@
         <v>1.14</v>
       </c>
       <c r="AP44">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ44">
         <v>1.33</v>
@@ -10698,7 +10698,7 @@
         <v>0.57</v>
       </c>
       <c r="AP48">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11319,7 +11319,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ51">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR51">
         <v>1.14</v>
@@ -11937,7 +11937,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR54">
         <v>1.4</v>
@@ -13170,7 +13170,7 @@
         <v>1.78</v>
       </c>
       <c r="AP60">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ60">
         <v>1.73</v>
@@ -13376,7 +13376,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ61">
         <v>1.08</v>
@@ -13997,7 +13997,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ64">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR64">
         <v>1.44</v>
@@ -14203,7 +14203,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ65">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR65">
         <v>1.17</v>
@@ -15103,6 +15103,212 @@
       </c>
       <c r="BP69">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:68">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>7793163</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45752.75</v>
+      </c>
+      <c r="F70">
+        <v>12</v>
+      </c>
+      <c r="G70" t="s">
+        <v>76</v>
+      </c>
+      <c r="H70" t="s">
+        <v>71</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>2</v>
+      </c>
+      <c r="O70" t="s">
+        <v>102</v>
+      </c>
+      <c r="P70" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q70">
+        <v>3.1</v>
+      </c>
+      <c r="R70">
+        <v>1.95</v>
+      </c>
+      <c r="S70">
+        <v>4</v>
+      </c>
+      <c r="T70">
+        <v>1.5</v>
+      </c>
+      <c r="U70">
+        <v>2.4</v>
+      </c>
+      <c r="V70">
+        <v>3.25</v>
+      </c>
+      <c r="W70">
+        <v>1.29</v>
+      </c>
+      <c r="X70">
+        <v>9.25</v>
+      </c>
+      <c r="Y70">
+        <v>1.05</v>
+      </c>
+      <c r="Z70">
+        <v>2.42</v>
+      </c>
+      <c r="AA70">
+        <v>2.97</v>
+      </c>
+      <c r="AB70">
+        <v>3.13</v>
+      </c>
+      <c r="AC70">
+        <v>1.06</v>
+      </c>
+      <c r="AD70">
+        <v>8.5</v>
+      </c>
+      <c r="AE70">
+        <v>1.43</v>
+      </c>
+      <c r="AF70">
+        <v>2.75</v>
+      </c>
+      <c r="AG70">
+        <v>2.25</v>
+      </c>
+      <c r="AH70">
+        <v>1.53</v>
+      </c>
+      <c r="AI70">
+        <v>2</v>
+      </c>
+      <c r="AJ70">
+        <v>1.71</v>
+      </c>
+      <c r="AK70">
+        <v>1.31</v>
+      </c>
+      <c r="AL70">
+        <v>1.35</v>
+      </c>
+      <c r="AM70">
+        <v>1.61</v>
+      </c>
+      <c r="AN70">
+        <v>0.91</v>
+      </c>
+      <c r="AO70">
+        <v>0.91</v>
+      </c>
+      <c r="AP70">
+        <v>0.92</v>
+      </c>
+      <c r="AQ70">
+        <v>0.92</v>
+      </c>
+      <c r="AR70">
+        <v>1.3</v>
+      </c>
+      <c r="AS70">
+        <v>1.54</v>
+      </c>
+      <c r="AT70">
+        <v>2.84</v>
+      </c>
+      <c r="AU70">
+        <v>5</v>
+      </c>
+      <c r="AV70">
+        <v>3</v>
+      </c>
+      <c r="AW70">
+        <v>4</v>
+      </c>
+      <c r="AX70">
+        <v>4</v>
+      </c>
+      <c r="AY70">
+        <v>9</v>
+      </c>
+      <c r="AZ70">
+        <v>7</v>
+      </c>
+      <c r="BA70">
+        <v>4</v>
+      </c>
+      <c r="BB70">
+        <v>3</v>
+      </c>
+      <c r="BC70">
+        <v>7</v>
+      </c>
+      <c r="BD70">
+        <v>1.88</v>
+      </c>
+      <c r="BE70">
+        <v>6.05</v>
+      </c>
+      <c r="BF70">
+        <v>2.38</v>
+      </c>
+      <c r="BG70">
+        <v>1.4</v>
+      </c>
+      <c r="BH70">
+        <v>2.56</v>
+      </c>
+      <c r="BI70">
+        <v>1.77</v>
+      </c>
+      <c r="BJ70">
+        <v>1.95</v>
+      </c>
+      <c r="BK70">
+        <v>2.24</v>
+      </c>
+      <c r="BL70">
+        <v>1.52</v>
+      </c>
+      <c r="BM70">
+        <v>3.05</v>
+      </c>
+      <c r="BN70">
+        <v>1.28</v>
+      </c>
+      <c r="BO70">
+        <v>4.35</v>
+      </c>
+      <c r="BP70">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="174">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -412,6 +412,12 @@
     <t>['40', '74', '90']</t>
   </si>
   <si>
+    <t>['45+10', '71']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -527,6 +533,9 @@
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['36']</t>
   </si>
 </sst>
 </file>
@@ -888,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP70"/>
+  <dimension ref="A1:BP73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1144,7 +1153,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1350,7 +1359,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1634,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1762,7 +1771,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1968,7 +1977,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2046,10 +2055,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2174,7 +2183,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2252,10 +2261,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2380,7 +2389,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2586,7 +2595,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2667,7 +2676,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ9">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2792,7 +2801,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -2873,7 +2882,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ10">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -2998,7 +3007,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3076,10 +3085,10 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ11">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3282,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="AP12">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3410,7 +3419,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3491,7 +3500,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ13">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -3900,10 +3909,10 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -4234,7 +4243,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4312,7 +4321,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17">
         <v>1.33</v>
@@ -4440,7 +4449,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4518,10 +4527,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ18">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR18">
         <v>1.16</v>
@@ -4724,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19">
         <v>0.92</v>
@@ -4933,7 +4942,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR20">
         <v>1.3</v>
@@ -5139,7 +5148,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ21">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5264,7 +5273,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5345,7 +5354,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ22">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5470,7 +5479,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5548,10 +5557,10 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ23">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR23">
         <v>1.04</v>
@@ -5963,7 +5972,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -6088,7 +6097,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6166,7 +6175,7 @@
         <v>1.25</v>
       </c>
       <c r="AP26">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ26">
         <v>0.92</v>
@@ -6500,7 +6509,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6578,10 +6587,10 @@
         <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR28">
         <v>1.14</v>
@@ -6706,7 +6715,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6784,7 +6793,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>1.33</v>
@@ -6912,7 +6921,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -6990,7 +6999,7 @@
         <v>1.75</v>
       </c>
       <c r="AP30">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30">
         <v>1.5</v>
@@ -7196,7 +7205,7 @@
         <v>1.25</v>
       </c>
       <c r="AP31">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ31">
         <v>1.08</v>
@@ -7324,7 +7333,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7402,7 +7411,7 @@
         <v>0.8</v>
       </c>
       <c r="AP32">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ32">
         <v>1.33</v>
@@ -7611,7 +7620,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ33">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR33">
         <v>1.83</v>
@@ -7736,7 +7745,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7817,7 +7826,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR34">
         <v>1.34</v>
@@ -7942,7 +7951,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8023,7 +8032,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ35">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR35">
         <v>1.46</v>
@@ -8148,7 +8157,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8226,10 +8235,10 @@
         <v>1.6</v>
       </c>
       <c r="AP36">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR36">
         <v>1.8</v>
@@ -8560,7 +8569,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8844,7 +8853,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ39">
         <v>0.92</v>
@@ -8972,7 +8981,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9053,7 +9062,7 @@
         <v>1</v>
       </c>
       <c r="AQ40">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -9256,7 +9265,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ41">
         <v>0.92</v>
@@ -9384,7 +9393,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9462,7 +9471,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ42">
         <v>1.5</v>
@@ -9590,7 +9599,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9668,10 +9677,10 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ43">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR43">
         <v>1.5</v>
@@ -9796,7 +9805,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -10002,7 +10011,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10083,7 +10092,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR45">
         <v>1.43</v>
@@ -10208,7 +10217,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10289,7 +10298,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR46">
         <v>1.32</v>
@@ -10414,7 +10423,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10492,10 +10501,10 @@
         <v>1.14</v>
       </c>
       <c r="AP47">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -10620,7 +10629,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -10701,7 +10710,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR48">
         <v>1.65</v>
@@ -10907,7 +10916,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ49">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR49">
         <v>1.28</v>
@@ -11110,7 +11119,7 @@
         <v>1.13</v>
       </c>
       <c r="AP50">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11316,7 +11325,7 @@
         <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ51">
         <v>0.92</v>
@@ -11522,10 +11531,10 @@
         <v>2.13</v>
       </c>
       <c r="AP52">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ52">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR52">
         <v>1.57</v>
@@ -11728,7 +11737,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ53">
         <v>1.08</v>
@@ -11856,7 +11865,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12062,7 +12071,7 @@
         <v>102</v>
       </c>
       <c r="P55" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q55">
         <v>2.78</v>
@@ -12140,7 +12149,7 @@
         <v>1.25</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ55">
         <v>1.5</v>
@@ -12268,7 +12277,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q56">
         <v>2.63</v>
@@ -12474,7 +12483,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -12555,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="AQ57">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR57">
         <v>1.3</v>
@@ -12680,7 +12689,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q58">
         <v>2.69</v>
@@ -12758,10 +12767,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP58">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR58">
         <v>1.71</v>
@@ -12886,7 +12895,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -12964,10 +12973,10 @@
         <v>1.56</v>
       </c>
       <c r="AP59">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ59">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
         <v>1.21</v>
@@ -13092,7 +13101,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13173,7 +13182,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ60">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR60">
         <v>1.65</v>
@@ -13504,7 +13513,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -13582,7 +13591,7 @@
         <v>1.2</v>
       </c>
       <c r="AP62">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ62">
         <v>1.5</v>
@@ -13788,10 +13797,10 @@
         <v>0.9</v>
       </c>
       <c r="AP63">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ63">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -13994,7 +14003,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ64">
         <v>0.92</v>
@@ -14122,7 +14131,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14409,7 +14418,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ66">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR66">
         <v>1.47</v>
@@ -14612,7 +14621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP67">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -14946,7 +14955,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15152,7 +15161,7 @@
         <v>102</v>
       </c>
       <c r="P70" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q70">
         <v>3.1</v>
@@ -15308,6 +15317,624 @@
         <v>4.35</v>
       </c>
       <c r="BP70">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:68">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7793158</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45752.85416666666</v>
+      </c>
+      <c r="F71">
+        <v>12</v>
+      </c>
+      <c r="G71" t="s">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s">
+        <v>75</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+      <c r="O71" t="s">
+        <v>122</v>
+      </c>
+      <c r="P71" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q71">
+        <v>3</v>
+      </c>
+      <c r="R71">
+        <v>2</v>
+      </c>
+      <c r="S71">
+        <v>4</v>
+      </c>
+      <c r="T71">
+        <v>1.5</v>
+      </c>
+      <c r="U71">
+        <v>2.5</v>
+      </c>
+      <c r="V71">
+        <v>3.4</v>
+      </c>
+      <c r="W71">
+        <v>1.3</v>
+      </c>
+      <c r="X71">
+        <v>10</v>
+      </c>
+      <c r="Y71">
+        <v>1.06</v>
+      </c>
+      <c r="Z71">
+        <v>2.14</v>
+      </c>
+      <c r="AA71">
+        <v>3.14</v>
+      </c>
+      <c r="AB71">
+        <v>3.51</v>
+      </c>
+      <c r="AC71">
+        <v>1.07</v>
+      </c>
+      <c r="AD71">
+        <v>8</v>
+      </c>
+      <c r="AE71">
+        <v>1.4</v>
+      </c>
+      <c r="AF71">
+        <v>2.82</v>
+      </c>
+      <c r="AG71">
+        <v>2.3</v>
+      </c>
+      <c r="AH71">
+        <v>1.5</v>
+      </c>
+      <c r="AI71">
+        <v>2</v>
+      </c>
+      <c r="AJ71">
+        <v>1.73</v>
+      </c>
+      <c r="AK71">
+        <v>1.29</v>
+      </c>
+      <c r="AL71">
+        <v>1.33</v>
+      </c>
+      <c r="AM71">
+        <v>1.68</v>
+      </c>
+      <c r="AN71">
+        <v>2.45</v>
+      </c>
+      <c r="AO71">
+        <v>1.64</v>
+      </c>
+      <c r="AP71">
+        <v>2.5</v>
+      </c>
+      <c r="AQ71">
+        <v>1.5</v>
+      </c>
+      <c r="AR71">
+        <v>1.62</v>
+      </c>
+      <c r="AS71">
+        <v>1.42</v>
+      </c>
+      <c r="AT71">
+        <v>3.04</v>
+      </c>
+      <c r="AU71">
+        <v>4</v>
+      </c>
+      <c r="AV71">
+        <v>7</v>
+      </c>
+      <c r="AW71">
+        <v>8</v>
+      </c>
+      <c r="AX71">
+        <v>9</v>
+      </c>
+      <c r="AY71">
+        <v>12</v>
+      </c>
+      <c r="AZ71">
+        <v>16</v>
+      </c>
+      <c r="BA71">
+        <v>7</v>
+      </c>
+      <c r="BB71">
+        <v>8</v>
+      </c>
+      <c r="BC71">
+        <v>15</v>
+      </c>
+      <c r="BD71">
+        <v>2</v>
+      </c>
+      <c r="BE71">
+        <v>5.95</v>
+      </c>
+      <c r="BF71">
+        <v>2.22</v>
+      </c>
+      <c r="BG71">
+        <v>1.41</v>
+      </c>
+      <c r="BH71">
+        <v>2.52</v>
+      </c>
+      <c r="BI71">
+        <v>1.77</v>
+      </c>
+      <c r="BJ71">
+        <v>1.95</v>
+      </c>
+      <c r="BK71">
+        <v>2.28</v>
+      </c>
+      <c r="BL71">
+        <v>1.5</v>
+      </c>
+      <c r="BM71">
+        <v>3.08</v>
+      </c>
+      <c r="BN71">
+        <v>1.28</v>
+      </c>
+      <c r="BO71">
+        <v>4.15</v>
+      </c>
+      <c r="BP71">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:68">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7793161</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45753.76041666666</v>
+      </c>
+      <c r="F72">
+        <v>12</v>
+      </c>
+      <c r="G72" t="s">
+        <v>79</v>
+      </c>
+      <c r="H72" t="s">
+        <v>74</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>2</v>
+      </c>
+      <c r="L72">
+        <v>2</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>3</v>
+      </c>
+      <c r="O72" t="s">
+        <v>132</v>
+      </c>
+      <c r="P72" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q72">
+        <v>3.8</v>
+      </c>
+      <c r="R72">
+        <v>1.9</v>
+      </c>
+      <c r="S72">
+        <v>2.95</v>
+      </c>
+      <c r="T72">
+        <v>1.52</v>
+      </c>
+      <c r="U72">
+        <v>2.35</v>
+      </c>
+      <c r="V72">
+        <v>3.4</v>
+      </c>
+      <c r="W72">
+        <v>1.27</v>
+      </c>
+      <c r="X72">
+        <v>9.75</v>
+      </c>
+      <c r="Y72">
+        <v>1.04</v>
+      </c>
+      <c r="Z72">
+        <v>3.34</v>
+      </c>
+      <c r="AA72">
+        <v>2.99</v>
+      </c>
+      <c r="AB72">
+        <v>2.29</v>
+      </c>
+      <c r="AC72">
+        <v>1.04</v>
+      </c>
+      <c r="AD72">
+        <v>6.9</v>
+      </c>
+      <c r="AE72">
+        <v>1.42</v>
+      </c>
+      <c r="AF72">
+        <v>2.49</v>
+      </c>
+      <c r="AG72">
+        <v>2.37</v>
+      </c>
+      <c r="AH72">
+        <v>1.48</v>
+      </c>
+      <c r="AI72">
+        <v>2.05</v>
+      </c>
+      <c r="AJ72">
+        <v>1.66</v>
+      </c>
+      <c r="AK72">
+        <v>1.6</v>
+      </c>
+      <c r="AL72">
+        <v>1.35</v>
+      </c>
+      <c r="AM72">
+        <v>1.32</v>
+      </c>
+      <c r="AN72">
+        <v>1.73</v>
+      </c>
+      <c r="AO72">
+        <v>1.64</v>
+      </c>
+      <c r="AP72">
+        <v>1.83</v>
+      </c>
+      <c r="AQ72">
+        <v>1.5</v>
+      </c>
+      <c r="AR72">
+        <v>1.29</v>
+      </c>
+      <c r="AS72">
+        <v>1.65</v>
+      </c>
+      <c r="AT72">
+        <v>2.94</v>
+      </c>
+      <c r="AU72">
+        <v>5</v>
+      </c>
+      <c r="AV72">
+        <v>5</v>
+      </c>
+      <c r="AW72">
+        <v>7</v>
+      </c>
+      <c r="AX72">
+        <v>18</v>
+      </c>
+      <c r="AY72">
+        <v>12</v>
+      </c>
+      <c r="AZ72">
+        <v>23</v>
+      </c>
+      <c r="BA72">
+        <v>4</v>
+      </c>
+      <c r="BB72">
+        <v>7</v>
+      </c>
+      <c r="BC72">
+        <v>11</v>
+      </c>
+      <c r="BD72">
+        <v>2.2</v>
+      </c>
+      <c r="BE72">
+        <v>7.5</v>
+      </c>
+      <c r="BF72">
+        <v>1.91</v>
+      </c>
+      <c r="BG72">
+        <v>1.36</v>
+      </c>
+      <c r="BH72">
+        <v>2.92</v>
+      </c>
+      <c r="BI72">
+        <v>1.62</v>
+      </c>
+      <c r="BJ72">
+        <v>2.22</v>
+      </c>
+      <c r="BK72">
+        <v>1.95</v>
+      </c>
+      <c r="BL72">
+        <v>1.77</v>
+      </c>
+      <c r="BM72">
+        <v>2.57</v>
+      </c>
+      <c r="BN72">
+        <v>1.45</v>
+      </c>
+      <c r="BO72">
+        <v>3.42</v>
+      </c>
+      <c r="BP72">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7793159</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45753.85416666666</v>
+      </c>
+      <c r="F73">
+        <v>12</v>
+      </c>
+      <c r="G73" t="s">
+        <v>78</v>
+      </c>
+      <c r="H73" t="s">
+        <v>72</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
+        <v>133</v>
+      </c>
+      <c r="P73" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q73">
+        <v>2.8</v>
+      </c>
+      <c r="R73">
+        <v>1.93</v>
+      </c>
+      <c r="S73">
+        <v>4.1</v>
+      </c>
+      <c r="T73">
+        <v>1.51</v>
+      </c>
+      <c r="U73">
+        <v>2.35</v>
+      </c>
+      <c r="V73">
+        <v>3.4</v>
+      </c>
+      <c r="W73">
+        <v>1.28</v>
+      </c>
+      <c r="X73">
+        <v>9.5</v>
+      </c>
+      <c r="Y73">
+        <v>1.04</v>
+      </c>
+      <c r="Z73">
+        <v>2.15</v>
+      </c>
+      <c r="AA73">
+        <v>3.02</v>
+      </c>
+      <c r="AB73">
+        <v>3.64</v>
+      </c>
+      <c r="AC73">
+        <v>1.09</v>
+      </c>
+      <c r="AD73">
+        <v>6.5</v>
+      </c>
+      <c r="AE73">
+        <v>1.48</v>
+      </c>
+      <c r="AF73">
+        <v>2.37</v>
+      </c>
+      <c r="AG73">
+        <v>2.38</v>
+      </c>
+      <c r="AH73">
+        <v>1.54</v>
+      </c>
+      <c r="AI73">
+        <v>2.05</v>
+      </c>
+      <c r="AJ73">
+        <v>1.66</v>
+      </c>
+      <c r="AK73">
+        <v>1.28</v>
+      </c>
+      <c r="AL73">
+        <v>1.34</v>
+      </c>
+      <c r="AM73">
+        <v>1.68</v>
+      </c>
+      <c r="AN73">
+        <v>1</v>
+      </c>
+      <c r="AO73">
+        <v>0.91</v>
+      </c>
+      <c r="AP73">
+        <v>1.17</v>
+      </c>
+      <c r="AQ73">
+        <v>0.83</v>
+      </c>
+      <c r="AR73">
+        <v>1.45</v>
+      </c>
+      <c r="AS73">
+        <v>1.21</v>
+      </c>
+      <c r="AT73">
+        <v>2.66</v>
+      </c>
+      <c r="AU73">
+        <v>7</v>
+      </c>
+      <c r="AV73">
+        <v>0</v>
+      </c>
+      <c r="AW73">
+        <v>9</v>
+      </c>
+      <c r="AX73">
+        <v>10</v>
+      </c>
+      <c r="AY73">
+        <v>16</v>
+      </c>
+      <c r="AZ73">
+        <v>10</v>
+      </c>
+      <c r="BA73">
+        <v>4</v>
+      </c>
+      <c r="BB73">
+        <v>0</v>
+      </c>
+      <c r="BC73">
+        <v>4</v>
+      </c>
+      <c r="BD73">
+        <v>1.74</v>
+      </c>
+      <c r="BE73">
+        <v>6.1</v>
+      </c>
+      <c r="BF73">
+        <v>2.35</v>
+      </c>
+      <c r="BG73">
+        <v>1.54</v>
+      </c>
+      <c r="BH73">
+        <v>2.28</v>
+      </c>
+      <c r="BI73">
+        <v>1.9</v>
+      </c>
+      <c r="BJ73">
+        <v>1.76</v>
+      </c>
+      <c r="BK73">
+        <v>2.45</v>
+      </c>
+      <c r="BL73">
+        <v>1.46</v>
+      </c>
+      <c r="BM73">
+        <v>3.3</v>
+      </c>
+      <c r="BN73">
+        <v>1.27</v>
+      </c>
+      <c r="BO73">
+        <v>4.35</v>
+      </c>
+      <c r="BP73">
         <v>1.15</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="177">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -418,6 +418,9 @@
     <t>['50']</t>
   </si>
   <si>
+    <t>['9']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -536,6 +539,12 @@
   </si>
   <si>
     <t>['36']</t>
+  </si>
+  <si>
+    <t>['10', '26', '39', '87']</t>
+  </si>
+  <si>
+    <t>['44']</t>
   </si>
 </sst>
 </file>
@@ -897,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP73"/>
+  <dimension ref="A1:BP75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1153,7 +1162,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1231,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ2">
         <v>1.08</v>
@@ -1359,7 +1368,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1643,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ4">
         <v>1.17</v>
@@ -1771,7 +1780,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1852,7 +1861,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1977,7 +1986,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2183,7 +2192,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2389,7 +2398,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2470,7 +2479,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -2595,7 +2604,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2673,10 +2682,10 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ9">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -2801,7 +2810,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q10">
         <v>5.5</v>
@@ -3007,7 +3016,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3419,7 +3428,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3703,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ14">
         <v>0.92</v>
@@ -4243,7 +4252,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4324,7 +4333,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4449,7 +4458,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4527,7 +4536,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ18">
         <v>1.83</v>
@@ -4939,7 +4948,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20">
         <v>1.17</v>
@@ -5145,7 +5154,7 @@
         <v>1.67</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21">
         <v>1.5</v>
@@ -5273,7 +5282,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5479,7 +5488,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5972,7 +5981,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -6097,7 +6106,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6175,7 +6184,7 @@
         <v>1.25</v>
       </c>
       <c r="AP26">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ26">
         <v>0.92</v>
@@ -6509,7 +6518,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6715,7 +6724,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6796,7 +6805,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -6921,7 +6930,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7002,7 +7011,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR30">
         <v>1.83</v>
@@ -7333,7 +7342,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7414,7 +7423,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR32">
         <v>1.08</v>
@@ -7620,7 +7629,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ33">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR33">
         <v>1.83</v>
@@ -7745,7 +7754,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7951,7 +7960,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8157,7 +8166,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8441,7 +8450,7 @@
         <v>1.4</v>
       </c>
       <c r="AP37">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -8569,7 +8578,7 @@
         <v>110</v>
       </c>
       <c r="P38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8647,7 +8656,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ38">
         <v>1.08</v>
@@ -8981,7 +8990,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9393,7 +9402,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9471,10 +9480,10 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR42">
         <v>1.17</v>
@@ -9599,7 +9608,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9805,7 +9814,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -9886,7 +9895,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10011,7 +10020,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10089,7 +10098,7 @@
         <v>2.71</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ45">
         <v>2.5</v>
@@ -10217,7 +10226,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10423,7 +10432,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10504,7 +10513,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -10629,7 +10638,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11119,7 +11128,7 @@
         <v>1.13</v>
       </c>
       <c r="AP50">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11865,7 +11874,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -11943,7 +11952,7 @@
         <v>0.75</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ54">
         <v>0.92</v>
@@ -12071,7 +12080,7 @@
         <v>102</v>
       </c>
       <c r="P55" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q55">
         <v>2.78</v>
@@ -12152,7 +12161,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ55">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR55">
         <v>1.34</v>
@@ -12277,7 +12286,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q56">
         <v>2.63</v>
@@ -12355,10 +12364,10 @@
         <v>1.22</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ56">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR56">
         <v>1.42</v>
@@ -12483,7 +12492,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -12689,7 +12698,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q58">
         <v>2.69</v>
@@ -12895,7 +12904,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -12973,7 +12982,7 @@
         <v>1.56</v>
       </c>
       <c r="AP59">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ59">
         <v>1.5</v>
@@ -13101,7 +13110,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13513,7 +13522,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -13594,7 +13603,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ62">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR62">
         <v>1.2</v>
@@ -13800,7 +13809,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ63">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14131,7 +14140,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14415,7 +14424,7 @@
         <v>1.7</v>
       </c>
       <c r="AP66">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ66">
         <v>1.5</v>
@@ -14827,7 +14836,7 @@
         <v>1.09</v>
       </c>
       <c r="AP68">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -14955,7 +14964,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15036,7 +15045,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ69">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR69">
         <v>1.22</v>
@@ -15161,7 +15170,7 @@
         <v>102</v>
       </c>
       <c r="P70" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q70">
         <v>3.1</v>
@@ -15573,7 +15582,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q72">
         <v>3.8</v>
@@ -15860,7 +15869,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ73">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR73">
         <v>1.45</v>
@@ -15936,6 +15945,418 @@
       </c>
       <c r="BP73">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7793168</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45757.75</v>
+      </c>
+      <c r="F74">
+        <v>13</v>
+      </c>
+      <c r="G74" t="s">
+        <v>72</v>
+      </c>
+      <c r="H74" t="s">
+        <v>77</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3</v>
+      </c>
+      <c r="K74">
+        <v>3</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>4</v>
+      </c>
+      <c r="N74">
+        <v>4</v>
+      </c>
+      <c r="O74" t="s">
+        <v>84</v>
+      </c>
+      <c r="P74" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q74">
+        <v>2.8</v>
+      </c>
+      <c r="R74">
+        <v>2</v>
+      </c>
+      <c r="S74">
+        <v>3.5</v>
+      </c>
+      <c r="T74">
+        <v>1.49</v>
+      </c>
+      <c r="U74">
+        <v>2.4</v>
+      </c>
+      <c r="V74">
+        <v>3.3</v>
+      </c>
+      <c r="W74">
+        <v>1.28</v>
+      </c>
+      <c r="X74">
+        <v>9.5</v>
+      </c>
+      <c r="Y74">
+        <v>1.01</v>
+      </c>
+      <c r="Z74">
+        <v>2.27</v>
+      </c>
+      <c r="AA74">
+        <v>2.9</v>
+      </c>
+      <c r="AB74">
+        <v>3.5</v>
+      </c>
+      <c r="AC74">
+        <v>1.05</v>
+      </c>
+      <c r="AD74">
+        <v>7.5</v>
+      </c>
+      <c r="AE74">
+        <v>1.45</v>
+      </c>
+      <c r="AF74">
+        <v>2.6</v>
+      </c>
+      <c r="AG74">
+        <v>2.25</v>
+      </c>
+      <c r="AH74">
+        <v>1.55</v>
+      </c>
+      <c r="AI74">
+        <v>2</v>
+      </c>
+      <c r="AJ74">
+        <v>1.79</v>
+      </c>
+      <c r="AK74">
+        <v>1.36</v>
+      </c>
+      <c r="AL74">
+        <v>1.31</v>
+      </c>
+      <c r="AM74">
+        <v>1.62</v>
+      </c>
+      <c r="AN74">
+        <v>0.83</v>
+      </c>
+      <c r="AO74">
+        <v>1.33</v>
+      </c>
+      <c r="AP74">
+        <v>0.77</v>
+      </c>
+      <c r="AQ74">
+        <v>1.46</v>
+      </c>
+      <c r="AR74">
+        <v>1.18</v>
+      </c>
+      <c r="AS74">
+        <v>1.43</v>
+      </c>
+      <c r="AT74">
+        <v>2.61</v>
+      </c>
+      <c r="AU74">
+        <v>2</v>
+      </c>
+      <c r="AV74">
+        <v>6</v>
+      </c>
+      <c r="AW74">
+        <v>7</v>
+      </c>
+      <c r="AX74">
+        <v>3</v>
+      </c>
+      <c r="AY74">
+        <v>9</v>
+      </c>
+      <c r="AZ74">
+        <v>9</v>
+      </c>
+      <c r="BA74">
+        <v>5</v>
+      </c>
+      <c r="BB74">
+        <v>2</v>
+      </c>
+      <c r="BC74">
+        <v>7</v>
+      </c>
+      <c r="BD74">
+        <v>1.68</v>
+      </c>
+      <c r="BE74">
+        <v>7.5</v>
+      </c>
+      <c r="BF74">
+        <v>2.7</v>
+      </c>
+      <c r="BG74">
+        <v>1.48</v>
+      </c>
+      <c r="BH74">
+        <v>2.25</v>
+      </c>
+      <c r="BI74">
+        <v>1.9</v>
+      </c>
+      <c r="BJ74">
+        <v>1.76</v>
+      </c>
+      <c r="BK74">
+        <v>2.4</v>
+      </c>
+      <c r="BL74">
+        <v>1.51</v>
+      </c>
+      <c r="BM74">
+        <v>3.3</v>
+      </c>
+      <c r="BN74">
+        <v>1.28</v>
+      </c>
+      <c r="BO74">
+        <v>4.2</v>
+      </c>
+      <c r="BP74">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7793165</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45757.84375</v>
+      </c>
+      <c r="F75">
+        <v>13</v>
+      </c>
+      <c r="G75" t="s">
+        <v>70</v>
+      </c>
+      <c r="H75" t="s">
+        <v>76</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>2</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>2</v>
+      </c>
+      <c r="O75" t="s">
+        <v>134</v>
+      </c>
+      <c r="P75" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q75">
+        <v>2.45</v>
+      </c>
+      <c r="R75">
+        <v>2</v>
+      </c>
+      <c r="S75">
+        <v>4.35</v>
+      </c>
+      <c r="T75">
+        <v>1.44</v>
+      </c>
+      <c r="U75">
+        <v>2.55</v>
+      </c>
+      <c r="V75">
+        <v>3.29</v>
+      </c>
+      <c r="W75">
+        <v>1.33</v>
+      </c>
+      <c r="X75">
+        <v>7.5</v>
+      </c>
+      <c r="Y75">
+        <v>1.06</v>
+      </c>
+      <c r="Z75">
+        <v>2.15</v>
+      </c>
+      <c r="AA75">
+        <v>3.16</v>
+      </c>
+      <c r="AB75">
+        <v>3.47</v>
+      </c>
+      <c r="AC75">
+        <v>1.07</v>
+      </c>
+      <c r="AD75">
+        <v>8</v>
+      </c>
+      <c r="AE75">
+        <v>1.37</v>
+      </c>
+      <c r="AF75">
+        <v>2.83</v>
+      </c>
+      <c r="AG75">
+        <v>2.1</v>
+      </c>
+      <c r="AH75">
+        <v>1.61</v>
+      </c>
+      <c r="AI75">
+        <v>1.85</v>
+      </c>
+      <c r="AJ75">
+        <v>1.85</v>
+      </c>
+      <c r="AK75">
+        <v>1.31</v>
+      </c>
+      <c r="AL75">
+        <v>1.31</v>
+      </c>
+      <c r="AM75">
+        <v>1.66</v>
+      </c>
+      <c r="AN75">
+        <v>1.5</v>
+      </c>
+      <c r="AO75">
+        <v>0.92</v>
+      </c>
+      <c r="AP75">
+        <v>1.46</v>
+      </c>
+      <c r="AQ75">
+        <v>0.92</v>
+      </c>
+      <c r="AR75">
+        <v>1.43</v>
+      </c>
+      <c r="AS75">
+        <v>1.31</v>
+      </c>
+      <c r="AT75">
+        <v>2.74</v>
+      </c>
+      <c r="AU75">
+        <v>4</v>
+      </c>
+      <c r="AV75">
+        <v>6</v>
+      </c>
+      <c r="AW75">
+        <v>4</v>
+      </c>
+      <c r="AX75">
+        <v>4</v>
+      </c>
+      <c r="AY75">
+        <v>8</v>
+      </c>
+      <c r="AZ75">
+        <v>10</v>
+      </c>
+      <c r="BA75">
+        <v>5</v>
+      </c>
+      <c r="BB75">
+        <v>4</v>
+      </c>
+      <c r="BC75">
+        <v>9</v>
+      </c>
+      <c r="BD75">
+        <v>1.68</v>
+      </c>
+      <c r="BE75">
+        <v>6.2</v>
+      </c>
+      <c r="BF75">
+        <v>2.48</v>
+      </c>
+      <c r="BG75">
+        <v>1.52</v>
+      </c>
+      <c r="BH75">
+        <v>2.3</v>
+      </c>
+      <c r="BI75">
+        <v>1.86</v>
+      </c>
+      <c r="BJ75">
+        <v>1.77</v>
+      </c>
+      <c r="BK75">
+        <v>2.78</v>
+      </c>
+      <c r="BL75">
+        <v>1.55</v>
+      </c>
+      <c r="BM75">
+        <v>3.05</v>
+      </c>
+      <c r="BN75">
+        <v>1.29</v>
+      </c>
+      <c r="BO75">
+        <v>4.33</v>
+      </c>
+      <c r="BP75">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="223">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,9 @@
     <t>['35', '57']</t>
   </si>
   <si>
+    <t>['43', '76']</t>
+  </si>
+  <si>
     <t>['7', '90']</t>
   </si>
   <si>
@@ -677,6 +680,9 @@
   </si>
   <si>
     <t>['53']</t>
+  </si>
+  <si>
+    <t>['18', '23', '37', '28']</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1294,7 +1300,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1372,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ2">
         <v>1.32</v>
@@ -1500,7 +1506,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1912,7 +1918,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1993,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2118,7 +2124,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2324,7 +2330,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2530,7 +2536,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2611,7 +2617,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ8">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR8">
         <v>1.35</v>
@@ -2736,7 +2742,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2814,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ9">
         <v>0.82</v>
@@ -3148,7 +3154,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3560,7 +3566,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3844,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4384,7 +4390,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4465,7 +4471,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR17">
         <v>1.68</v>
@@ -4590,7 +4596,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -5080,7 +5086,7 @@
         <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ20">
         <v>1.14</v>
@@ -5286,7 +5292,7 @@
         <v>1.67</v>
       </c>
       <c r="AP21">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ21">
         <v>1.77</v>
@@ -5414,7 +5420,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5620,7 +5626,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -6238,7 +6244,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6650,7 +6656,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6856,7 +6862,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6937,7 +6943,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ29">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -7062,7 +7068,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7143,7 +7149,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR30">
         <v>1.83</v>
@@ -7474,7 +7480,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7555,7 +7561,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ32">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR32">
         <v>1.08</v>
@@ -7886,7 +7892,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -8092,7 +8098,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8298,7 +8304,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8582,7 +8588,7 @@
         <v>1.4</v>
       </c>
       <c r="AP37">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -8788,7 +8794,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ38">
         <v>1.32</v>
@@ -9122,7 +9128,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9534,7 +9540,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9615,7 +9621,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ42">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR42">
         <v>1.17</v>
@@ -9946,7 +9952,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -10027,7 +10033,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ44">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10152,7 +10158,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10230,7 +10236,7 @@
         <v>2.71</v>
       </c>
       <c r="AP45">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ45">
         <v>2</v>
@@ -10358,7 +10364,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10564,7 +10570,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -12006,7 +12012,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12084,7 +12090,7 @@
         <v>0.75</v>
       </c>
       <c r="AP54">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12293,7 +12299,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ55">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR55">
         <v>1.34</v>
@@ -12496,10 +12502,10 @@
         <v>1.22</v>
       </c>
       <c r="AP56">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ56">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR56">
         <v>1.42</v>
@@ -12624,7 +12630,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -13036,7 +13042,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -13242,7 +13248,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13654,7 +13660,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -13735,7 +13741,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ62">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR62">
         <v>1.2</v>
@@ -14272,7 +14278,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14556,7 +14562,7 @@
         <v>1.7</v>
       </c>
       <c r="AP66">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ66">
         <v>1.5</v>
@@ -14968,7 +14974,7 @@
         <v>1.09</v>
       </c>
       <c r="AP68">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15096,7 +15102,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15177,7 +15183,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ69">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR69">
         <v>1.22</v>
@@ -15302,7 +15308,7 @@
         <v>102</v>
       </c>
       <c r="P70" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q70">
         <v>3.1</v>
@@ -15714,7 +15720,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>3.8</v>
@@ -16126,7 +16132,7 @@
         <v>84</v>
       </c>
       <c r="P74" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -16207,7 +16213,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ74">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR74">
         <v>1.18</v>
@@ -16332,7 +16338,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q75">
         <v>2.45</v>
@@ -16410,7 +16416,7 @@
         <v>0.92</v>
       </c>
       <c r="AP75">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ75">
         <v>0.82</v>
@@ -17440,7 +17446,7 @@
         <v>2.54</v>
       </c>
       <c r="AP80">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ80">
         <v>2</v>
@@ -17649,7 +17655,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR81">
         <v>1.44</v>
@@ -17774,7 +17780,7 @@
         <v>122</v>
       </c>
       <c r="P82" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q82">
         <v>4</v>
@@ -17980,7 +17986,7 @@
         <v>84</v>
       </c>
       <c r="P83" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q83">
         <v>2.75</v>
@@ -18392,7 +18398,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q85">
         <v>4.41</v>
@@ -18598,7 +18604,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q86">
         <v>2.2</v>
@@ -18804,7 +18810,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q87">
         <v>2.2</v>
@@ -19010,7 +19016,7 @@
         <v>84</v>
       </c>
       <c r="P88" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q88">
         <v>3.55</v>
@@ -19297,7 +19303,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ89">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR89">
         <v>1.53</v>
@@ -19422,7 +19428,7 @@
         <v>141</v>
       </c>
       <c r="P90" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19709,7 +19715,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ91">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR91">
         <v>1.46</v>
@@ -20040,7 +20046,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q93">
         <v>3.2</v>
@@ -20736,7 +20742,7 @@
         <v>1.67</v>
       </c>
       <c r="AP96">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ96">
         <v>1.5</v>
@@ -20864,7 +20870,7 @@
         <v>143</v>
       </c>
       <c r="P97" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q97">
         <v>4.8</v>
@@ -20942,7 +20948,7 @@
         <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ97">
         <v>1.77</v>
@@ -21276,7 +21282,7 @@
         <v>84</v>
       </c>
       <c r="P99" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21354,7 +21360,7 @@
         <v>1.81</v>
       </c>
       <c r="AP99">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ99">
         <v>1.73</v>
@@ -21482,7 +21488,7 @@
         <v>146</v>
       </c>
       <c r="P100" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q100">
         <v>2.8</v>
@@ -22100,7 +22106,7 @@
         <v>147</v>
       </c>
       <c r="P103" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q103">
         <v>3.15</v>
@@ -22181,7 +22187,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR103">
         <v>1.2</v>
@@ -22384,7 +22390,7 @@
         <v>0.88</v>
       </c>
       <c r="AP104">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ104">
         <v>0.82</v>
@@ -22512,7 +22518,7 @@
         <v>149</v>
       </c>
       <c r="P105" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22718,7 +22724,7 @@
         <v>84</v>
       </c>
       <c r="P106" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q106">
         <v>3.65</v>
@@ -22924,7 +22930,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23005,7 +23011,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ107">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR107">
         <v>1.27</v>
@@ -23130,7 +23136,7 @@
         <v>84</v>
       </c>
       <c r="P108" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q108">
         <v>2.2</v>
@@ -23542,7 +23548,7 @@
         <v>151</v>
       </c>
       <c r="P110" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -23620,7 +23626,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP110">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ110">
         <v>0.82</v>
@@ -24160,7 +24166,7 @@
         <v>154</v>
       </c>
       <c r="P113" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q113">
         <v>2.15</v>
@@ -24241,7 +24247,7 @@
         <v>2</v>
       </c>
       <c r="AQ113">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -24572,7 +24578,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q115">
         <v>2.9</v>
@@ -24859,7 +24865,7 @@
         <v>1</v>
       </c>
       <c r="AQ116">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25062,7 +25068,7 @@
         <v>1.11</v>
       </c>
       <c r="AP117">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ117">
         <v>1.14</v>
@@ -25190,7 +25196,7 @@
         <v>157</v>
       </c>
       <c r="P118" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q118">
         <v>3.3</v>
@@ -25602,7 +25608,7 @@
         <v>97</v>
       </c>
       <c r="P120" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q120">
         <v>3.25</v>
@@ -26014,7 +26020,7 @@
         <v>158</v>
       </c>
       <c r="P122" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q122">
         <v>2.71</v>
@@ -27044,7 +27050,7 @@
         <v>159</v>
       </c>
       <c r="P127" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q127">
         <v>3.7</v>
@@ -27122,10 +27128,10 @@
         <v>1.4</v>
       </c>
       <c r="AP127">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AQ127">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AR127">
         <v>1.41</v>
@@ -27250,7 +27256,7 @@
         <v>162</v>
       </c>
       <c r="P128" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q128">
         <v>4.33</v>
@@ -27456,7 +27462,7 @@
         <v>147</v>
       </c>
       <c r="P129" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q129">
         <v>6</v>
@@ -27743,7 +27749,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ130">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AR130">
         <v>1.67</v>
@@ -27946,7 +27952,7 @@
         <v>1.81</v>
       </c>
       <c r="AP131">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ131">
         <v>1.73</v>
@@ -28074,7 +28080,7 @@
         <v>84</v>
       </c>
       <c r="P132" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q132">
         <v>3.8</v>
@@ -28437,6 +28443,212 @@
       </c>
       <c r="BP133">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7771411</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45842.77083333334</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134" t="s">
+        <v>77</v>
+      </c>
+      <c r="H134" t="s">
+        <v>70</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134">
+        <v>4</v>
+      </c>
+      <c r="K134">
+        <v>5</v>
+      </c>
+      <c r="L134">
+        <v>2</v>
+      </c>
+      <c r="M134">
+        <v>4</v>
+      </c>
+      <c r="N134">
+        <v>6</v>
+      </c>
+      <c r="O134" t="s">
+        <v>164</v>
+      </c>
+      <c r="P134" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+      <c r="S134">
+        <v>0</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134">
+        <v>0</v>
+      </c>
+      <c r="V134">
+        <v>0</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>0</v>
+      </c>
+      <c r="Z134">
+        <v>3</v>
+      </c>
+      <c r="AA134">
+        <v>3.2</v>
+      </c>
+      <c r="AB134">
+        <v>2.1</v>
+      </c>
+      <c r="AC134">
+        <v>0</v>
+      </c>
+      <c r="AD134">
+        <v>0</v>
+      </c>
+      <c r="AE134">
+        <v>0</v>
+      </c>
+      <c r="AF134">
+        <v>0</v>
+      </c>
+      <c r="AG134">
+        <v>2</v>
+      </c>
+      <c r="AH134">
+        <v>1.8</v>
+      </c>
+      <c r="AI134">
+        <v>0</v>
+      </c>
+      <c r="AJ134">
+        <v>0</v>
+      </c>
+      <c r="AK134">
+        <v>0</v>
+      </c>
+      <c r="AL134">
+        <v>0</v>
+      </c>
+      <c r="AM134">
+        <v>0</v>
+      </c>
+      <c r="AN134">
+        <v>1.23</v>
+      </c>
+      <c r="AO134">
+        <v>1.55</v>
+      </c>
+      <c r="AP134">
+        <v>1.17</v>
+      </c>
+      <c r="AQ134">
+        <v>1.61</v>
+      </c>
+      <c r="AR134">
+        <v>1.46</v>
+      </c>
+      <c r="AS134">
+        <v>1.54</v>
+      </c>
+      <c r="AT134">
+        <v>3</v>
+      </c>
+      <c r="AU134">
+        <v>9</v>
+      </c>
+      <c r="AV134">
+        <v>11</v>
+      </c>
+      <c r="AW134">
+        <v>10</v>
+      </c>
+      <c r="AX134">
+        <v>8</v>
+      </c>
+      <c r="AY134">
+        <v>19</v>
+      </c>
+      <c r="AZ134">
+        <v>19</v>
+      </c>
+      <c r="BA134">
+        <v>9</v>
+      </c>
+      <c r="BB134">
+        <v>7</v>
+      </c>
+      <c r="BC134">
+        <v>16</v>
+      </c>
+      <c r="BD134">
+        <v>0</v>
+      </c>
+      <c r="BE134">
+        <v>0</v>
+      </c>
+      <c r="BF134">
+        <v>0</v>
+      </c>
+      <c r="BG134">
+        <v>0</v>
+      </c>
+      <c r="BH134">
+        <v>0</v>
+      </c>
+      <c r="BI134">
+        <v>0</v>
+      </c>
+      <c r="BJ134">
+        <v>0</v>
+      </c>
+      <c r="BK134">
+        <v>0</v>
+      </c>
+      <c r="BL134">
+        <v>0</v>
+      </c>
+      <c r="BM134">
+        <v>0</v>
+      </c>
+      <c r="BN134">
+        <v>0</v>
+      </c>
+      <c r="BO134">
+        <v>0</v>
+      </c>
+      <c r="BP134">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="224">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -509,6 +509,9 @@
   </si>
   <si>
     <t>['43', '76']</t>
+  </si>
+  <si>
+    <t>['66', '34', '32']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -1044,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1300,7 +1303,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1506,7 +1509,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1918,7 +1921,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1996,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ5">
         <v>1.17</v>
@@ -2124,7 +2127,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2330,7 +2333,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2408,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -2536,7 +2539,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2742,7 +2745,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3029,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR10">
         <v>2.15</v>
@@ -3154,7 +3157,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3441,7 +3444,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR12">
         <v>1.05</v>
@@ -3566,7 +3569,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -4056,7 +4059,7 @@
         <v>0.5</v>
       </c>
       <c r="AP15">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ15">
         <v>1.14</v>
@@ -4262,7 +4265,7 @@
         <v>2</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ16">
         <v>1.32</v>
@@ -4390,7 +4393,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4596,7 +4599,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -5295,7 +5298,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ21">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5420,7 +5423,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5626,7 +5629,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5913,7 +5916,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -6244,7 +6247,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6528,7 +6531,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6656,7 +6659,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6862,7 +6865,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -6940,7 +6943,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ29">
         <v>1.17</v>
@@ -7068,7 +7071,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7480,7 +7483,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7892,7 +7895,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -8098,7 +8101,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8304,7 +8307,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8385,7 +8388,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR36">
         <v>1.8</v>
@@ -8591,7 +8594,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR37">
         <v>1.52</v>
@@ -9128,7 +9131,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9206,7 +9209,7 @@
         <v>2.17</v>
       </c>
       <c r="AP40">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ40">
         <v>1.5</v>
@@ -9540,7 +9543,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9824,7 +9827,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ43">
         <v>1.73</v>
@@ -9952,7 +9955,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -10158,7 +10161,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10364,7 +10367,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10442,10 +10445,10 @@
         <v>1.14</v>
       </c>
       <c r="AP46">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ46">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR46">
         <v>1.32</v>
@@ -10570,7 +10573,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -11269,7 +11272,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR50">
         <v>1.1</v>
@@ -11884,7 +11887,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ53">
         <v>1.32</v>
@@ -12012,7 +12015,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12630,7 +12633,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -12708,7 +12711,7 @@
         <v>2.56</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ57">
         <v>2</v>
@@ -13042,7 +13045,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -13123,7 +13126,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ59">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR59">
         <v>1.21</v>
@@ -13248,7 +13251,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13660,7 +13663,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -14150,7 +14153,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ64">
         <v>0.82</v>
@@ -14278,7 +14281,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14771,7 +14774,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR67">
         <v>1.43</v>
@@ -14977,7 +14980,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR68">
         <v>1.43</v>
@@ -15102,7 +15105,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15308,7 +15311,7 @@
         <v>102</v>
       </c>
       <c r="P70" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q70">
         <v>3.1</v>
@@ -15595,7 +15598,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR71">
         <v>1.62</v>
@@ -15720,7 +15723,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q72">
         <v>3.8</v>
@@ -16132,7 +16135,7 @@
         <v>84</v>
       </c>
       <c r="P74" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -16338,7 +16341,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q75">
         <v>2.45</v>
@@ -16828,7 +16831,7 @@
         <v>0.92</v>
       </c>
       <c r="AP77">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17240,7 +17243,7 @@
         <v>1.83</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ79">
         <v>1.73</v>
@@ -17780,7 +17783,7 @@
         <v>122</v>
       </c>
       <c r="P82" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q82">
         <v>4</v>
@@ -17861,7 +17864,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ82">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR82">
         <v>1.47</v>
@@ -17986,7 +17989,7 @@
         <v>84</v>
       </c>
       <c r="P83" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q83">
         <v>2.75</v>
@@ -18067,7 +18070,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR83">
         <v>1.28</v>
@@ -18398,7 +18401,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q85">
         <v>4.41</v>
@@ -18604,7 +18607,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q86">
         <v>2.2</v>
@@ -18810,7 +18813,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q87">
         <v>2.2</v>
@@ -19016,7 +19019,7 @@
         <v>84</v>
       </c>
       <c r="P88" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q88">
         <v>3.55</v>
@@ -19094,7 +19097,7 @@
         <v>0.86</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ88">
         <v>0.82</v>
@@ -19300,7 +19303,7 @@
         <v>1.36</v>
       </c>
       <c r="AP89">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ89">
         <v>1.61</v>
@@ -19428,7 +19431,7 @@
         <v>141</v>
       </c>
       <c r="P90" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20046,7 +20049,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q93">
         <v>3.2</v>
@@ -20333,7 +20336,7 @@
         <v>1</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR94">
         <v>1.46</v>
@@ -20870,7 +20873,7 @@
         <v>143</v>
       </c>
       <c r="P97" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q97">
         <v>4.8</v>
@@ -20951,7 +20954,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ97">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR97">
         <v>1.39</v>
@@ -21282,7 +21285,7 @@
         <v>84</v>
       </c>
       <c r="P99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21488,7 +21491,7 @@
         <v>146</v>
       </c>
       <c r="P100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q100">
         <v>2.8</v>
@@ -21566,7 +21569,7 @@
         <v>1.63</v>
       </c>
       <c r="AP100">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ100">
         <v>1.5</v>
@@ -22106,7 +22109,7 @@
         <v>147</v>
       </c>
       <c r="P103" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q103">
         <v>3.15</v>
@@ -22184,7 +22187,7 @@
         <v>1.25</v>
       </c>
       <c r="AP103">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ103">
         <v>1.61</v>
@@ -22518,7 +22521,7 @@
         <v>149</v>
       </c>
       <c r="P105" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22724,7 +22727,7 @@
         <v>84</v>
       </c>
       <c r="P106" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q106">
         <v>3.65</v>
@@ -22805,7 +22808,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ106">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR106">
         <v>1.31</v>
@@ -22930,7 +22933,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23136,7 +23139,7 @@
         <v>84</v>
       </c>
       <c r="P108" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q108">
         <v>2.2</v>
@@ -23217,7 +23220,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR108">
         <v>1.7</v>
@@ -23548,7 +23551,7 @@
         <v>151</v>
       </c>
       <c r="P110" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -23832,10 +23835,10 @@
         <v>1.17</v>
       </c>
       <c r="AP111">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR111">
         <v>1.55</v>
@@ -24166,7 +24169,7 @@
         <v>154</v>
       </c>
       <c r="P113" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q113">
         <v>2.15</v>
@@ -24578,7 +24581,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q115">
         <v>2.9</v>
@@ -25196,7 +25199,7 @@
         <v>157</v>
       </c>
       <c r="P118" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q118">
         <v>3.3</v>
@@ -25274,7 +25277,7 @@
         <v>0.84</v>
       </c>
       <c r="AP118">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ118">
         <v>0.82</v>
@@ -25483,7 +25486,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ119">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -25608,7 +25611,7 @@
         <v>97</v>
       </c>
       <c r="P120" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q120">
         <v>3.25</v>
@@ -26020,7 +26023,7 @@
         <v>158</v>
       </c>
       <c r="P122" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q122">
         <v>2.71</v>
@@ -26307,7 +26310,7 @@
         <v>2</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR123">
         <v>1.59</v>
@@ -26510,7 +26513,7 @@
         <v>0.85</v>
       </c>
       <c r="AP124">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AQ124">
         <v>0.82</v>
@@ -27050,7 +27053,7 @@
         <v>159</v>
       </c>
       <c r="P127" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q127">
         <v>3.7</v>
@@ -27256,7 +27259,7 @@
         <v>162</v>
       </c>
       <c r="P128" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q128">
         <v>4.33</v>
@@ -27334,7 +27337,7 @@
         <v>1.05</v>
       </c>
       <c r="AP128">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ128">
         <v>1.14</v>
@@ -27462,7 +27465,7 @@
         <v>147</v>
       </c>
       <c r="P129" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q129">
         <v>6</v>
@@ -27543,7 +27546,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ129">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AR129">
         <v>1.28</v>
@@ -28080,7 +28083,7 @@
         <v>84</v>
       </c>
       <c r="P132" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q132">
         <v>3.8</v>
@@ -28492,7 +28495,7 @@
         <v>164</v>
       </c>
       <c r="P134" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -28649,6 +28652,212 @@
       </c>
       <c r="BP134">
         <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7771407</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45843.66666666666</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s">
+        <v>75</v>
+      </c>
+      <c r="H135" t="s">
+        <v>73</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>2</v>
+      </c>
+      <c r="L135">
+        <v>3</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>4</v>
+      </c>
+      <c r="O135" t="s">
+        <v>165</v>
+      </c>
+      <c r="P135" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q135">
+        <v>1.94</v>
+      </c>
+      <c r="R135">
+        <v>2.22</v>
+      </c>
+      <c r="S135">
+        <v>6.5</v>
+      </c>
+      <c r="T135">
+        <v>1.36</v>
+      </c>
+      <c r="U135">
+        <v>2.84</v>
+      </c>
+      <c r="V135">
+        <v>2.76</v>
+      </c>
+      <c r="W135">
+        <v>1.42</v>
+      </c>
+      <c r="X135">
+        <v>6.4</v>
+      </c>
+      <c r="Y135">
+        <v>1.09</v>
+      </c>
+      <c r="Z135">
+        <v>1.43</v>
+      </c>
+      <c r="AA135">
+        <v>4.1</v>
+      </c>
+      <c r="AB135">
+        <v>6.98</v>
+      </c>
+      <c r="AC135">
+        <v>1.05</v>
+      </c>
+      <c r="AD135">
+        <v>8.9</v>
+      </c>
+      <c r="AE135">
+        <v>1.28</v>
+      </c>
+      <c r="AF135">
+        <v>3.4</v>
+      </c>
+      <c r="AG135">
+        <v>1.9</v>
+      </c>
+      <c r="AH135">
+        <v>1.9</v>
+      </c>
+      <c r="AI135">
+        <v>2.1</v>
+      </c>
+      <c r="AJ135">
+        <v>1.7</v>
+      </c>
+      <c r="AK135">
+        <v>1.22</v>
+      </c>
+      <c r="AL135">
+        <v>1.21</v>
+      </c>
+      <c r="AM135">
+        <v>2.63</v>
+      </c>
+      <c r="AN135">
+        <v>1.77</v>
+      </c>
+      <c r="AO135">
+        <v>1</v>
+      </c>
+      <c r="AP135">
+        <v>1.83</v>
+      </c>
+      <c r="AQ135">
+        <v>0.96</v>
+      </c>
+      <c r="AR135">
+        <v>1.6</v>
+      </c>
+      <c r="AS135">
+        <v>1.27</v>
+      </c>
+      <c r="AT135">
+        <v>2.87</v>
+      </c>
+      <c r="AU135">
+        <v>7</v>
+      </c>
+      <c r="AV135">
+        <v>5</v>
+      </c>
+      <c r="AW135">
+        <v>7</v>
+      </c>
+      <c r="AX135">
+        <v>6</v>
+      </c>
+      <c r="AY135">
+        <v>14</v>
+      </c>
+      <c r="AZ135">
+        <v>11</v>
+      </c>
+      <c r="BA135">
+        <v>4</v>
+      </c>
+      <c r="BB135">
+        <v>2</v>
+      </c>
+      <c r="BC135">
+        <v>6</v>
+      </c>
+      <c r="BD135">
+        <v>1.22</v>
+      </c>
+      <c r="BE135">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF135">
+        <v>5.1</v>
+      </c>
+      <c r="BG135">
+        <v>1.39</v>
+      </c>
+      <c r="BH135">
+        <v>2.7</v>
+      </c>
+      <c r="BI135">
+        <v>1.7</v>
+      </c>
+      <c r="BJ135">
+        <v>2.1</v>
+      </c>
+      <c r="BK135">
+        <v>2.12</v>
+      </c>
+      <c r="BL135">
+        <v>1.67</v>
+      </c>
+      <c r="BM135">
+        <v>2.62</v>
+      </c>
+      <c r="BN135">
+        <v>1.42</v>
+      </c>
+      <c r="BO135">
+        <v>3.4</v>
+      </c>
+      <c r="BP135">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="224">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1047,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP135"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ3">
         <v>0.82</v>
@@ -2414,7 +2414,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ7">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ10">
         <v>1.83</v>
@@ -3238,7 +3238,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR11">
         <v>0.7</v>
@@ -3856,7 +3856,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR14">
         <v>1.54</v>
@@ -4471,7 +4471,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ17">
         <v>1.17</v>
@@ -5501,7 +5501,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ22">
         <v>1.5</v>
@@ -5710,7 +5710,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR23">
         <v>1.04</v>
@@ -6534,7 +6534,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR27">
         <v>1.17</v>
@@ -7355,7 +7355,7 @@
         <v>1.25</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ31">
         <v>1.32</v>
@@ -7767,7 +7767,7 @@
         <v>1.2</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ33">
         <v>0.82</v>
@@ -8182,7 +8182,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ35">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR35">
         <v>1.46</v>
@@ -9003,10 +9003,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR39">
         <v>1.59</v>
@@ -10242,7 +10242,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR45">
         <v>1.43</v>
@@ -10857,7 +10857,7 @@
         <v>0.57</v>
       </c>
       <c r="AP48">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ48">
         <v>1.14</v>
@@ -11681,7 +11681,7 @@
         <v>2.13</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ52">
         <v>1.5</v>
@@ -12096,7 +12096,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR54">
         <v>1.4</v>
@@ -12714,7 +12714,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ57">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR57">
         <v>1.3</v>
@@ -13329,7 +13329,7 @@
         <v>1.78</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ60">
         <v>1.73</v>
@@ -13947,7 +13947,7 @@
         <v>0.9</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ63">
         <v>0.82</v>
@@ -14362,7 +14362,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR65">
         <v>1.17</v>
@@ -15392,7 +15392,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR70">
         <v>1.3</v>
@@ -15595,7 +15595,7 @@
         <v>1.64</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ71">
         <v>1.83</v>
@@ -16625,7 +16625,7 @@
         <v>1.17</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ76">
         <v>1.14</v>
@@ -16834,7 +16834,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR77">
         <v>1.45</v>
@@ -17452,7 +17452,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ80">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR80">
         <v>1.4</v>
@@ -17655,7 +17655,7 @@
         <v>1.46</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ81">
         <v>1.61</v>
@@ -18685,7 +18685,7 @@
         <v>1.64</v>
       </c>
       <c r="AP86">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ86">
         <v>1.73</v>
@@ -18894,7 +18894,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR87">
         <v>1.67</v>
@@ -20333,7 +20333,7 @@
         <v>1.07</v>
       </c>
       <c r="AP94">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ94">
         <v>0.96</v>
@@ -20542,7 +20542,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ95">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR95">
         <v>1.3</v>
@@ -21160,7 +21160,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR98">
         <v>1.29</v>
@@ -21981,7 +21981,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ102">
         <v>0.82</v>
@@ -23423,10 +23423,10 @@
         <v>2.12</v>
       </c>
       <c r="AP109">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ109">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR109">
         <v>1.46</v>
@@ -24044,7 +24044,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR112">
         <v>1.66</v>
@@ -24247,7 +24247,7 @@
         <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ113">
         <v>1.61</v>
@@ -24865,7 +24865,7 @@
         <v>1.32</v>
       </c>
       <c r="AP116">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ116">
         <v>1.17</v>
@@ -25898,7 +25898,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ121">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR121">
         <v>1.67</v>
@@ -26104,7 +26104,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR122">
         <v>1.29</v>
@@ -26307,7 +26307,7 @@
         <v>1.1</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ123">
         <v>0.96</v>
@@ -28164,7 +28164,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ132">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AR132">
         <v>1.3</v>
@@ -28367,7 +28367,7 @@
         <v>1.33</v>
       </c>
       <c r="AP133">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ133">
         <v>1.32</v>
@@ -28858,6 +28858,212 @@
       </c>
       <c r="BP135">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7771408</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45843.77083333334</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136" t="s">
+        <v>81</v>
+      </c>
+      <c r="H136" t="s">
+        <v>71</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>1</v>
+      </c>
+      <c r="O136" t="s">
+        <v>84</v>
+      </c>
+      <c r="P136" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q136">
+        <v>2.02</v>
+      </c>
+      <c r="R136">
+        <v>2.09</v>
+      </c>
+      <c r="S136">
+        <v>5.8</v>
+      </c>
+      <c r="T136">
+        <v>1.4</v>
+      </c>
+      <c r="U136">
+        <v>2.8</v>
+      </c>
+      <c r="V136">
+        <v>3.08</v>
+      </c>
+      <c r="W136">
+        <v>1.38</v>
+      </c>
+      <c r="X136">
+        <v>7.2</v>
+      </c>
+      <c r="Y136">
+        <v>1.08</v>
+      </c>
+      <c r="Z136">
+        <v>1.43</v>
+      </c>
+      <c r="AA136">
+        <v>4</v>
+      </c>
+      <c r="AB136">
+        <v>6.9</v>
+      </c>
+      <c r="AC136">
+        <v>1.06</v>
+      </c>
+      <c r="AD136">
+        <v>10</v>
+      </c>
+      <c r="AE136">
+        <v>1.3</v>
+      </c>
+      <c r="AF136">
+        <v>3.2</v>
+      </c>
+      <c r="AG136">
+        <v>1.91</v>
+      </c>
+      <c r="AH136">
+        <v>1.75</v>
+      </c>
+      <c r="AI136">
+        <v>2.15</v>
+      </c>
+      <c r="AJ136">
+        <v>1.57</v>
+      </c>
+      <c r="AK136">
+        <v>1.08</v>
+      </c>
+      <c r="AL136">
+        <v>1.21</v>
+      </c>
+      <c r="AM136">
+        <v>2.7</v>
+      </c>
+      <c r="AN136">
+        <v>2</v>
+      </c>
+      <c r="AO136">
+        <v>1</v>
+      </c>
+      <c r="AP136">
+        <v>1.91</v>
+      </c>
+      <c r="AQ136">
+        <v>1.09</v>
+      </c>
+      <c r="AR136">
+        <v>1.58</v>
+      </c>
+      <c r="AS136">
+        <v>1.39</v>
+      </c>
+      <c r="AT136">
+        <v>2.97</v>
+      </c>
+      <c r="AU136">
+        <v>4</v>
+      </c>
+      <c r="AV136">
+        <v>5</v>
+      </c>
+      <c r="AW136">
+        <v>12</v>
+      </c>
+      <c r="AX136">
+        <v>5</v>
+      </c>
+      <c r="AY136">
+        <v>16</v>
+      </c>
+      <c r="AZ136">
+        <v>10</v>
+      </c>
+      <c r="BA136">
+        <v>9</v>
+      </c>
+      <c r="BB136">
+        <v>4</v>
+      </c>
+      <c r="BC136">
+        <v>13</v>
+      </c>
+      <c r="BD136">
+        <v>1.33</v>
+      </c>
+      <c r="BE136">
+        <v>8.9</v>
+      </c>
+      <c r="BF136">
+        <v>3.94</v>
+      </c>
+      <c r="BG136">
+        <v>1.48</v>
+      </c>
+      <c r="BH136">
+        <v>2.57</v>
+      </c>
+      <c r="BI136">
+        <v>1.76</v>
+      </c>
+      <c r="BJ136">
+        <v>1.94</v>
+      </c>
+      <c r="BK136">
+        <v>2.24</v>
+      </c>
+      <c r="BL136">
+        <v>1.56</v>
+      </c>
+      <c r="BM136">
+        <v>3.02</v>
+      </c>
+      <c r="BN136">
+        <v>1.36</v>
+      </c>
+      <c r="BO136">
+        <v>4.37</v>
+      </c>
+      <c r="BP136">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -28800,25 +28800,25 @@
         <v>5</v>
       </c>
       <c r="AW135">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX135">
+        <v>4</v>
+      </c>
+      <c r="AY135">
+        <v>11</v>
+      </c>
+      <c r="AZ135">
+        <v>9</v>
+      </c>
+      <c r="BA135">
         <v>6</v>
       </c>
-      <c r="AY135">
-        <v>14</v>
-      </c>
-      <c r="AZ135">
-        <v>11</v>
-      </c>
-      <c r="BA135">
-        <v>4</v>
-      </c>
       <c r="BB135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC135">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD135">
         <v>1.22</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -511,7 +511,10 @@
     <t>['43', '76']</t>
   </si>
   <si>
-    <t>['66', '34', '32']</t>
+    <t>['65', '33', '32']</t>
+  </si>
+  <si>
+    <t>['45+1', '79', '90+5']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -1047,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1303,7 +1306,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1509,7 +1512,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1793,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1921,7 +1924,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2127,7 +2130,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2205,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ6">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2333,7 +2336,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2539,7 +2542,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2745,7 +2748,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2826,7 +2829,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ9">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR9">
         <v>1.34</v>
@@ -3157,7 +3160,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3235,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11">
         <v>1.91</v>
@@ -3441,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="AP12">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ12">
         <v>0.96</v>
@@ -3569,7 +3572,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3650,7 +3653,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR13">
         <v>1.78</v>
@@ -4062,7 +4065,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ15">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR15">
         <v>1.24</v>
@@ -4393,7 +4396,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4599,7 +4602,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4677,10 +4680,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ18">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR18">
         <v>1.16</v>
@@ -4883,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ19">
         <v>0.82</v>
@@ -5092,7 +5095,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR20">
         <v>1.3</v>
@@ -5423,7 +5426,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5504,7 +5507,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ22">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5629,7 +5632,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5707,7 +5710,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ23">
         <v>1.91</v>
@@ -6122,7 +6125,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ25">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR25">
         <v>1.38</v>
@@ -6247,7 +6250,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6325,7 +6328,7 @@
         <v>1.25</v>
       </c>
       <c r="AP26">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ26">
         <v>0.82</v>
@@ -6659,7 +6662,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6737,10 +6740,10 @@
         <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ28">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR28">
         <v>1.14</v>
@@ -6865,7 +6868,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -7071,7 +7074,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7149,7 +7152,7 @@
         <v>1.75</v>
       </c>
       <c r="AP30">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ30">
         <v>1.61</v>
@@ -7483,7 +7486,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7561,7 +7564,7 @@
         <v>0.8</v>
       </c>
       <c r="AP32">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ32">
         <v>1.17</v>
@@ -7770,7 +7773,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ33">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR33">
         <v>1.83</v>
@@ -7895,7 +7898,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7976,7 +7979,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR34">
         <v>1.34</v>
@@ -8101,7 +8104,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8307,7 +8310,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8385,7 +8388,7 @@
         <v>1.6</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ36">
         <v>1.83</v>
@@ -9131,7 +9134,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9212,7 +9215,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ40">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -9415,7 +9418,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ41">
         <v>0.82</v>
@@ -9543,7 +9546,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9621,7 +9624,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ42">
         <v>1.61</v>
@@ -9830,7 +9833,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ43">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR43">
         <v>1.5</v>
@@ -9955,7 +9958,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -10161,7 +10164,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10367,7 +10370,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10573,7 +10576,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -10651,10 +10654,10 @@
         <v>1.14</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ47">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -10860,7 +10863,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR48">
         <v>1.65</v>
@@ -11066,7 +11069,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ49">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR49">
         <v>1.28</v>
@@ -11269,7 +11272,7 @@
         <v>1.13</v>
       </c>
       <c r="AP50">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ50">
         <v>0.96</v>
@@ -11475,7 +11478,7 @@
         <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ51">
         <v>0.82</v>
@@ -11684,7 +11687,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ52">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR52">
         <v>1.57</v>
@@ -12015,7 +12018,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12299,7 +12302,7 @@
         <v>1.25</v>
       </c>
       <c r="AP55">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ55">
         <v>1.61</v>
@@ -12633,7 +12636,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -12917,10 +12920,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ58">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR58">
         <v>1.71</v>
@@ -13045,7 +13048,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -13123,7 +13126,7 @@
         <v>1.56</v>
       </c>
       <c r="AP59">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ59">
         <v>1.83</v>
@@ -13251,7 +13254,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13332,7 +13335,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ60">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR60">
         <v>1.65</v>
@@ -13663,7 +13666,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -13741,7 +13744,7 @@
         <v>1.2</v>
       </c>
       <c r="AP62">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ62">
         <v>1.61</v>
@@ -13950,7 +13953,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ63">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14281,7 +14284,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14568,7 +14571,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ66">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR66">
         <v>1.47</v>
@@ -14771,7 +14774,7 @@
         <v>1.2</v>
       </c>
       <c r="AP67">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ67">
         <v>0.96</v>
@@ -15105,7 +15108,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15311,7 +15314,7 @@
         <v>102</v>
       </c>
       <c r="P70" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q70">
         <v>3.1</v>
@@ -15723,7 +15726,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q72">
         <v>3.8</v>
@@ -15801,10 +15804,10 @@
         <v>1.64</v>
       </c>
       <c r="AP72">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ72">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR72">
         <v>1.29</v>
@@ -16007,10 +16010,10 @@
         <v>0.91</v>
       </c>
       <c r="AP73">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ73">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR73">
         <v>1.45</v>
@@ -16135,7 +16138,7 @@
         <v>84</v>
       </c>
       <c r="P74" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -16213,7 +16216,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ74">
         <v>1.17</v>
@@ -16341,7 +16344,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q75">
         <v>2.45</v>
@@ -16628,7 +16631,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ76">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR76">
         <v>1.6</v>
@@ -17037,7 +17040,7 @@
         <v>1.08</v>
       </c>
       <c r="AP78">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ78">
         <v>1.32</v>
@@ -17246,7 +17249,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ79">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR79">
         <v>1.28</v>
@@ -17783,7 +17786,7 @@
         <v>122</v>
       </c>
       <c r="P82" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q82">
         <v>4</v>
@@ -17861,7 +17864,7 @@
         <v>1.46</v>
       </c>
       <c r="AP82">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ82">
         <v>1.83</v>
@@ -17989,7 +17992,7 @@
         <v>84</v>
       </c>
       <c r="P83" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q83">
         <v>2.75</v>
@@ -18273,10 +18276,10 @@
         <v>0.77</v>
       </c>
       <c r="AP84">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ84">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR84">
         <v>1.28</v>
@@ -18401,7 +18404,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q85">
         <v>4.41</v>
@@ -18482,7 +18485,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ85">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR85">
         <v>1.32</v>
@@ -18607,7 +18610,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q86">
         <v>2.2</v>
@@ -18688,7 +18691,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ86">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR86">
         <v>1.64</v>
@@ -18813,7 +18816,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q87">
         <v>2.2</v>
@@ -18891,7 +18894,7 @@
         <v>1.07</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ87">
         <v>1.09</v>
@@ -19019,7 +19022,7 @@
         <v>84</v>
       </c>
       <c r="P88" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q88">
         <v>3.55</v>
@@ -19431,7 +19434,7 @@
         <v>141</v>
       </c>
       <c r="P90" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19509,7 +19512,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ90">
         <v>1.32</v>
@@ -19715,7 +19718,7 @@
         <v>1.43</v>
       </c>
       <c r="AP91">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ91">
         <v>1.17</v>
@@ -19924,7 +19927,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ92">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR92">
         <v>1.33</v>
@@ -20049,7 +20052,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q93">
         <v>3.2</v>
@@ -20127,10 +20130,10 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ93">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR93">
         <v>1.29</v>
@@ -20748,7 +20751,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ96">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR96">
         <v>1.44</v>
@@ -20873,7 +20876,7 @@
         <v>143</v>
       </c>
       <c r="P97" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q97">
         <v>4.8</v>
@@ -21157,7 +21160,7 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ98">
         <v>1.09</v>
@@ -21285,7 +21288,7 @@
         <v>84</v>
       </c>
       <c r="P99" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21366,7 +21369,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ99">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -21491,7 +21494,7 @@
         <v>146</v>
       </c>
       <c r="P100" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q100">
         <v>2.8</v>
@@ -21572,7 +21575,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ100">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR100">
         <v>1.58</v>
@@ -21775,7 +21778,7 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ101">
         <v>1.32</v>
@@ -22109,7 +22112,7 @@
         <v>147</v>
       </c>
       <c r="P103" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q103">
         <v>3.15</v>
@@ -22396,7 +22399,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ104">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR104">
         <v>1.47</v>
@@ -22521,7 +22524,7 @@
         <v>149</v>
       </c>
       <c r="P105" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22602,7 +22605,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ105">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR105">
         <v>1.31</v>
@@ -22727,7 +22730,7 @@
         <v>84</v>
       </c>
       <c r="P106" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q106">
         <v>3.65</v>
@@ -22805,7 +22808,7 @@
         <v>1.65</v>
       </c>
       <c r="AP106">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ106">
         <v>1.83</v>
@@ -22933,7 +22936,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23139,7 +23142,7 @@
         <v>84</v>
       </c>
       <c r="P108" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q108">
         <v>2.2</v>
@@ -23217,7 +23220,7 @@
         <v>1.06</v>
       </c>
       <c r="AP108">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ108">
         <v>0.96</v>
@@ -23551,7 +23554,7 @@
         <v>151</v>
       </c>
       <c r="P110" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -24041,7 +24044,7 @@
         <v>1.11</v>
       </c>
       <c r="AP112">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ112">
         <v>1.09</v>
@@ -24169,7 +24172,7 @@
         <v>154</v>
       </c>
       <c r="P113" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q113">
         <v>2.15</v>
@@ -24453,10 +24456,10 @@
         <v>1.61</v>
       </c>
       <c r="AP114">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ114">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR114">
         <v>1.32</v>
@@ -24581,7 +24584,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q115">
         <v>2.9</v>
@@ -24659,7 +24662,7 @@
         <v>1.17</v>
       </c>
       <c r="AP115">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ115">
         <v>1.32</v>
@@ -25074,7 +25077,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ117">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR117">
         <v>1.54</v>
@@ -25199,7 +25202,7 @@
         <v>157</v>
       </c>
       <c r="P118" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q118">
         <v>3.3</v>
@@ -25280,7 +25283,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ118">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR118">
         <v>1.28</v>
@@ -25611,7 +25614,7 @@
         <v>97</v>
       </c>
       <c r="P120" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q120">
         <v>3.25</v>
@@ -25692,7 +25695,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ120">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR120">
         <v>1.3</v>
@@ -25895,7 +25898,7 @@
         <v>1.95</v>
       </c>
       <c r="AP121">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ121">
         <v>1.91</v>
@@ -26023,7 +26026,7 @@
         <v>158</v>
       </c>
       <c r="P122" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q122">
         <v>2.71</v>
@@ -26101,7 +26104,7 @@
         <v>1.05</v>
       </c>
       <c r="AP122">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AQ122">
         <v>1.09</v>
@@ -26516,7 +26519,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ124">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR124">
         <v>1.56</v>
@@ -26719,10 +26722,10 @@
         <v>1.55</v>
       </c>
       <c r="AP125">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ125">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR125">
         <v>1.66</v>
@@ -27053,7 +27056,7 @@
         <v>159</v>
       </c>
       <c r="P127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q127">
         <v>3.7</v>
@@ -27259,7 +27262,7 @@
         <v>162</v>
       </c>
       <c r="P128" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q128">
         <v>4.33</v>
@@ -27340,7 +27343,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ128">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR128">
         <v>1.26</v>
@@ -27465,7 +27468,7 @@
         <v>147</v>
       </c>
       <c r="P129" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q129">
         <v>6</v>
@@ -27749,7 +27752,7 @@
         <v>1.24</v>
       </c>
       <c r="AP130">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ130">
         <v>1.17</v>
@@ -27958,7 +27961,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ131">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AR131">
         <v>1.52</v>
@@ -28083,7 +28086,7 @@
         <v>84</v>
       </c>
       <c r="P132" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q132">
         <v>3.8</v>
@@ -28161,7 +28164,7 @@
         <v>1.95</v>
       </c>
       <c r="AP132">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ132">
         <v>1.91</v>
@@ -28495,7 +28498,7 @@
         <v>164</v>
       </c>
       <c r="P134" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -28701,7 +28704,7 @@
         <v>165</v>
       </c>
       <c r="P135" t="s">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="Q135">
         <v>1.94</v>
@@ -28800,25 +28803,25 @@
         <v>5</v>
       </c>
       <c r="AW135">
+        <v>7</v>
+      </c>
+      <c r="AX135">
+        <v>6</v>
+      </c>
+      <c r="AY135">
+        <v>14</v>
+      </c>
+      <c r="AZ135">
+        <v>11</v>
+      </c>
+      <c r="BA135">
         <v>4</v>
       </c>
-      <c r="AX135">
-        <v>4</v>
-      </c>
-      <c r="AY135">
-        <v>11</v>
-      </c>
-      <c r="AZ135">
-        <v>9</v>
-      </c>
-      <c r="BA135">
+      <c r="BB135">
+        <v>2</v>
+      </c>
+      <c r="BC135">
         <v>6</v>
-      </c>
-      <c r="BB135">
-        <v>3</v>
-      </c>
-      <c r="BC135">
-        <v>9</v>
       </c>
       <c r="BD135">
         <v>1.22</v>
@@ -29064,6 +29067,418 @@
       </c>
       <c r="BP136">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7771410</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45844.66666666666</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137" t="s">
+        <v>74</v>
+      </c>
+      <c r="H137" t="s">
+        <v>78</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>2</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137">
+        <v>1</v>
+      </c>
+      <c r="N137">
+        <v>2</v>
+      </c>
+      <c r="O137" t="s">
+        <v>122</v>
+      </c>
+      <c r="P137" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q137">
+        <v>2.9</v>
+      </c>
+      <c r="R137">
+        <v>1.87</v>
+      </c>
+      <c r="S137">
+        <v>4.1</v>
+      </c>
+      <c r="T137">
+        <v>1.5</v>
+      </c>
+      <c r="U137">
+        <v>2.4</v>
+      </c>
+      <c r="V137">
+        <v>3.3</v>
+      </c>
+      <c r="W137">
+        <v>1.29</v>
+      </c>
+      <c r="X137">
+        <v>9.5</v>
+      </c>
+      <c r="Y137">
+        <v>1.01</v>
+      </c>
+      <c r="Z137">
+        <v>2.13</v>
+      </c>
+      <c r="AA137">
+        <v>2.93</v>
+      </c>
+      <c r="AB137">
+        <v>3.25</v>
+      </c>
+      <c r="AC137">
+        <v>1.06</v>
+      </c>
+      <c r="AD137">
+        <v>6.5</v>
+      </c>
+      <c r="AE137">
+        <v>1.44</v>
+      </c>
+      <c r="AF137">
+        <v>2.5</v>
+      </c>
+      <c r="AG137">
+        <v>2.4</v>
+      </c>
+      <c r="AH137">
+        <v>1.51</v>
+      </c>
+      <c r="AI137">
+        <v>2.05</v>
+      </c>
+      <c r="AJ137">
+        <v>1.73</v>
+      </c>
+      <c r="AK137">
+        <v>1.36</v>
+      </c>
+      <c r="AL137">
+        <v>0</v>
+      </c>
+      <c r="AM137">
+        <v>1.65</v>
+      </c>
+      <c r="AN137">
+        <v>1.5</v>
+      </c>
+      <c r="AO137">
+        <v>1.14</v>
+      </c>
+      <c r="AP137">
+        <v>1.48</v>
+      </c>
+      <c r="AQ137">
+        <v>1.13</v>
+      </c>
+      <c r="AR137">
+        <v>1.63</v>
+      </c>
+      <c r="AS137">
+        <v>1.67</v>
+      </c>
+      <c r="AT137">
+        <v>3.3</v>
+      </c>
+      <c r="AU137">
+        <v>5</v>
+      </c>
+      <c r="AV137">
+        <v>4</v>
+      </c>
+      <c r="AW137">
+        <v>9</v>
+      </c>
+      <c r="AX137">
+        <v>3</v>
+      </c>
+      <c r="AY137">
+        <v>14</v>
+      </c>
+      <c r="AZ137">
+        <v>7</v>
+      </c>
+      <c r="BA137">
+        <v>3</v>
+      </c>
+      <c r="BB137">
+        <v>2</v>
+      </c>
+      <c r="BC137">
+        <v>5</v>
+      </c>
+      <c r="BD137">
+        <v>1.77</v>
+      </c>
+      <c r="BE137">
+        <v>6.25</v>
+      </c>
+      <c r="BF137">
+        <v>1.95</v>
+      </c>
+      <c r="BG137">
+        <v>1.43</v>
+      </c>
+      <c r="BH137">
+        <v>2.5</v>
+      </c>
+      <c r="BI137">
+        <v>1.75</v>
+      </c>
+      <c r="BJ137">
+        <v>1.95</v>
+      </c>
+      <c r="BK137">
+        <v>2.33</v>
+      </c>
+      <c r="BL137">
+        <v>1.57</v>
+      </c>
+      <c r="BM137">
+        <v>2.9</v>
+      </c>
+      <c r="BN137">
+        <v>1.36</v>
+      </c>
+      <c r="BO137">
+        <v>3.8</v>
+      </c>
+      <c r="BP137">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7771409</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45844.77083333334</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138" t="s">
+        <v>79</v>
+      </c>
+      <c r="H138" t="s">
+        <v>72</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>3</v>
+      </c>
+      <c r="M138">
+        <v>1</v>
+      </c>
+      <c r="N138">
+        <v>4</v>
+      </c>
+      <c r="O138" t="s">
+        <v>166</v>
+      </c>
+      <c r="P138" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q138">
+        <v>3.1</v>
+      </c>
+      <c r="R138">
+        <v>1.83</v>
+      </c>
+      <c r="S138">
+        <v>4</v>
+      </c>
+      <c r="T138">
+        <v>1.57</v>
+      </c>
+      <c r="U138">
+        <v>2.25</v>
+      </c>
+      <c r="V138">
+        <v>3.3</v>
+      </c>
+      <c r="W138">
+        <v>1.27</v>
+      </c>
+      <c r="X138">
+        <v>10</v>
+      </c>
+      <c r="Y138">
+        <v>1.03</v>
+      </c>
+      <c r="Z138">
+        <v>2.28</v>
+      </c>
+      <c r="AA138">
+        <v>2.92</v>
+      </c>
+      <c r="AB138">
+        <v>3.18</v>
+      </c>
+      <c r="AC138">
+        <v>1.11</v>
+      </c>
+      <c r="AD138">
+        <v>6.5</v>
+      </c>
+      <c r="AE138">
+        <v>1.49</v>
+      </c>
+      <c r="AF138">
+        <v>2.4</v>
+      </c>
+      <c r="AG138">
+        <v>2.6</v>
+      </c>
+      <c r="AH138">
+        <v>1.5</v>
+      </c>
+      <c r="AI138">
+        <v>2.05</v>
+      </c>
+      <c r="AJ138">
+        <v>1.72</v>
+      </c>
+      <c r="AK138">
+        <v>1.4</v>
+      </c>
+      <c r="AL138">
+        <v>0</v>
+      </c>
+      <c r="AM138">
+        <v>1.57</v>
+      </c>
+      <c r="AN138">
+        <v>1.73</v>
+      </c>
+      <c r="AO138">
+        <v>0.82</v>
+      </c>
+      <c r="AP138">
+        <v>1.78</v>
+      </c>
+      <c r="AQ138">
+        <v>0.78</v>
+      </c>
+      <c r="AR138">
+        <v>1.3</v>
+      </c>
+      <c r="AS138">
+        <v>1.29</v>
+      </c>
+      <c r="AT138">
+        <v>2.59</v>
+      </c>
+      <c r="AU138">
+        <v>6</v>
+      </c>
+      <c r="AV138">
+        <v>3</v>
+      </c>
+      <c r="AW138">
+        <v>2</v>
+      </c>
+      <c r="AX138">
+        <v>6</v>
+      </c>
+      <c r="AY138">
+        <v>8</v>
+      </c>
+      <c r="AZ138">
+        <v>9</v>
+      </c>
+      <c r="BA138">
+        <v>4</v>
+      </c>
+      <c r="BB138">
+        <v>4</v>
+      </c>
+      <c r="BC138">
+        <v>8</v>
+      </c>
+      <c r="BD138">
+        <v>2.16</v>
+      </c>
+      <c r="BE138">
+        <v>6.73</v>
+      </c>
+      <c r="BF138">
+        <v>2.13</v>
+      </c>
+      <c r="BG138">
+        <v>1.5</v>
+      </c>
+      <c r="BH138">
+        <v>2.4</v>
+      </c>
+      <c r="BI138">
+        <v>1.8</v>
+      </c>
+      <c r="BJ138">
+        <v>1.82</v>
+      </c>
+      <c r="BK138">
+        <v>2.41</v>
+      </c>
+      <c r="BL138">
+        <v>1.45</v>
+      </c>
+      <c r="BM138">
+        <v>3.34</v>
+      </c>
+      <c r="BN138">
+        <v>1.33</v>
+      </c>
+      <c r="BO138">
+        <v>4</v>
+      </c>
+      <c r="BP138">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -28803,25 +28803,25 @@
         <v>5</v>
       </c>
       <c r="AW135">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX135">
+        <v>4</v>
+      </c>
+      <c r="AY135">
+        <v>11</v>
+      </c>
+      <c r="AZ135">
+        <v>9</v>
+      </c>
+      <c r="BA135">
         <v>6</v>
       </c>
-      <c r="AY135">
-        <v>14</v>
-      </c>
-      <c r="AZ135">
-        <v>11</v>
-      </c>
-      <c r="BA135">
-        <v>4</v>
-      </c>
       <c r="BB135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC135">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD135">
         <v>1.22</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Paraguay Division Profesional_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -515,6 +515,9 @@
   </si>
   <si>
     <t>['45+1', '79', '90+5']</t>
+  </si>
+  <si>
+    <t>['30']</t>
   </si>
   <si>
     <t>['7', '90']</t>
@@ -1050,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP138"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1306,7 +1309,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -1387,7 +1390,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ2">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1512,7 +1515,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1593,7 +1596,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ3">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1924,7 +1927,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -2130,7 +2133,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2336,7 +2339,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2542,7 +2545,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2620,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ8">
         <v>1.61</v>
@@ -2748,7 +2751,7 @@
         <v>84</v>
       </c>
       <c r="P9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3160,7 +3163,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3572,7 +3575,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q13">
         <v>4.33</v>
@@ -3650,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ13">
         <v>1.48</v>
@@ -4271,7 +4274,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ16">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR16">
         <v>1.31</v>
@@ -4396,7 +4399,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4602,7 +4605,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>3.75</v>
@@ -4889,7 +4892,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ19">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR19">
         <v>1.79</v>
@@ -5426,7 +5429,7 @@
         <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q22">
         <v>4.79</v>
@@ -5632,7 +5635,7 @@
         <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q23">
         <v>3.74</v>
@@ -5916,7 +5919,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ24">
         <v>0.96</v>
@@ -6122,7 +6125,7 @@
         <v>1.33</v>
       </c>
       <c r="AP25">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ25">
         <v>0.78</v>
@@ -6250,7 +6253,7 @@
         <v>100</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>2.6</v>
@@ -6331,7 +6334,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ26">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR26">
         <v>1.14</v>
@@ -6662,7 +6665,7 @@
         <v>102</v>
       </c>
       <c r="P28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>3.25</v>
@@ -6868,7 +6871,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q29">
         <v>1.8</v>
@@ -7074,7 +7077,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7361,7 +7364,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ31">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR31">
         <v>1.72</v>
@@ -7486,7 +7489,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q32">
         <v>2.6</v>
@@ -7898,7 +7901,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>3.29</v>
@@ -7976,7 +7979,7 @@
         <v>0.2</v>
       </c>
       <c r="AP34">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ34">
         <v>1.13</v>
@@ -8104,7 +8107,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>5.47</v>
@@ -8182,7 +8185,7 @@
         <v>2.6</v>
       </c>
       <c r="AP35">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ35">
         <v>1.91</v>
@@ -8310,7 +8313,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8803,7 +8806,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ38">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR38">
         <v>1.26</v>
@@ -9134,7 +9137,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q40">
         <v>4.4</v>
@@ -9421,7 +9424,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ41">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR41">
         <v>1.17</v>
@@ -9546,7 +9549,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9958,7 +9961,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q44">
         <v>3.5</v>
@@ -10036,7 +10039,7 @@
         <v>1.14</v>
       </c>
       <c r="AP44">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ44">
         <v>1.17</v>
@@ -10164,7 +10167,7 @@
         <v>116</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q45">
         <v>4.6</v>
@@ -10370,7 +10373,7 @@
         <v>84</v>
       </c>
       <c r="P46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10576,7 +10579,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -11066,7 +11069,7 @@
         <v>2.14</v>
       </c>
       <c r="AP49">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ49">
         <v>1.78</v>
@@ -11481,7 +11484,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ51">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR51">
         <v>1.14</v>
@@ -11893,7 +11896,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ53">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR53">
         <v>1.53</v>
@@ -12018,7 +12021,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12636,7 +12639,7 @@
         <v>84</v>
       </c>
       <c r="P57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q57">
         <v>4.75</v>
@@ -13048,7 +13051,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q59">
         <v>4.96</v>
@@ -13254,7 +13257,7 @@
         <v>84</v>
       </c>
       <c r="P60" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q60">
         <v>3.5</v>
@@ -13538,10 +13541,10 @@
         <v>1.33</v>
       </c>
       <c r="AP61">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ61">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR61">
         <v>1.44</v>
@@ -13666,7 +13669,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -14159,7 +14162,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ64">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR64">
         <v>1.44</v>
@@ -14284,7 +14287,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14362,7 +14365,7 @@
         <v>0.9</v>
       </c>
       <c r="AP65">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ65">
         <v>1.09</v>
@@ -15108,7 +15111,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15186,7 +15189,7 @@
         <v>1.36</v>
       </c>
       <c r="AP69">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ69">
         <v>1.61</v>
@@ -15314,7 +15317,7 @@
         <v>102</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q70">
         <v>3.1</v>
@@ -15392,7 +15395,7 @@
         <v>0.91</v>
       </c>
       <c r="AP70">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ70">
         <v>1.09</v>
@@ -15726,7 +15729,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q72">
         <v>3.8</v>
@@ -16138,7 +16141,7 @@
         <v>84</v>
       </c>
       <c r="P74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -16344,7 +16347,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q75">
         <v>2.45</v>
@@ -16425,7 +16428,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ75">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR75">
         <v>1.43</v>
@@ -17043,7 +17046,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ78">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR78">
         <v>1.69</v>
@@ -17786,7 +17789,7 @@
         <v>122</v>
       </c>
       <c r="P82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q82">
         <v>4</v>
@@ -17992,7 +17995,7 @@
         <v>84</v>
       </c>
       <c r="P83" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q83">
         <v>2.75</v>
@@ -18070,7 +18073,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ83">
         <v>0.96</v>
@@ -18404,7 +18407,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q85">
         <v>4.41</v>
@@ -18482,7 +18485,7 @@
         <v>1.46</v>
       </c>
       <c r="AP85">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ85">
         <v>1.48</v>
@@ -18610,7 +18613,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q86">
         <v>2.2</v>
@@ -18816,7 +18819,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q87">
         <v>2.2</v>
@@ -19022,7 +19025,7 @@
         <v>84</v>
       </c>
       <c r="P88" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q88">
         <v>3.55</v>
@@ -19103,7 +19106,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ88">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR88">
         <v>1.25</v>
@@ -19434,7 +19437,7 @@
         <v>141</v>
       </c>
       <c r="P90" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19515,7 +19518,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ90">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR90">
         <v>1.27</v>
@@ -19924,7 +19927,7 @@
         <v>0.87</v>
       </c>
       <c r="AP92">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ92">
         <v>0.78</v>
@@ -20052,7 +20055,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q93">
         <v>3.2</v>
@@ -20542,7 +20545,7 @@
         <v>2.27</v>
       </c>
       <c r="AP95">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ95">
         <v>1.91</v>
@@ -20876,7 +20879,7 @@
         <v>143</v>
       </c>
       <c r="P97" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q97">
         <v>4.8</v>
@@ -21288,7 +21291,7 @@
         <v>84</v>
       </c>
       <c r="P99" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21494,7 +21497,7 @@
         <v>146</v>
       </c>
       <c r="P100" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q100">
         <v>2.8</v>
@@ -21781,7 +21784,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ101">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR101">
         <v>1.59</v>
@@ -21987,7 +21990,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ102">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR102">
         <v>1.57</v>
@@ -22112,7 +22115,7 @@
         <v>147</v>
       </c>
       <c r="P103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q103">
         <v>3.15</v>
@@ -22524,7 +22527,7 @@
         <v>149</v>
       </c>
       <c r="P105" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22602,7 +22605,7 @@
         <v>0.88</v>
       </c>
       <c r="AP105">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ105">
         <v>1.13</v>
@@ -22730,7 +22733,7 @@
         <v>84</v>
       </c>
       <c r="P106" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q106">
         <v>3.65</v>
@@ -22936,7 +22939,7 @@
         <v>150</v>
       </c>
       <c r="P107" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23014,7 +23017,7 @@
         <v>1.24</v>
       </c>
       <c r="AP107">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ107">
         <v>1.17</v>
@@ -23142,7 +23145,7 @@
         <v>84</v>
       </c>
       <c r="P108" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q108">
         <v>2.2</v>
@@ -23554,7 +23557,7 @@
         <v>151</v>
       </c>
       <c r="P110" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q110">
         <v>3</v>
@@ -23635,7 +23638,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ110">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR110">
         <v>1.41</v>
@@ -24172,7 +24175,7 @@
         <v>154</v>
       </c>
       <c r="P113" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q113">
         <v>2.15</v>
@@ -24584,7 +24587,7 @@
         <v>155</v>
       </c>
       <c r="P115" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q115">
         <v>2.9</v>
@@ -24665,7 +24668,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ115">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR115">
         <v>1.32</v>
@@ -25202,7 +25205,7 @@
         <v>157</v>
       </c>
       <c r="P118" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q118">
         <v>3.3</v>
@@ -25486,7 +25489,7 @@
         <v>1.79</v>
       </c>
       <c r="AP119">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ119">
         <v>1.83</v>
@@ -25614,7 +25617,7 @@
         <v>97</v>
       </c>
       <c r="P120" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q120">
         <v>3.25</v>
@@ -25692,7 +25695,7 @@
         <v>1.68</v>
       </c>
       <c r="AP120">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ120">
         <v>1.78</v>
@@ -26026,7 +26029,7 @@
         <v>158</v>
       </c>
       <c r="P122" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q122">
         <v>2.71</v>
@@ -26928,10 +26931,10 @@
         <v>0.9</v>
       </c>
       <c r="AP126">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ126">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AR126">
         <v>1.3</v>
@@ -27056,7 +27059,7 @@
         <v>159</v>
       </c>
       <c r="P127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q127">
         <v>3.7</v>
@@ -27262,7 +27265,7 @@
         <v>162</v>
       </c>
       <c r="P128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q128">
         <v>4.33</v>
@@ -27468,7 +27471,7 @@
         <v>147</v>
       </c>
       <c r="P129" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q129">
         <v>6</v>
@@ -27546,7 +27549,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AQ129">
         <v>1.83</v>
@@ -28086,7 +28089,7 @@
         <v>84</v>
       </c>
       <c r="P132" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q132">
         <v>3.8</v>
@@ -28373,7 +28376,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ133">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR133">
         <v>1.38</v>
@@ -28498,7 +28501,7 @@
         <v>164</v>
       </c>
       <c r="P134" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -29322,7 +29325,7 @@
         <v>166</v>
       </c>
       <c r="P138" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q138">
         <v>3.1</v>
@@ -29479,6 +29482,212 @@
       </c>
       <c r="BP138">
         <v>1.1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7771412</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45845.77083333334</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139" t="s">
+        <v>80</v>
+      </c>
+      <c r="H139" t="s">
+        <v>76</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="O139" t="s">
+        <v>167</v>
+      </c>
+      <c r="P139" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q139">
+        <v>2.35</v>
+      </c>
+      <c r="R139">
+        <v>2.01</v>
+      </c>
+      <c r="S139">
+        <v>5.6</v>
+      </c>
+      <c r="T139">
+        <v>1.5</v>
+      </c>
+      <c r="U139">
+        <v>2.25</v>
+      </c>
+      <c r="V139">
+        <v>3.5</v>
+      </c>
+      <c r="W139">
+        <v>1.25</v>
+      </c>
+      <c r="X139">
+        <v>7.5</v>
+      </c>
+      <c r="Y139">
+        <v>1.04</v>
+      </c>
+      <c r="Z139">
+        <v>1.6</v>
+      </c>
+      <c r="AA139">
+        <v>3.4</v>
+      </c>
+      <c r="AB139">
+        <v>5</v>
+      </c>
+      <c r="AC139">
+        <v>1.05</v>
+      </c>
+      <c r="AD139">
+        <v>8</v>
+      </c>
+      <c r="AE139">
+        <v>1.47</v>
+      </c>
+      <c r="AF139">
+        <v>2.43</v>
+      </c>
+      <c r="AG139">
+        <v>2.6</v>
+      </c>
+      <c r="AH139">
+        <v>1.44</v>
+      </c>
+      <c r="AI139">
+        <v>2.3</v>
+      </c>
+      <c r="AJ139">
+        <v>1.57</v>
+      </c>
+      <c r="AK139">
+        <v>1.31</v>
+      </c>
+      <c r="AL139">
+        <v>1.31</v>
+      </c>
+      <c r="AM139">
+        <v>2.1</v>
+      </c>
+      <c r="AN139">
+        <v>1.32</v>
+      </c>
+      <c r="AO139">
+        <v>0.82</v>
+      </c>
+      <c r="AP139">
+        <v>1.39</v>
+      </c>
+      <c r="AQ139">
+        <v>0.78</v>
+      </c>
+      <c r="AR139">
+        <v>1.34</v>
+      </c>
+      <c r="AS139">
+        <v>1.29</v>
+      </c>
+      <c r="AT139">
+        <v>2.63</v>
+      </c>
+      <c r="AU139">
+        <v>6</v>
+      </c>
+      <c r="AV139">
+        <v>2</v>
+      </c>
+      <c r="AW139">
+        <v>15</v>
+      </c>
+      <c r="AX139">
+        <v>3</v>
+      </c>
+      <c r="AY139">
+        <v>21</v>
+      </c>
+      <c r="AZ139">
+        <v>5</v>
+      </c>
+      <c r="BA139">
+        <v>6</v>
+      </c>
+      <c r="BB139">
+        <v>6</v>
+      </c>
+      <c r="BC139">
+        <v>12</v>
+      </c>
+      <c r="BD139">
+        <v>1.58</v>
+      </c>
+      <c r="BE139">
+        <v>7.7</v>
+      </c>
+      <c r="BF139">
+        <v>3.13</v>
+      </c>
+      <c r="BG139">
+        <v>1.57</v>
+      </c>
+      <c r="BH139">
+        <v>2.25</v>
+      </c>
+      <c r="BI139">
+        <v>1.94</v>
+      </c>
+      <c r="BJ139">
+        <v>1.8</v>
+      </c>
+      <c r="BK139">
+        <v>2.56</v>
+      </c>
+      <c r="BL139">
+        <v>1.5</v>
+      </c>
+      <c r="BM139">
+        <v>3.3</v>
+      </c>
+      <c r="BN139">
+        <v>1.23</v>
+      </c>
+      <c r="BO139">
+        <v>5.1</v>
+      </c>
+      <c r="BP139">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>
